--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Misc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2BE308-2B49-4BE2-A5FC-C09A8A3343FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBC9001-FE05-40F6-87D7-CED6FF139481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5025" yWindow="0" windowWidth="28770" windowHeight="20985" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="3885" yWindow="825" windowWidth="24360" windowHeight="16905" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="71">
   <si>
     <t>Total</t>
   </si>
@@ -285,6 +285,12 @@
   <si>
     <t>Sparky to Serra</t>
   </si>
+  <si>
+    <t>Be you</t>
+  </si>
+  <si>
+    <t>Sick (not sure why I used "Be You" insteaed of actual sick time)</t>
+  </si>
 </sst>
 </file>
 
@@ -332,7 +338,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -405,14 +411,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="75">
+  <borders count="76">
     <border>
       <left/>
       <right/>
@@ -1386,11 +1386,22 @@
         <color auto="1"/>
       </diagonal>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="331">
+  <cellXfs count="327">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2318,35 +2329,23 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="74" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="53" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="64" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2593,7 +2592,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>557335</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>81149</xdr:rowOff>
+      <xdr:rowOff>92355</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2679,9 +2678,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>446144</xdr:colOff>
+      <xdr:colOff>446143</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>17300</xdr:rowOff>
+      <xdr:rowOff>28505</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3822,7 +3821,7 @@
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="57" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3932,11 +3931,11 @@
       </c>
       <c r="D8" s="2">
         <f>C8-E8</f>
-        <v>4</v>
+        <v>11.999999999999998</v>
       </c>
       <c r="E8" s="1">
         <f>C8 - SUMIF(H14:H36, "Be You", G14:G36)</f>
-        <v>12</v>
+        <v>4.0000000000000018</v>
       </c>
       <c r="J8" s="51"/>
     </row>
@@ -3950,11 +3949,11 @@
       </c>
       <c r="D9" s="7">
         <f>D8/8</f>
-        <v>0.5</v>
+        <v>1.4999999999999998</v>
       </c>
       <c r="E9" s="15">
         <f>E8/8</f>
-        <v>1.5</v>
+        <v>0.50000000000000022</v>
       </c>
     </row>
     <row r="10" spans="2:11">
@@ -4025,66 +4024,76 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B14" s="321"/>
-      <c r="C14" s="322" t="str">
-        <f t="shared" ref="C14:C36" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
-        <v>Sat</v>
-      </c>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="324">
-        <f t="shared" ref="F14:F36" si="1">((E14 - D14) * 24)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="325">
-        <f t="shared" ref="G14:G36" si="2">IF(F14 &gt; 4, (F14 - 1), F14)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="326"/>
+    <row r="14" spans="2:11">
+      <c r="B14" s="122">
+        <v>46059</v>
+      </c>
+      <c r="C14" s="240" t="str">
+        <f t="shared" ref="C14:C19" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
+        <v>Fri</v>
+      </c>
+      <c r="D14" s="241">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E14" s="241">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F14" s="263">
+        <f>((E14 - D14) * 24)</f>
+        <v>5</v>
+      </c>
+      <c r="G14" s="240">
+        <f t="shared" ref="G14:G19" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
+        <v>4</v>
+      </c>
+      <c r="H14" s="242" t="s">
+        <v>10</v>
+      </c>
       <c r="I14" s="196" t="s">
-        <v>67</v>
-      </c>
-      <c r="J14" s="327"/>
-      <c r="K14" s="192" t="str">
-        <f t="shared" ref="K14:K36" ca="1" si="3">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
-        <v>IDK!!</v>
+        <v>20</v>
+      </c>
+      <c r="J14" s="243" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" s="42" t="str">
+        <f t="shared" ref="K14:K19" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
+        <v>Passed</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B15" s="122">
-        <v>46059</v>
-      </c>
-      <c r="C15" s="240" t="str">
-        <f>IF(ISNUMBER(FIND("?", B15, 1)), "TBD", TEXT(B15, "ddd"))</f>
+      <c r="B15" s="321">
+        <v>46080</v>
+      </c>
+      <c r="C15" s="322" t="str">
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D15" s="328">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E15" s="328">
+      <c r="D15" s="323">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E15" s="323">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F15" s="329">
+      <c r="F15" s="324">
         <f>((E15 - D15) * 24)</f>
-        <v>5</v>
-      </c>
-      <c r="G15" s="330">
-        <f t="shared" ref="G15:G19" si="4">IF(F15 &gt; 4, (F15 - 1), F15)</f>
-        <v>4</v>
-      </c>
-      <c r="H15" s="242" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="243" t="s">
-        <v>68</v>
-      </c>
-      <c r="K15" s="47" t="str">
-        <f t="shared" ref="K15:K19" ca="1" si="5">IF(C15 = "TBD", "TBD", IF(B15 = "", "IDK!!", IF(TODAY() &gt; B15, "Passed", IF(TODAY() = B15, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G15" s="322">
+        <f>IF(F15 &gt; 4, (F15 - 1), F15)</f>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H15" s="325" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="326" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" s="60" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Passed</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="15.75" thickBot="1">
@@ -4092,7 +4101,7 @@
         <v>46164</v>
       </c>
       <c r="C16" s="271" t="str">
-        <f>IF(ISNUMBER(FIND("?", B16, 1)), "TBD", TEXT(B16, "ddd"))</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="D16" s="300">
@@ -4102,11 +4111,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F16" s="301">
-        <f t="shared" ref="F16:F19" si="6">((E16 - D16) * 24)</f>
+        <f t="shared" ref="F16:F19" si="3">((E16 - D16) * 24)</f>
         <v>5</v>
       </c>
       <c r="G16" s="299">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H16" s="272" t="s">
@@ -4119,7 +4128,7 @@
         <v>42</v>
       </c>
       <c r="K16" s="47" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4128,7 +4137,7 @@
         <v>46213</v>
       </c>
       <c r="C17" s="217" t="str">
-        <f>IF(ISNUMBER(FIND("?", B17, 1)), "TBD", TEXT(B17, "ddd"))</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="D17" s="287">
@@ -4138,11 +4147,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F17" s="290">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G17" s="165">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>7.9999999999999982</v>
       </c>
       <c r="H17" s="288" t="s">
@@ -4155,7 +4164,7 @@
         <v>61</v>
       </c>
       <c r="K17" s="47" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4164,7 +4173,7 @@
         <v>46237</v>
       </c>
       <c r="C18" s="240" t="str">
-        <f>IF(ISNUMBER(FIND("?", B18, 1)), "TBD", TEXT(B18, "ddd"))</f>
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="D18" s="241">
@@ -4174,11 +4183,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F18" s="263">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="G18" s="240">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H18" s="242" t="s">
@@ -4191,7 +4200,7 @@
         <v>59</v>
       </c>
       <c r="K18" s="258" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4200,7 +4209,7 @@
         <v>46238</v>
       </c>
       <c r="C19" s="250" t="str">
-        <f>IF(ISNUMBER(FIND("?", B19, 1)), "TBD", TEXT(B19, "ddd"))</f>
+        <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
       <c r="D19" s="251">
@@ -4210,11 +4219,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F19" s="264">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="G19" s="250">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H19" s="252" t="s">
@@ -4227,7 +4236,7 @@
         <v>59</v>
       </c>
       <c r="K19" s="59" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4236,7 +4245,7 @@
         <v>46239</v>
       </c>
       <c r="C20" s="250" t="str">
-        <f t="shared" ref="C20:C34" si="7">IF(ISNUMBER(FIND("?", B20, 1)), "TBD", TEXT(B20, "ddd"))</f>
+        <f t="shared" ref="C20:C34" si="4">IF(ISNUMBER(FIND("?", B20, 1)), "TBD", TEXT(B20, "ddd"))</f>
         <v>Wed</v>
       </c>
       <c r="D20" s="251">
@@ -4246,11 +4255,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F20" s="264">
-        <f t="shared" ref="F20:F31" si="8">((E20 - D20) * 24)</f>
+        <f t="shared" ref="F20:F31" si="5">((E20 - D20) * 24)</f>
         <v>5</v>
       </c>
       <c r="G20" s="250">
-        <f t="shared" ref="G20:G34" si="9">IF(F20 &gt; 4, (F20 - 1), F20)</f>
+        <f t="shared" ref="G20:G34" si="6">IF(F20 &gt; 4, (F20 - 1), F20)</f>
         <v>4</v>
       </c>
       <c r="H20" s="252" t="s">
@@ -4263,7 +4272,7 @@
         <v>59</v>
       </c>
       <c r="K20" s="59" t="str">
-        <f t="shared" ref="K20:K34" ca="1" si="10">IF(C20 = "TBD", "TBD", IF(B20 = "", "IDK!!", IF(TODAY() &gt; B20, "Passed", IF(TODAY() = B20, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="K20:K34" ca="1" si="7">IF(C20 = "TBD", "TBD", IF(B20 = "", "IDK!!", IF(TODAY() &gt; B20, "Passed", IF(TODAY() = B20, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4272,7 +4281,7 @@
         <v>46240</v>
       </c>
       <c r="C21" s="250" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Thu</v>
       </c>
       <c r="D21" s="251">
@@ -4282,11 +4291,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F21" s="264">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="G21" s="250">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H21" s="252" t="s">
@@ -4299,7 +4308,7 @@
         <v>59</v>
       </c>
       <c r="K21" s="59" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4308,7 +4317,7 @@
         <v>46241</v>
       </c>
       <c r="C22" s="250" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Fri</v>
       </c>
       <c r="D22" s="251">
@@ -4318,11 +4327,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F22" s="264">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="G22" s="250">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H22" s="252" t="s">
@@ -4335,7 +4344,7 @@
         <v>59</v>
       </c>
       <c r="K22" s="59" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4344,7 +4353,7 @@
         <v>46244</v>
       </c>
       <c r="C23" s="250" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Mon</v>
       </c>
       <c r="D23" s="251">
@@ -4354,11 +4363,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F23" s="264">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="G23" s="250">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H23" s="252" t="s">
@@ -4371,7 +4380,7 @@
         <v>39</v>
       </c>
       <c r="K23" s="59" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4380,7 +4389,7 @@
         <v>46245</v>
       </c>
       <c r="C24" s="250" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Tue</v>
       </c>
       <c r="D24" s="251">
@@ -4390,11 +4399,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F24" s="264">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="G24" s="250">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H24" s="252" t="s">
@@ -4407,7 +4416,7 @@
         <v>39</v>
       </c>
       <c r="K24" s="59" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4416,7 +4425,7 @@
         <v>46246</v>
       </c>
       <c r="C25" s="250" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Wed</v>
       </c>
       <c r="D25" s="251">
@@ -4426,11 +4435,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F25" s="264">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="G25" s="250">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H25" s="252" t="s">
@@ -4443,7 +4452,7 @@
         <v>39</v>
       </c>
       <c r="K25" s="59" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4452,7 +4461,7 @@
         <v>46247</v>
       </c>
       <c r="C26" s="250" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Thu</v>
       </c>
       <c r="D26" s="251">
@@ -4462,11 +4471,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F26" s="264">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="G26" s="250">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H26" s="252" t="s">
@@ -4479,7 +4488,7 @@
         <v>39</v>
       </c>
       <c r="K26" s="59" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4488,7 +4497,7 @@
         <v>46248</v>
       </c>
       <c r="C27" s="245" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Fri</v>
       </c>
       <c r="D27" s="246">
@@ -4498,11 +4507,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F27" s="268">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="G27" s="245">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H27" s="247" t="s">
@@ -4515,7 +4524,7 @@
         <v>39</v>
       </c>
       <c r="K27" s="257" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4524,7 +4533,7 @@
         <v>46269</v>
       </c>
       <c r="C28" s="311" t="str">
-        <f t="shared" ref="C28" si="11">IF(ISNUMBER(FIND("?", B28, 1)), "TBD", TEXT(B28, "ddd"))</f>
+        <f t="shared" ref="C28" si="8">IF(ISNUMBER(FIND("?", B28, 1)), "TBD", TEXT(B28, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D28" s="312">
@@ -4534,11 +4543,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F28" s="313">
-        <f t="shared" ref="F28" si="12">((E28 - D28) * 24)</f>
+        <f t="shared" ref="F28" si="9">((E28 - D28) * 24)</f>
         <v>5</v>
       </c>
       <c r="G28" s="311">
-        <f t="shared" ref="G28" si="13">IF(F28 &gt; 4, (F28 - 1), F28)</f>
+        <f t="shared" ref="G28" si="10">IF(F28 &gt; 4, (F28 - 1), F28)</f>
         <v>4</v>
       </c>
       <c r="H28" s="314" t="s">
@@ -4551,7 +4560,7 @@
         <v>24</v>
       </c>
       <c r="K28" s="192" t="str">
-        <f t="shared" ref="K28" ca="1" si="14">IF(C28 = "TBD", "TBD", IF(B28 = "", "IDK!!", IF(TODAY() &gt; B28, "Passed", IF(TODAY() = B28, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="K28" ca="1" si="11">IF(C28 = "TBD", "TBD", IF(B28 = "", "IDK!!", IF(TODAY() &gt; B28, "Passed", IF(TODAY() = B28, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4560,7 +4569,7 @@
         <v>46353</v>
       </c>
       <c r="C29" s="173" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Fri</v>
       </c>
       <c r="D29" s="155">
@@ -4570,11 +4579,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F29" s="226">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G29" s="173">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>7.9999999999999982</v>
       </c>
       <c r="H29" s="188" t="s">
@@ -4587,7 +4596,7 @@
         <v>14</v>
       </c>
       <c r="K29" s="192" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4596,7 +4605,7 @@
         <v>46380</v>
       </c>
       <c r="C30" s="271" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Thu</v>
       </c>
       <c r="D30" s="269">
@@ -4606,11 +4615,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F30" s="270">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G30" s="271">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>7.9999999999999982</v>
       </c>
       <c r="H30" s="272" t="s">
@@ -4623,7 +4632,7 @@
         <v>60</v>
       </c>
       <c r="K30" s="42" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4632,7 +4641,7 @@
         <v>46384</v>
       </c>
       <c r="C31" s="281" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Mon</v>
       </c>
       <c r="D31" s="282">
@@ -4642,11 +4651,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F31" s="283">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G31" s="281">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>7.9999999999999982</v>
       </c>
       <c r="H31" s="284" t="s">
@@ -4659,7 +4668,7 @@
         <v>60</v>
       </c>
       <c r="K31" s="59" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4668,7 +4677,7 @@
         <v>46385</v>
       </c>
       <c r="C32" s="278" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Tue</v>
       </c>
       <c r="D32" s="282">
@@ -4678,11 +4687,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F32" s="283">
-        <f t="shared" ref="F32:F34" si="15">((E32 - D32) * 24)</f>
+        <f t="shared" ref="F32:F34" si="12">((E32 - D32) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G32" s="281">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>7.9999999999999982</v>
       </c>
       <c r="H32" s="279" t="s">
@@ -4695,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="K32" s="193" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4704,7 +4713,7 @@
         <v>46386</v>
       </c>
       <c r="C33" s="278" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Wed</v>
       </c>
       <c r="D33" s="282">
@@ -4714,11 +4723,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F33" s="283">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G33" s="281">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>7.9999999999999982</v>
       </c>
       <c r="H33" s="279" t="s">
@@ -4731,7 +4740,7 @@
         <v>60</v>
       </c>
       <c r="K33" s="193" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4740,7 +4749,7 @@
         <v>46387</v>
       </c>
       <c r="C34" s="278" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>Thu</v>
       </c>
       <c r="D34" s="282">
@@ -4750,11 +4759,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F34" s="283">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G34" s="281">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>7.9999999999999982</v>
       </c>
       <c r="H34" s="274" t="s">
@@ -4767,24 +4776,24 @@
         <v>60</v>
       </c>
       <c r="K34" s="193" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="7"/>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="35" spans="2:11">
       <c r="B35" s="102"/>
       <c r="C35" s="165" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C35:C36" si="13">IF(ISNUMBER(FIND("?", B35, 1)), "TBD", TEXT(B35, "ddd"))</f>
         <v>Sat</v>
       </c>
       <c r="D35" s="157"/>
       <c r="E35" s="157"/>
       <c r="F35" s="220">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F35:F36" si="14">((E35 - D35) * 24)</f>
         <v>0</v>
       </c>
       <c r="G35" s="217">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G35:G36" si="15">IF(F35 &gt; 4, (F35 - 1), F35)</f>
         <v>0</v>
       </c>
       <c r="H35" s="180"/>
@@ -4793,24 +4802,24 @@
       </c>
       <c r="J35" s="205"/>
       <c r="K35" s="258" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ref="K35:K36" ca="1" si="16">IF(C35 = "TBD", "TBD", IF(B35 = "", "IDK!!", IF(TODAY() &gt; B35, "Passed", IF(TODAY() = B35, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
     </row>
     <row r="36" spans="2:11" ht="15.75" thickBot="1">
       <c r="B36" s="265"/>
       <c r="C36" s="259" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>Sat</v>
       </c>
       <c r="D36" s="266"/>
       <c r="E36" s="266"/>
       <c r="F36" s="267">
-        <f t="shared" si="1"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G36" s="259">
-        <f t="shared" si="2"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H36" s="260"/>
@@ -4819,7 +4828,7 @@
       </c>
       <c r="J36" s="261"/>
       <c r="K36" s="256" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="16"/>
         <v>IDK!!</v>
       </c>
     </row>
@@ -4832,11 +4841,11 @@
       <c r="E37" s="320"/>
       <c r="F37" s="228">
         <f>SUM(F14:F36)</f>
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G37" s="262">
         <f>SUM(G14:G36)</f>
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H37" s="316"/>
       <c r="I37" s="317"/>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBC9001-FE05-40F6-87D7-CED6FF139481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A317162-5171-47E1-8684-D89FE12257CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3885" yWindow="825" windowWidth="24360" windowHeight="16905" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="72">
   <si>
     <t>Total</t>
   </si>
@@ -291,6 +291,9 @@
   <si>
     <t>Sick (not sure why I used "Be You" insteaed of actual sick time)</t>
   </si>
+  <si>
+    <t>Meeting</t>
+  </si>
 </sst>
 </file>
 
@@ -1401,7 +1404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="327">
+  <cellXfs count="331">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2346,6 +2349,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2717,13 +2732,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>458322</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3811,7 +3826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:K37"/>
+  <dimension ref="B1:K38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -3853,7 +3868,7 @@
         <v>144</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H36, "PTO", G14:G36)</f>
+        <f ca="1">C3 - C6 - SUMIF(H14:H37, "PTO", G14:G37)</f>
         <v>24.5</v>
       </c>
       <c r="J3" s="56" t="str" cm="1">
@@ -3901,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H36, "Sick", G14:G36)</f>
+        <f>C6 - SUMIF(H14:H37, "Sick", G14:G37)</f>
         <v>40</v>
       </c>
     </row>
@@ -3931,11 +3946,11 @@
       </c>
       <c r="D8" s="2">
         <f>C8-E8</f>
-        <v>11.999999999999998</v>
+        <v>12.999999999999996</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H36, "Be You", G14:G36)</f>
-        <v>4.0000000000000018</v>
+        <f>C8 - SUMIF(H14:H37, "Be You", G14:G37)</f>
+        <v>3.0000000000000036</v>
       </c>
       <c r="J8" s="51"/>
     </row>
@@ -3949,11 +3964,11 @@
       </c>
       <c r="D9" s="7">
         <f>D8/8</f>
-        <v>1.4999999999999998</v>
+        <v>1.6249999999999996</v>
       </c>
       <c r="E9" s="15">
         <f>E8/8</f>
-        <v>0.50000000000000022</v>
+        <v>0.37500000000000044</v>
       </c>
     </row>
     <row r="10" spans="2:11">
@@ -3968,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H36, "Volunteer", G14:G36)</f>
+        <f>C10 - SUMIF(H14:H37, "Volunteer", G14:G37)</f>
         <v>4</v>
       </c>
       <c r="J10" s="36"/>
@@ -4029,7 +4044,7 @@
         <v>46059</v>
       </c>
       <c r="C14" s="240" t="str">
-        <f t="shared" ref="C14:C19" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
+        <f t="shared" ref="C14:C20" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D14" s="241">
@@ -4043,7 +4058,7 @@
         <v>5</v>
       </c>
       <c r="G14" s="240">
-        <f t="shared" ref="G14:G19" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
+        <f t="shared" ref="G14:G20" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
         <v>4</v>
       </c>
       <c r="H14" s="242" t="s">
@@ -4056,7 +4071,7 @@
         <v>68</v>
       </c>
       <c r="K14" s="42" t="str">
-        <f t="shared" ref="K14:K19" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="K14:K20" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
@@ -4097,71 +4112,71 @@
       </c>
     </row>
     <row r="16" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B16" s="112">
+      <c r="B16" s="291">
+        <v>46093</v>
+      </c>
+      <c r="C16" s="327" t="str">
+        <f t="shared" ref="C16" si="3">IF(ISNUMBER(FIND("?", B16, 1)), "TBD", TEXT(B16, "ddd"))</f>
+        <v>Thu</v>
+      </c>
+      <c r="D16" s="328">
+        <v>0.625</v>
+      </c>
+      <c r="E16" s="328">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F16" s="329">
+        <f>((E16 - D16) * 24)</f>
+        <v>0.99999999999999911</v>
+      </c>
+      <c r="G16" s="327">
+        <f>IF(F16 &gt; 4, (F16 - 1), F16)</f>
+        <v>0.99999999999999911</v>
+      </c>
+      <c r="H16" s="330" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="297" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" s="60" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B17" s="112">
         <v>46164</v>
       </c>
-      <c r="C16" s="271" t="str">
+      <c r="C17" s="271" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D16" s="300">
+      <c r="D17" s="300">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E16" s="300">
+      <c r="E17" s="300">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F16" s="301">
-        <f t="shared" ref="F16:F19" si="3">((E16 - D16) * 24)</f>
+      <c r="F17" s="301">
+        <f t="shared" ref="F17:F20" si="4">((E17 - D17) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G16" s="299">
+      <c r="G17" s="299">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H16" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I16" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="273" t="s">
+      <c r="H17" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="273" t="s">
         <v>42</v>
-      </c>
-      <c r="K16" s="47" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B17" s="286">
-        <v>46213</v>
-      </c>
-      <c r="C17" s="217" t="str">
-        <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="D17" s="287">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E17" s="287">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F17" s="290">
-        <f t="shared" si="3"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G17" s="165">
-        <f t="shared" si="1"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H17" s="288" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="289" t="s">
-        <v>61</v>
       </c>
       <c r="K17" s="47" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4169,120 +4184,120 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B18" s="122">
+      <c r="B18" s="286">
+        <v>46213</v>
+      </c>
+      <c r="C18" s="217" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="D18" s="287">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E18" s="287">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F18" s="290">
+        <f t="shared" si="4"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G18" s="165">
+        <f t="shared" si="1"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H18" s="288" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="196" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="289" t="s">
+        <v>61</v>
+      </c>
+      <c r="K18" s="47" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B19" s="122">
         <v>46237</v>
       </c>
-      <c r="C18" s="240" t="str">
+      <c r="C19" s="240" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="D18" s="241">
+      <c r="D19" s="241">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E18" s="241">
+      <c r="E19" s="241">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F18" s="263">
-        <f t="shared" si="3"/>
+      <c r="F19" s="263">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G18" s="240">
+      <c r="G19" s="240">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H18" s="242" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="243" t="s">
+      <c r="H19" s="242" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="243" t="s">
         <v>59</v>
       </c>
-      <c r="K18" s="258" t="str">
+      <c r="K19" s="258" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B19" s="123">
+    <row r="20" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B20" s="123">
         <v>46238</v>
       </c>
-      <c r="C19" s="250" t="str">
+      <c r="C20" s="250" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="D19" s="251">
+      <c r="D20" s="251">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E19" s="251">
+      <c r="E20" s="251">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F19" s="264">
-        <f t="shared" si="3"/>
+      <c r="F20" s="264">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G19" s="250">
+      <c r="G20" s="250">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H19" s="252" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="253" t="s">
+      <c r="H20" s="252" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="253" t="s">
         <v>59</v>
       </c>
-      <c r="K19" s="59" t="str">
+      <c r="K20" s="59" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B20" s="254">
-        <v>46239</v>
-      </c>
-      <c r="C20" s="250" t="str">
-        <f t="shared" ref="C20:C34" si="4">IF(ISNUMBER(FIND("?", B20, 1)), "TBD", TEXT(B20, "ddd"))</f>
-        <v>Wed</v>
-      </c>
-      <c r="D20" s="251">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E20" s="251">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F20" s="264">
-        <f t="shared" ref="F20:F31" si="5">((E20 - D20) * 24)</f>
-        <v>5</v>
-      </c>
-      <c r="G20" s="250">
-        <f t="shared" ref="G20:G34" si="6">IF(F20 &gt; 4, (F20 - 1), F20)</f>
-        <v>4</v>
-      </c>
-      <c r="H20" s="252" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="253" t="s">
-        <v>59</v>
-      </c>
-      <c r="K20" s="59" t="str">
-        <f t="shared" ref="K20:K34" ca="1" si="7">IF(C20 = "TBD", "TBD", IF(B20 = "", "IDK!!", IF(TODAY() &gt; B20, "Passed", IF(TODAY() = B20, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
-      </c>
-    </row>
     <row r="21" spans="2:11" ht="15.75" thickBot="1">
       <c r="B21" s="254">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="C21" s="250" t="str">
-        <f t="shared" si="4"/>
-        <v>Thu</v>
+        <f t="shared" ref="C21:C35" si="5">IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
+        <v>Wed</v>
       </c>
       <c r="D21" s="251">
         <v>0.45833333333333331</v>
@@ -4291,11 +4306,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F21" s="264">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="F21:F32" si="6">((E21 - D21) * 24)</f>
         <v>5</v>
       </c>
       <c r="G21" s="250">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G21:G35" si="7">IF(F21 &gt; 4, (F21 - 1), F21)</f>
         <v>4</v>
       </c>
       <c r="H21" s="252" t="s">
@@ -4308,17 +4323,17 @@
         <v>59</v>
       </c>
       <c r="K21" s="59" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ref="K21:K35" ca="1" si="8">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="15.75" thickBot="1">
       <c r="B22" s="254">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="C22" s="250" t="str">
-        <f t="shared" si="4"/>
-        <v>Fri</v>
+        <f t="shared" si="5"/>
+        <v>Thu</v>
       </c>
       <c r="D22" s="251">
         <v>0.45833333333333331</v>
@@ -4327,11 +4342,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F22" s="264">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="G22" s="250">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="H22" s="252" t="s">
@@ -4344,17 +4359,17 @@
         <v>59</v>
       </c>
       <c r="K22" s="59" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="15.75" thickBot="1">
       <c r="B23" s="254">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="C23" s="250" t="str">
-        <f t="shared" si="4"/>
-        <v>Mon</v>
+        <f t="shared" si="5"/>
+        <v>Fri</v>
       </c>
       <c r="D23" s="251">
         <v>0.45833333333333331</v>
@@ -4363,11 +4378,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F23" s="264">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="G23" s="250">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="H23" s="252" t="s">
@@ -4377,20 +4392,20 @@
         <v>20</v>
       </c>
       <c r="J23" s="253" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="K23" s="59" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="24" spans="2:11" ht="15.75" thickBot="1">
       <c r="B24" s="254">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="C24" s="250" t="str">
-        <f t="shared" si="4"/>
-        <v>Tue</v>
+        <f t="shared" si="5"/>
+        <v>Mon</v>
       </c>
       <c r="D24" s="251">
         <v>0.45833333333333331</v>
@@ -4399,11 +4414,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F24" s="264">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="G24" s="250">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="H24" s="252" t="s">
@@ -4416,17 +4431,17 @@
         <v>39</v>
       </c>
       <c r="K24" s="59" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="15.75" thickBot="1">
       <c r="B25" s="254">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="C25" s="250" t="str">
-        <f t="shared" si="4"/>
-        <v>Wed</v>
+        <f t="shared" si="5"/>
+        <v>Tue</v>
       </c>
       <c r="D25" s="251">
         <v>0.45833333333333331</v>
@@ -4435,11 +4450,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F25" s="264">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="G25" s="250">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="H25" s="252" t="s">
@@ -4452,17 +4467,17 @@
         <v>39</v>
       </c>
       <c r="K25" s="59" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B26" s="255">
-        <v>46247</v>
+      <c r="B26" s="254">
+        <v>46246</v>
       </c>
       <c r="C26" s="250" t="str">
-        <f t="shared" si="4"/>
-        <v>Thu</v>
+        <f t="shared" si="5"/>
+        <v>Wed</v>
       </c>
       <c r="D26" s="251">
         <v>0.45833333333333331</v>
@@ -4471,11 +4486,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F26" s="264">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="G26" s="250">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="H26" s="252" t="s">
@@ -4488,197 +4503,197 @@
         <v>39</v>
       </c>
       <c r="K26" s="59" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="15.75" thickBot="1">
       <c r="B27" s="255">
+        <v>46247</v>
+      </c>
+      <c r="C27" s="250" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D27" s="251">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E27" s="251">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F27" s="264">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G27" s="250">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H27" s="252" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="253" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" s="59" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B28" s="255">
         <v>46248</v>
       </c>
-      <c r="C27" s="245" t="str">
-        <f t="shared" si="4"/>
+      <c r="C28" s="245" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D27" s="246">
+      <c r="D28" s="246">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E27" s="246">
+      <c r="E28" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F27" s="268">
+      <c r="F28" s="268">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G28" s="245">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H28" s="247" t="s">
+        <v>4</v>
+      </c>
+      <c r="I28" s="248" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="249" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" s="257" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B29" s="310">
+        <v>46269</v>
+      </c>
+      <c r="C29" s="311" t="str">
+        <f t="shared" ref="C29" si="9">IF(ISNUMBER(FIND("?", B29, 1)), "TBD", TEXT(B29, "ddd"))</f>
+        <v>Fri</v>
+      </c>
+      <c r="D29" s="312">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E29" s="312">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F29" s="313">
+        <f t="shared" ref="F29" si="10">((E29 - D29) * 24)</f>
+        <v>5</v>
+      </c>
+      <c r="G29" s="311">
+        <f t="shared" ref="G29" si="11">IF(F29 &gt; 4, (F29 - 1), F29)</f>
+        <v>4</v>
+      </c>
+      <c r="H29" s="314" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="315" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="192" t="str">
+        <f t="shared" ref="K29" ca="1" si="12">IF(C29 = "TBD", "TBD", IF(B29 = "", "IDK!!", IF(TODAY() &gt; B29, "Passed", IF(TODAY() = B29, "Today!!", "Upcoming"))))</f>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B30" s="124">
+        <v>46353</v>
+      </c>
+      <c r="C30" s="173" t="str">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="G27" s="245">
+        <v>Fri</v>
+      </c>
+      <c r="D30" s="155">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E30" s="155">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F30" s="226">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="H27" s="247" t="s">
-        <v>4</v>
-      </c>
-      <c r="I27" s="248" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" s="249" t="s">
-        <v>39</v>
-      </c>
-      <c r="K27" s="257" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G30" s="173">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H30" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="276" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="192" t="str">
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B28" s="310">
-        <v>46269</v>
-      </c>
-      <c r="C28" s="311" t="str">
-        <f t="shared" ref="C28" si="8">IF(ISNUMBER(FIND("?", B28, 1)), "TBD", TEXT(B28, "ddd"))</f>
-        <v>Fri</v>
-      </c>
-      <c r="D28" s="312">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E28" s="312">
+    <row r="31" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B31" s="112">
+        <v>46380</v>
+      </c>
+      <c r="C31" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D31" s="269">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E31" s="269">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F28" s="313">
-        <f t="shared" ref="F28" si="9">((E28 - D28) * 24)</f>
-        <v>5</v>
-      </c>
-      <c r="G28" s="311">
-        <f t="shared" ref="G28" si="10">IF(F28 &gt; 4, (F28 - 1), F28)</f>
-        <v>4</v>
-      </c>
-      <c r="H28" s="314" t="s">
-        <v>4</v>
-      </c>
-      <c r="I28" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="315" t="s">
-        <v>24</v>
-      </c>
-      <c r="K28" s="192" t="str">
-        <f t="shared" ref="K28" ca="1" si="11">IF(C28 = "TBD", "TBD", IF(B28 = "", "IDK!!", IF(TODAY() &gt; B28, "Passed", IF(TODAY() = B28, "Today!!", "Upcoming"))))</f>
+      <c r="F31" s="270">
+        <f t="shared" si="6"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G31" s="271">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H31" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="273" t="s">
+        <v>60</v>
+      </c>
+      <c r="K31" s="42" t="str">
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B29" s="124">
-        <v>46353</v>
-      </c>
-      <c r="C29" s="173" t="str">
-        <f t="shared" si="4"/>
-        <v>Fri</v>
-      </c>
-      <c r="D29" s="155">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E29" s="155">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F29" s="226">
+    <row r="32" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B32" s="120">
+        <v>46384</v>
+      </c>
+      <c r="C32" s="281" t="str">
         <f t="shared" si="5"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G29" s="173">
-        <f t="shared" si="6"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H29" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" s="276" t="s">
-        <v>14</v>
-      </c>
-      <c r="K29" s="192" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B30" s="112">
-        <v>46380</v>
-      </c>
-      <c r="C30" s="271" t="str">
-        <f t="shared" si="4"/>
-        <v>Thu</v>
-      </c>
-      <c r="D30" s="269">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E30" s="269">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F30" s="270">
-        <f t="shared" si="5"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G30" s="271">
-        <f t="shared" si="6"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H30" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I30" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="273" t="s">
-        <v>60</v>
-      </c>
-      <c r="K30" s="42" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B31" s="120">
-        <v>46384</v>
-      </c>
-      <c r="C31" s="281" t="str">
-        <f t="shared" si="4"/>
         <v>Mon</v>
-      </c>
-      <c r="D31" s="282">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E31" s="282">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F31" s="283">
-        <f t="shared" si="5"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G31" s="281">
-        <f t="shared" si="6"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H31" s="284" t="s">
-        <v>4</v>
-      </c>
-      <c r="I31" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="285" t="s">
-        <v>60</v>
-      </c>
-      <c r="K31" s="59" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B32" s="277">
-        <v>46385</v>
-      </c>
-      <c r="C32" s="278" t="str">
-        <f t="shared" si="4"/>
-        <v>Tue</v>
       </c>
       <c r="D32" s="282">
         <v>0.29166666666666669</v>
@@ -4687,34 +4702,34 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F32" s="283">
-        <f t="shared" ref="F32:F34" si="12">((E32 - D32) * 24)</f>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G32" s="281">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H32" s="279" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="280" t="s">
+      <c r="H32" s="284" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="285" t="s">
         <v>60</v>
       </c>
-      <c r="K32" s="193" t="str">
-        <f t="shared" ca="1" si="7"/>
+      <c r="K32" s="59" t="str">
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="33" spans="2:11">
+    <row r="33" spans="2:11" ht="15.75" thickBot="1">
       <c r="B33" s="277">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C33" s="278" t="str">
-        <f t="shared" si="4"/>
-        <v>Wed</v>
+        <f t="shared" si="5"/>
+        <v>Tue</v>
       </c>
       <c r="D33" s="282">
         <v>0.29166666666666669</v>
@@ -4723,11 +4738,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F33" s="283">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="F33:F35" si="13">((E33 - D33) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G33" s="281">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
       <c r="H33" s="279" t="s">
@@ -4740,17 +4755,17 @@
         <v>60</v>
       </c>
       <c r="K33" s="193" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B34" s="113">
-        <v>46387</v>
+    <row r="34" spans="2:11">
+      <c r="B34" s="277">
+        <v>46386</v>
       </c>
       <c r="C34" s="278" t="str">
-        <f t="shared" si="4"/>
-        <v>Thu</v>
+        <f t="shared" si="5"/>
+        <v>Wed</v>
       </c>
       <c r="D34" s="282">
         <v>0.29166666666666669</v>
@@ -4759,107 +4774,143 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F34" s="283">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G34" s="281">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H34" s="274" t="s">
-        <v>4</v>
-      </c>
-      <c r="I34" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="275" t="s">
+      <c r="H34" s="279" t="s">
+        <v>4</v>
+      </c>
+      <c r="I34" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="280" t="s">
         <v>60</v>
       </c>
       <c r="K34" s="193" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="102"/>
-      <c r="C35" s="165" t="str">
-        <f t="shared" ref="C35:C36" si="13">IF(ISNUMBER(FIND("?", B35, 1)), "TBD", TEXT(B35, "ddd"))</f>
+    <row r="35" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B35" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C35" s="278" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D35" s="282">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E35" s="282">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F35" s="283">
+        <f t="shared" si="13"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G35" s="281">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H35" s="274" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="275" t="s">
+        <v>60</v>
+      </c>
+      <c r="K35" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" s="102"/>
+      <c r="C36" s="165" t="str">
+        <f t="shared" ref="C36:C37" si="14">IF(ISNUMBER(FIND("?", B36, 1)), "TBD", TEXT(B36, "ddd"))</f>
         <v>Sat</v>
       </c>
-      <c r="D35" s="157"/>
-      <c r="E35" s="157"/>
-      <c r="F35" s="220">
-        <f t="shared" ref="F35:F36" si="14">((E35 - D35) * 24)</f>
+      <c r="D36" s="157"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="220">
+        <f t="shared" ref="F36:F37" si="15">((E36 - D36) * 24)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="217">
-        <f t="shared" ref="G35:G36" si="15">IF(F35 &gt; 4, (F35 - 1), F35)</f>
+      <c r="G36" s="217">
+        <f t="shared" ref="G36:G37" si="16">IF(F36 &gt; 4, (F36 - 1), F36)</f>
         <v>0</v>
       </c>
-      <c r="H35" s="180"/>
-      <c r="I35" s="197" t="s">
+      <c r="H36" s="180"/>
+      <c r="I36" s="197" t="s">
         <v>67</v>
       </c>
-      <c r="J35" s="205"/>
-      <c r="K35" s="258" t="str">
-        <f t="shared" ref="K35:K36" ca="1" si="16">IF(C35 = "TBD", "TBD", IF(B35 = "", "IDK!!", IF(TODAY() &gt; B35, "Passed", IF(TODAY() = B35, "Today!!", "Upcoming"))))</f>
+      <c r="J36" s="205"/>
+      <c r="K36" s="258" t="str">
+        <f t="shared" ref="K36:K37" ca="1" si="17">IF(C36 = "TBD", "TBD", IF(B36 = "", "IDK!!", IF(TODAY() &gt; B36, "Passed", IF(TODAY() = B36, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="36" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B36" s="265"/>
-      <c r="C36" s="259" t="str">
-        <f t="shared" si="13"/>
+    <row r="37" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B37" s="265"/>
+      <c r="C37" s="259" t="str">
+        <f t="shared" si="14"/>
         <v>Sat</v>
       </c>
-      <c r="D36" s="266"/>
-      <c r="E36" s="266"/>
-      <c r="F36" s="267">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="259">
+      <c r="D37" s="266"/>
+      <c r="E37" s="266"/>
+      <c r="F37" s="267">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H36" s="260"/>
-      <c r="I36" s="202" t="s">
+      <c r="G37" s="259">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="260"/>
+      <c r="I37" s="202" t="s">
         <v>67</v>
       </c>
-      <c r="J36" s="261"/>
-      <c r="K36" s="256" t="str">
-        <f t="shared" ca="1" si="16"/>
+      <c r="J37" s="261"/>
+      <c r="K37" s="256" t="str">
+        <f t="shared" ca="1" si="17"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="37" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B37" s="86" t="s">
+    <row r="38" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B38" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="318"/>
-      <c r="D37" s="319"/>
-      <c r="E37" s="320"/>
-      <c r="F37" s="228">
-        <f>SUM(F14:F36)</f>
-        <v>137</v>
-      </c>
-      <c r="G37" s="262">
-        <f>SUM(G14:G36)</f>
-        <v>116</v>
-      </c>
-      <c r="H37" s="316"/>
-      <c r="I37" s="317"/>
-      <c r="J37" s="317"/>
-      <c r="K37" s="317"/>
+      <c r="C38" s="318"/>
+      <c r="D38" s="319"/>
+      <c r="E38" s="320"/>
+      <c r="F38" s="228">
+        <f>SUM(F14:F37)</f>
+        <v>138</v>
+      </c>
+      <c r="G38" s="262">
+        <f>SUM(G14:G37)</f>
+        <v>117</v>
+      </c>
+      <c r="H38" s="316"/>
+      <c r="I38" s="317"/>
+      <c r="J38" s="317"/>
+      <c r="K38" s="317"/>
     </row>
   </sheetData>
-  <autoFilter ref="B13:J37" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
-  <conditionalFormatting sqref="B14:K36">
+  <autoFilter ref="B13:J38" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <conditionalFormatting sqref="B14:K37">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F36 K14:K36">
+  <conditionalFormatting sqref="C14:F37 K14:K37">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -4874,7 +4925,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I36">
+  <conditionalFormatting sqref="I14:I37">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A317162-5171-47E1-8684-D89FE12257CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AC0164-556E-4506-A254-2CD0946CC10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="4155" yWindow="0" windowWidth="24360" windowHeight="20985" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="73">
   <si>
     <t>Total</t>
   </si>
@@ -294,6 +294,9 @@
   <si>
     <t>Meeting</t>
   </si>
+  <si>
+    <t>Kids' first day of school</t>
+  </si>
 </sst>
 </file>
 
@@ -1404,7 +1407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="331">
+  <cellXfs count="324">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2114,21 +2117,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2150,9 +2138,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2181,9 +2166,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="18" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2607,7 +2589,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>557335</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>92355</xdr:rowOff>
+      <xdr:rowOff>103561</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2695,7 +2677,7 @@
       <xdr:col>25</xdr:col>
       <xdr:colOff>446143</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>28505</xdr:rowOff>
+      <xdr:rowOff>39711</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2732,13 +2714,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>458322</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3826,7 +3808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:K38"/>
+  <dimension ref="B1:K39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -3865,11 +3847,11 @@
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H37, "PTO", G14:G37)</f>
-        <v>24.5</v>
+        <f ca="1">C3 - C6 - SUMIF(H14:H38, "PTO", G14:G38)</f>
+        <v>20.5</v>
       </c>
       <c r="J3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename",A2),LEN(CELL("filename",A2))-SEARCH("]",CELL("filename",A2)))) + 1</f>
@@ -3897,11 +3879,11 @@
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>3.0625</v>
+        <v>2.5625</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -3916,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H37, "Sick", G14:G37)</f>
+        <f>C6 - SUMIF(H14:H38, "Sick", G14:G38)</f>
         <v>40</v>
       </c>
     </row>
@@ -3949,7 +3931,7 @@
         <v>12.999999999999996</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H37, "Be You", G14:G37)</f>
+        <f>C8 - SUMIF(H14:H38, "Be You", G14:G38)</f>
         <v>3.0000000000000036</v>
       </c>
       <c r="J8" s="51"/>
@@ -3983,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H37, "Volunteer", G14:G37)</f>
+        <f>C10 - SUMIF(H14:H38, "Volunteer", G14:G38)</f>
         <v>4</v>
       </c>
       <c r="J10" s="36"/>
@@ -4053,7 +4035,7 @@
       <c r="E14" s="241">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F14" s="263">
+      <c r="F14" s="257">
         <f>((E14 - D14) * 24)</f>
         <v>5</v>
       </c>
@@ -4076,34 +4058,34 @@
       </c>
     </row>
     <row r="15" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B15" s="321">
+      <c r="B15" s="314">
         <v>46080</v>
       </c>
-      <c r="C15" s="322" t="str">
+      <c r="C15" s="315" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D15" s="323">
+      <c r="D15" s="316">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E15" s="323">
+      <c r="E15" s="316">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F15" s="324">
+      <c r="F15" s="317">
         <f>((E15 - D15) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G15" s="322">
+      <c r="G15" s="315">
         <f>IF(F15 &gt; 4, (F15 - 1), F15)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H15" s="325" t="s">
+      <c r="H15" s="318" t="s">
         <v>69</v>
       </c>
       <c r="I15" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="326" t="s">
+      <c r="J15" s="319" t="s">
         <v>70</v>
       </c>
       <c r="K15" s="60" t="str">
@@ -4112,70 +4094,70 @@
       </c>
     </row>
     <row r="16" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B16" s="291">
+      <c r="B16" s="284">
         <v>46093</v>
       </c>
-      <c r="C16" s="327" t="str">
+      <c r="C16" s="320" t="str">
         <f t="shared" ref="C16" si="3">IF(ISNUMBER(FIND("?", B16, 1)), "TBD", TEXT(B16, "ddd"))</f>
         <v>Thu</v>
       </c>
-      <c r="D16" s="328">
+      <c r="D16" s="321">
         <v>0.625</v>
       </c>
-      <c r="E16" s="328">
+      <c r="E16" s="321">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F16" s="329">
+      <c r="F16" s="322">
         <f>((E16 - D16) * 24)</f>
         <v>0.99999999999999911</v>
       </c>
-      <c r="G16" s="327">
+      <c r="G16" s="320">
         <f>IF(F16 &gt; 4, (F16 - 1), F16)</f>
         <v>0.99999999999999911</v>
       </c>
-      <c r="H16" s="330" t="s">
+      <c r="H16" s="323" t="s">
         <v>69</v>
       </c>
       <c r="I16" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="297" t="s">
+      <c r="J16" s="290" t="s">
         <v>71</v>
       </c>
       <c r="K16" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="15.75" thickBot="1">
       <c r="B17" s="112">
         <v>46164</v>
       </c>
-      <c r="C17" s="271" t="str">
+      <c r="C17" s="264" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D17" s="300">
+      <c r="D17" s="293">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E17" s="300">
+      <c r="E17" s="293">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F17" s="301">
+      <c r="F17" s="294">
         <f t="shared" ref="F17:F20" si="4">((E17 - D17) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G17" s="299">
+      <c r="G17" s="292">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H17" s="272" t="s">
+      <c r="H17" s="265" t="s">
         <v>4</v>
       </c>
       <c r="I17" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="273" t="s">
+      <c r="J17" s="266" t="s">
         <v>42</v>
       </c>
       <c r="K17" s="47" t="str">
@@ -4184,20 +4166,20 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B18" s="286">
+      <c r="B18" s="279">
         <v>46213</v>
       </c>
       <c r="C18" s="217" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D18" s="287">
+      <c r="D18" s="280">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E18" s="287">
+      <c r="E18" s="280">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F18" s="290">
+      <c r="F18" s="283">
         <f t="shared" si="4"/>
         <v>8.9999999999999982</v>
       </c>
@@ -4205,13 +4187,13 @@
         <f t="shared" si="1"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H18" s="288" t="s">
+      <c r="H18" s="281" t="s">
         <v>4</v>
       </c>
       <c r="I18" s="196" t="s">
         <v>28</v>
       </c>
-      <c r="J18" s="289" t="s">
+      <c r="J18" s="282" t="s">
         <v>61</v>
       </c>
       <c r="K18" s="47" t="str">
@@ -4233,7 +4215,7 @@
       <c r="E19" s="241">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F19" s="263">
+      <c r="F19" s="257">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
@@ -4250,7 +4232,7 @@
       <c r="J19" s="243" t="s">
         <v>59</v>
       </c>
-      <c r="K19" s="258" t="str">
+      <c r="K19" s="252" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
@@ -4259,31 +4241,31 @@
       <c r="B20" s="123">
         <v>46238</v>
       </c>
-      <c r="C20" s="250" t="str">
+      <c r="C20" s="245" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="D20" s="251">
+      <c r="D20" s="246">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E20" s="251">
+      <c r="E20" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F20" s="264">
+      <c r="F20" s="258">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G20" s="250">
+      <c r="G20" s="245">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H20" s="252" t="s">
+      <c r="H20" s="247" t="s">
         <v>4</v>
       </c>
       <c r="I20" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="253" t="s">
+      <c r="J20" s="248" t="s">
         <v>59</v>
       </c>
       <c r="K20" s="59" t="str">
@@ -4292,70 +4274,70 @@
       </c>
     </row>
     <row r="21" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B21" s="254">
+      <c r="B21" s="249">
         <v>46239</v>
       </c>
-      <c r="C21" s="250" t="str">
-        <f t="shared" ref="C21:C35" si="5">IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
+      <c r="C21" s="245" t="str">
+        <f t="shared" ref="C21:C36" si="5">IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
         <v>Wed</v>
       </c>
-      <c r="D21" s="251">
+      <c r="D21" s="246">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E21" s="251">
+      <c r="E21" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F21" s="264">
-        <f t="shared" ref="F21:F32" si="6">((E21 - D21) * 24)</f>
+      <c r="F21" s="258">
+        <f t="shared" ref="F21:F33" si="6">((E21 - D21) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G21" s="250">
-        <f t="shared" ref="G21:G35" si="7">IF(F21 &gt; 4, (F21 - 1), F21)</f>
-        <v>4</v>
-      </c>
-      <c r="H21" s="252" t="s">
+      <c r="G21" s="245">
+        <f t="shared" ref="G21:G36" si="7">IF(F21 &gt; 4, (F21 - 1), F21)</f>
+        <v>4</v>
+      </c>
+      <c r="H21" s="247" t="s">
         <v>4</v>
       </c>
       <c r="I21" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J21" s="253" t="s">
+      <c r="J21" s="248" t="s">
         <v>59</v>
       </c>
       <c r="K21" s="59" t="str">
-        <f t="shared" ref="K21:K35" ca="1" si="8">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="K21:K36" ca="1" si="8">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B22" s="254">
+      <c r="B22" s="249">
         <v>46240</v>
       </c>
-      <c r="C22" s="250" t="str">
+      <c r="C22" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D22" s="251">
+      <c r="D22" s="246">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E22" s="251">
+      <c r="E22" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F22" s="264">
+      <c r="F22" s="258">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="G22" s="250">
+      <c r="G22" s="245">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="H22" s="252" t="s">
+      <c r="H22" s="247" t="s">
         <v>4</v>
       </c>
       <c r="I22" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J22" s="253" t="s">
+      <c r="J22" s="248" t="s">
         <v>59</v>
       </c>
       <c r="K22" s="59" t="str">
@@ -4364,34 +4346,34 @@
       </c>
     </row>
     <row r="23" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B23" s="254">
+      <c r="B23" s="249">
         <v>46241</v>
       </c>
-      <c r="C23" s="250" t="str">
+      <c r="C23" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D23" s="251">
+      <c r="D23" s="246">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E23" s="251">
+      <c r="E23" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F23" s="264">
+      <c r="F23" s="258">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="G23" s="250">
+      <c r="G23" s="245">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="H23" s="252" t="s">
+      <c r="H23" s="247" t="s">
         <v>4</v>
       </c>
       <c r="I23" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="253" t="s">
+      <c r="J23" s="248" t="s">
         <v>59</v>
       </c>
       <c r="K23" s="59" t="str">
@@ -4400,34 +4382,34 @@
       </c>
     </row>
     <row r="24" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B24" s="254">
+      <c r="B24" s="249">
         <v>46244</v>
       </c>
-      <c r="C24" s="250" t="str">
+      <c r="C24" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D24" s="251">
+      <c r="D24" s="246">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E24" s="251">
+      <c r="E24" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F24" s="264">
+      <c r="F24" s="258">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="G24" s="250">
+      <c r="G24" s="245">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="H24" s="252" t="s">
+      <c r="H24" s="247" t="s">
         <v>4</v>
       </c>
       <c r="I24" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J24" s="253" t="s">
+      <c r="J24" s="248" t="s">
         <v>39</v>
       </c>
       <c r="K24" s="59" t="str">
@@ -4436,34 +4418,34 @@
       </c>
     </row>
     <row r="25" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B25" s="254">
+      <c r="B25" s="249">
         <v>46245</v>
       </c>
-      <c r="C25" s="250" t="str">
+      <c r="C25" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="D25" s="251">
+      <c r="D25" s="246">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E25" s="251">
+      <c r="E25" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F25" s="264">
+      <c r="F25" s="258">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="G25" s="250">
+      <c r="G25" s="245">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="H25" s="252" t="s">
+      <c r="H25" s="247" t="s">
         <v>4</v>
       </c>
       <c r="I25" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J25" s="253" t="s">
+      <c r="J25" s="248" t="s">
         <v>39</v>
       </c>
       <c r="K25" s="59" t="str">
@@ -4472,34 +4454,34 @@
       </c>
     </row>
     <row r="26" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B26" s="254">
+      <c r="B26" s="249">
         <v>46246</v>
       </c>
-      <c r="C26" s="250" t="str">
+      <c r="C26" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="D26" s="251">
+      <c r="D26" s="246">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E26" s="251">
+      <c r="E26" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F26" s="264">
+      <c r="F26" s="258">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="G26" s="250">
+      <c r="G26" s="245">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="H26" s="252" t="s">
+      <c r="H26" s="247" t="s">
         <v>4</v>
       </c>
       <c r="I26" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="253" t="s">
+      <c r="J26" s="248" t="s">
         <v>39</v>
       </c>
       <c r="K26" s="59" t="str">
@@ -4508,34 +4490,34 @@
       </c>
     </row>
     <row r="27" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B27" s="255">
+      <c r="B27" s="250">
         <v>46247</v>
       </c>
-      <c r="C27" s="250" t="str">
+      <c r="C27" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D27" s="251">
+      <c r="D27" s="246">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E27" s="251">
+      <c r="E27" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F27" s="264">
+      <c r="F27" s="258">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="G27" s="250">
+      <c r="G27" s="245">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="H27" s="252" t="s">
+      <c r="H27" s="247" t="s">
         <v>4</v>
       </c>
       <c r="I27" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J27" s="253" t="s">
+      <c r="J27" s="248" t="s">
         <v>39</v>
       </c>
       <c r="K27" s="59" t="str">
@@ -4543,8 +4525,8 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B28" s="255">
+    <row r="28" spans="2:11">
+      <c r="B28" s="250">
         <v>46248</v>
       </c>
       <c r="C28" s="245" t="str">
@@ -4557,7 +4539,7 @@
       <c r="E28" s="246">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F28" s="268">
+      <c r="F28" s="258">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
@@ -4568,226 +4550,226 @@
       <c r="H28" s="247" t="s">
         <v>4</v>
       </c>
-      <c r="I28" s="248" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="249" t="s">
+      <c r="I28" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="K28" s="257" t="str">
+      <c r="K28" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="29" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B29" s="310">
+      <c r="B29" s="250">
+        <v>46253</v>
+      </c>
+      <c r="C29" s="245" t="str">
+        <f t="shared" si="5"/>
+        <v>Wed</v>
+      </c>
+      <c r="D29" s="246">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E29" s="246">
+        <v>0.5</v>
+      </c>
+      <c r="F29" s="258">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G29" s="245">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H29" s="247" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="248" t="s">
+        <v>72</v>
+      </c>
+      <c r="K29" s="59" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B30" s="303">
         <v>46269</v>
       </c>
-      <c r="C29" s="311" t="str">
-        <f t="shared" ref="C29" si="9">IF(ISNUMBER(FIND("?", B29, 1)), "TBD", TEXT(B29, "ddd"))</f>
+      <c r="C30" s="304" t="str">
+        <f t="shared" ref="C30" si="9">IF(ISNUMBER(FIND("?", B30, 1)), "TBD", TEXT(B30, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D29" s="312">
+      <c r="D30" s="305">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E29" s="312">
+      <c r="E30" s="305">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F29" s="313">
-        <f t="shared" ref="F29" si="10">((E29 - D29) * 24)</f>
+      <c r="F30" s="306">
+        <f t="shared" ref="F30" si="10">((E30 - D30) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G29" s="311">
-        <f t="shared" ref="G29" si="11">IF(F29 &gt; 4, (F29 - 1), F29)</f>
-        <v>4</v>
-      </c>
-      <c r="H29" s="314" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" s="315" t="s">
+      <c r="G30" s="304">
+        <f t="shared" ref="G30" si="11">IF(F30 &gt; 4, (F30 - 1), F30)</f>
+        <v>4</v>
+      </c>
+      <c r="H30" s="307" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="308" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="192" t="str">
-        <f t="shared" ref="K29" ca="1" si="12">IF(C29 = "TBD", "TBD", IF(B29 = "", "IDK!!", IF(TODAY() &gt; B29, "Passed", IF(TODAY() = B29, "Today!!", "Upcoming"))))</f>
+      <c r="K30" s="192" t="str">
+        <f t="shared" ref="K30" ca="1" si="12">IF(C30 = "TBD", "TBD", IF(B30 = "", "IDK!!", IF(TODAY() &gt; B30, "Passed", IF(TODAY() = B30, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B30" s="124">
+    <row r="31" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B31" s="124">
         <v>46353</v>
       </c>
-      <c r="C30" s="173" t="str">
+      <c r="C31" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D30" s="155">
+      <c r="D31" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E30" s="155">
+      <c r="E31" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F30" s="226">
+      <c r="F31" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G30" s="173">
+      <c r="G31" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H30" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I30" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="276" t="s">
+      <c r="H31" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="K30" s="192" t="str">
+      <c r="K31" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B31" s="112">
+    <row r="32" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B32" s="112">
         <v>46380</v>
       </c>
-      <c r="C31" s="271" t="str">
+      <c r="C32" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D31" s="269">
+      <c r="D32" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E31" s="269">
+      <c r="E32" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F31" s="270">
+      <c r="F32" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G31" s="271">
+      <c r="G32" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H31" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I31" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="273" t="s">
+      <c r="H32" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="K31" s="42" t="str">
+      <c r="K32" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B32" s="120">
+    <row r="33" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B33" s="120">
         <v>46384</v>
       </c>
-      <c r="C32" s="281" t="str">
+      <c r="C33" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D32" s="282">
+      <c r="D33" s="275">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E32" s="282">
+      <c r="E33" s="275">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F32" s="283">
+      <c r="F33" s="276">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G32" s="281">
+      <c r="G33" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H32" s="284" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="285" t="s">
+      <c r="H33" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="K32" s="59" t="str">
+      <c r="K33" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B33" s="277">
+    <row r="34" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B34" s="270">
         <v>46385</v>
       </c>
-      <c r="C33" s="278" t="str">
+      <c r="C34" s="271" t="str">
         <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="D33" s="282">
+      <c r="D34" s="275">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E33" s="282">
+      <c r="E34" s="275">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F33" s="283">
-        <f t="shared" ref="F33:F35" si="13">((E33 - D33) * 24)</f>
+      <c r="F34" s="276">
+        <f t="shared" ref="F34:F36" si="13">((E34 - D34) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G33" s="281">
+      <c r="G34" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H33" s="279" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="280" t="s">
-        <v>60</v>
-      </c>
-      <c r="K33" s="193" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="277">
-        <v>46386</v>
-      </c>
-      <c r="C34" s="278" t="str">
-        <f t="shared" si="5"/>
-        <v>Wed</v>
-      </c>
-      <c r="D34" s="282">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E34" s="282">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F34" s="283">
-        <f t="shared" si="13"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G34" s="281">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H34" s="279" t="s">
+      <c r="H34" s="272" t="s">
         <v>4</v>
       </c>
       <c r="I34" s="198" t="s">
         <v>20</v>
       </c>
-      <c r="J34" s="280" t="s">
+      <c r="J34" s="273" t="s">
         <v>60</v>
       </c>
       <c r="K34" s="193" t="str">
@@ -4795,35 +4777,35 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B35" s="113">
-        <v>46387</v>
-      </c>
-      <c r="C35" s="278" t="str">
+    <row r="35" spans="2:11">
+      <c r="B35" s="270">
+        <v>46386</v>
+      </c>
+      <c r="C35" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
-      </c>
-      <c r="D35" s="282">
+        <v>Wed</v>
+      </c>
+      <c r="D35" s="275">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E35" s="282">
+      <c r="E35" s="275">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F35" s="283">
+      <c r="F35" s="276">
         <f t="shared" si="13"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G35" s="281">
+      <c r="G35" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H35" s="274" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="275" t="s">
+      <c r="H35" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="273" t="s">
         <v>60</v>
       </c>
       <c r="K35" s="193" t="str">
@@ -4831,86 +4813,122 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="102"/>
-      <c r="C36" s="165" t="str">
-        <f t="shared" ref="C36:C37" si="14">IF(ISNUMBER(FIND("?", B36, 1)), "TBD", TEXT(B36, "ddd"))</f>
+    <row r="36" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B36" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C36" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D36" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E36" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F36" s="276">
+        <f t="shared" si="13"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G36" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H36" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37" s="102"/>
+      <c r="C37" s="165" t="str">
+        <f t="shared" ref="C37:C38" si="14">IF(ISNUMBER(FIND("?", B37, 1)), "TBD", TEXT(B37, "ddd"))</f>
         <v>Sat</v>
       </c>
-      <c r="D36" s="157"/>
-      <c r="E36" s="157"/>
-      <c r="F36" s="220">
-        <f t="shared" ref="F36:F37" si="15">((E36 - D36) * 24)</f>
+      <c r="D37" s="157"/>
+      <c r="E37" s="157"/>
+      <c r="F37" s="220">
+        <f t="shared" ref="F37:F38" si="15">((E37 - D37) * 24)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="217">
-        <f t="shared" ref="G36:G37" si="16">IF(F36 &gt; 4, (F36 - 1), F36)</f>
+      <c r="G37" s="217">
+        <f t="shared" ref="G37:G38" si="16">IF(F37 &gt; 4, (F37 - 1), F37)</f>
         <v>0</v>
       </c>
-      <c r="H36" s="180"/>
-      <c r="I36" s="197" t="s">
+      <c r="H37" s="180"/>
+      <c r="I37" s="197" t="s">
         <v>67</v>
       </c>
-      <c r="J36" s="205"/>
-      <c r="K36" s="258" t="str">
-        <f t="shared" ref="K36:K37" ca="1" si="17">IF(C36 = "TBD", "TBD", IF(B36 = "", "IDK!!", IF(TODAY() &gt; B36, "Passed", IF(TODAY() = B36, "Today!!", "Upcoming"))))</f>
+      <c r="J37" s="205"/>
+      <c r="K37" s="252" t="str">
+        <f t="shared" ref="K37:K38" ca="1" si="17">IF(C37 = "TBD", "TBD", IF(B37 = "", "IDK!!", IF(TODAY() &gt; B37, "Passed", IF(TODAY() = B37, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="37" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B37" s="265"/>
-      <c r="C37" s="259" t="str">
+    <row r="38" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B38" s="259"/>
+      <c r="C38" s="253" t="str">
         <f t="shared" si="14"/>
         <v>Sat</v>
       </c>
-      <c r="D37" s="266"/>
-      <c r="E37" s="266"/>
-      <c r="F37" s="267">
+      <c r="D38" s="260"/>
+      <c r="E38" s="260"/>
+      <c r="F38" s="261">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G37" s="259">
+      <c r="G38" s="253">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H37" s="260"/>
-      <c r="I37" s="202" t="s">
+      <c r="H38" s="254"/>
+      <c r="I38" s="202" t="s">
         <v>67</v>
       </c>
-      <c r="J37" s="261"/>
-      <c r="K37" s="256" t="str">
+      <c r="J38" s="255"/>
+      <c r="K38" s="251" t="str">
         <f t="shared" ca="1" si="17"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B38" s="86" t="s">
+    <row r="39" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B39" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="318"/>
-      <c r="D38" s="319"/>
-      <c r="E38" s="320"/>
-      <c r="F38" s="228">
-        <f>SUM(F14:F37)</f>
-        <v>138</v>
-      </c>
-      <c r="G38" s="262">
-        <f>SUM(G14:G37)</f>
-        <v>117</v>
-      </c>
-      <c r="H38" s="316"/>
-      <c r="I38" s="317"/>
-      <c r="J38" s="317"/>
-      <c r="K38" s="317"/>
+      <c r="C39" s="311"/>
+      <c r="D39" s="312"/>
+      <c r="E39" s="313"/>
+      <c r="F39" s="228">
+        <f>SUM(F14:F38)</f>
+        <v>143</v>
+      </c>
+      <c r="G39" s="256">
+        <f>SUM(G14:G38)</f>
+        <v>121</v>
+      </c>
+      <c r="H39" s="309"/>
+      <c r="I39" s="310"/>
+      <c r="J39" s="310"/>
+      <c r="K39" s="310"/>
     </row>
   </sheetData>
-  <autoFilter ref="B13:J38" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
-  <conditionalFormatting sqref="B14:K37">
+  <autoFilter ref="B13:J39" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <conditionalFormatting sqref="B14:K38">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F37 K14:K37">
+  <conditionalFormatting sqref="C14:F38 K14:K38">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -4925,7 +4943,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I37">
+  <conditionalFormatting sqref="I14:I38">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
@@ -6966,7 +6984,7 @@
       <c r="H36" s="233" t="s">
         <v>4</v>
       </c>
-      <c r="I36" s="272" t="s">
+      <c r="I36" s="265" t="s">
         <v>20</v>
       </c>
       <c r="J36" s="209" t="s">
@@ -6978,34 +6996,34 @@
       </c>
     </row>
     <row r="37" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B37" s="291">
+      <c r="B37" s="284">
         <v>45936</v>
       </c>
-      <c r="C37" s="292" t="str">
+      <c r="C37" s="285" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="D37" s="293">
+      <c r="D37" s="286">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E37" s="293">
+      <c r="E37" s="286">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F37" s="294">
+      <c r="F37" s="287">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G37" s="292">
+      <c r="G37" s="285">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H37" s="295" t="s">
+      <c r="H37" s="288" t="s">
         <v>32</v>
       </c>
-      <c r="I37" s="296" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="297" t="s">
+      <c r="I37" s="289" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="290" t="s">
         <v>64</v>
       </c>
       <c r="K37" s="67" t="str">
@@ -7014,34 +7032,34 @@
       </c>
     </row>
     <row r="38" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B38" s="298">
+      <c r="B38" s="291">
         <v>45989</v>
       </c>
-      <c r="C38" s="299" t="str">
+      <c r="C38" s="292" t="str">
         <f t="shared" ref="C38" si="8">IF(ISNUMBER(FIND("?", B38, 1)), "TBD", TEXT(B38, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D38" s="300">
+      <c r="D38" s="293">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E38" s="300">
+      <c r="E38" s="293">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F38" s="301">
+      <c r="F38" s="294">
         <f>((E38 - D38) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G38" s="299">
+      <c r="G38" s="292">
         <f>IF(F38 &gt; 4, (F38 - 1), F38)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H38" s="302" t="s">
+      <c r="H38" s="295" t="s">
         <v>4</v>
       </c>
       <c r="I38" s="197" t="s">
         <v>20</v>
       </c>
-      <c r="J38" s="303" t="s">
+      <c r="J38" s="296" t="s">
         <v>14</v>
       </c>
       <c r="K38" s="47" t="str">
@@ -7050,34 +7068,34 @@
       </c>
     </row>
     <row r="39" spans="2:11">
-      <c r="B39" s="304">
+      <c r="B39" s="297">
         <v>45999</v>
       </c>
-      <c r="C39" s="305" t="str">
+      <c r="C39" s="298" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="D39" s="306">
+      <c r="D39" s="299">
         <v>0.60416666666666663</v>
       </c>
-      <c r="E39" s="306">
+      <c r="E39" s="299">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F39" s="307">
+      <c r="F39" s="300">
         <f>((E39 - D39) * 24)</f>
         <v>1.5</v>
       </c>
-      <c r="G39" s="305">
+      <c r="G39" s="298">
         <f>IF(F39 &gt; 4, (F39 - 1), F39)</f>
         <v>1.5</v>
       </c>
-      <c r="H39" s="308" t="s">
+      <c r="H39" s="301" t="s">
         <v>32</v>
       </c>
       <c r="I39" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="J39" s="309" t="s">
+      <c r="J39" s="302" t="s">
         <v>62</v>
       </c>
       <c r="K39" s="42" t="str">

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AC0164-556E-4506-A254-2CD0946CC10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EB71FA-E5F8-4716-839A-4CB1EFB46EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="0" windowWidth="24360" windowHeight="20985" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="1920" yWindow="435" windowWidth="34875" windowHeight="19860" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="74">
   <si>
     <t>Total</t>
   </si>
@@ -297,6 +297,9 @@
   <si>
     <t>Kids' first day of school</t>
   </si>
+  <si>
+    <t>Doctor (split across PTO &amp; Be You)</t>
+  </si>
 </sst>
 </file>
 
@@ -1407,7 +1410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="324">
+  <cellXfs count="331">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2290,24 +2293,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="73" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2343,6 +2328,45 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2589,7 +2613,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>557335</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>103561</xdr:rowOff>
+      <xdr:rowOff>114767</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2714,13 +2738,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>458322</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3808,7 +3832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:K39"/>
+  <dimension ref="B1:K41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -3847,11 +3871,11 @@
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H38, "PTO", G14:G38)</f>
-        <v>20.5</v>
+        <f ca="1">C3 - C6 - SUMIF(H14:H40, "PTO", G14:G40)</f>
+        <v>19.5</v>
       </c>
       <c r="J3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename",A2),LEN(CELL("filename",A2))-SEARCH("]",CELL("filename",A2)))) + 1</f>
@@ -3879,11 +3903,11 @@
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
-        <v>18.5</v>
+        <v>18.625</v>
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>2.5625</v>
+        <v>2.4375</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -3898,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H38, "Sick", G14:G38)</f>
+        <f>C6 - SUMIF(H14:H40, "Sick", G14:G40)</f>
         <v>40</v>
       </c>
     </row>
@@ -3928,11 +3952,11 @@
       </c>
       <c r="D8" s="2">
         <f>C8-E8</f>
-        <v>12.999999999999996</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H38, "Be You", G14:G38)</f>
-        <v>3.0000000000000036</v>
+        <f>C8 - SUMIF(H14:H40, "Be You", G14:G40)</f>
+        <v>0</v>
       </c>
       <c r="J8" s="51"/>
     </row>
@@ -3946,11 +3970,11 @@
       </c>
       <c r="D9" s="7">
         <f>D8/8</f>
-        <v>1.6249999999999996</v>
+        <v>2</v>
       </c>
       <c r="E9" s="15">
         <f>E8/8</f>
-        <v>0.37500000000000044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:11">
@@ -3965,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H38, "Volunteer", G14:G38)</f>
+        <f>C10 - SUMIF(H14:H40, "Volunteer", G14:G40)</f>
         <v>4</v>
       </c>
       <c r="J10" s="36"/>
@@ -4058,34 +4082,34 @@
       </c>
     </row>
     <row r="15" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B15" s="314">
+      <c r="B15" s="308">
         <v>46080</v>
       </c>
-      <c r="C15" s="315" t="str">
+      <c r="C15" s="309" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D15" s="316">
+      <c r="D15" s="310">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E15" s="316">
+      <c r="E15" s="310">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F15" s="317">
+      <c r="F15" s="311">
         <f>((E15 - D15) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G15" s="315">
+      <c r="G15" s="309">
         <f>IF(F15 &gt; 4, (F15 - 1), F15)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H15" s="318" t="s">
+      <c r="H15" s="312" t="s">
         <v>69</v>
       </c>
       <c r="I15" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="319" t="s">
+      <c r="J15" s="313" t="s">
         <v>70</v>
       </c>
       <c r="K15" s="60" t="str">
@@ -4097,25 +4121,25 @@
       <c r="B16" s="284">
         <v>46093</v>
       </c>
-      <c r="C16" s="320" t="str">
+      <c r="C16" s="314" t="str">
         <f t="shared" ref="C16" si="3">IF(ISNUMBER(FIND("?", B16, 1)), "TBD", TEXT(B16, "ddd"))</f>
         <v>Thu</v>
       </c>
-      <c r="D16" s="321">
+      <c r="D16" s="315">
         <v>0.625</v>
       </c>
-      <c r="E16" s="321">
+      <c r="E16" s="315">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F16" s="322">
+      <c r="F16" s="316">
         <f>((E16 - D16) * 24)</f>
         <v>0.99999999999999911</v>
       </c>
-      <c r="G16" s="320">
+      <c r="G16" s="314">
         <f>IF(F16 &gt; 4, (F16 - 1), F16)</f>
         <v>0.99999999999999911</v>
       </c>
-      <c r="H16" s="323" t="s">
+      <c r="H16" s="317" t="s">
         <v>69</v>
       </c>
       <c r="I16" s="244" t="s">
@@ -4278,7 +4302,7 @@
         <v>46239</v>
       </c>
       <c r="C21" s="245" t="str">
-        <f t="shared" ref="C21:C36" si="5">IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
+        <f t="shared" ref="C21:C38" si="5">IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
         <v>Wed</v>
       </c>
       <c r="D21" s="246">
@@ -4288,11 +4312,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F21" s="258">
-        <f t="shared" ref="F21:F33" si="6">((E21 - D21) * 24)</f>
+        <f t="shared" ref="F21:F35" si="6">((E21 - D21) * 24)</f>
         <v>5</v>
       </c>
       <c r="G21" s="245">
-        <f t="shared" ref="G21:G36" si="7">IF(F21 &gt; 4, (F21 - 1), F21)</f>
+        <f t="shared" ref="G21:G38" si="7">IF(F21 &gt; 4, (F21 - 1), F21)</f>
         <v>4</v>
       </c>
       <c r="H21" s="247" t="s">
@@ -4305,7 +4329,7 @@
         <v>59</v>
       </c>
       <c r="K21" s="59" t="str">
-        <f t="shared" ref="K21:K36" ca="1" si="8">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="K21:K38" ca="1" si="8">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4597,194 +4621,194 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B30" s="303">
+    <row r="30" spans="2:11">
+      <c r="B30" s="105">
         <v>46269</v>
       </c>
-      <c r="C30" s="304" t="str">
-        <f t="shared" ref="C30" si="9">IF(ISNUMBER(FIND("?", B30, 1)), "TBD", TEXT(B30, "ddd"))</f>
+      <c r="C30" s="170" t="str">
+        <f t="shared" ref="C30:C32" si="9">IF(ISNUMBER(FIND("?", B30, 1)), "TBD", TEXT(B30, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D30" s="305">
+      <c r="D30" s="160">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E30" s="305">
+      <c r="E30" s="160">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F30" s="306">
-        <f t="shared" ref="F30" si="10">((E30 - D30) * 24)</f>
+      <c r="F30" s="224">
+        <f t="shared" ref="F30:F32" si="10">((E30 - D30) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G30" s="304">
-        <f t="shared" ref="G30" si="11">IF(F30 &gt; 4, (F30 - 1), F30)</f>
-        <v>4</v>
-      </c>
-      <c r="H30" s="307" t="s">
-        <v>4</v>
-      </c>
-      <c r="I30" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="308" t="s">
+      <c r="G30" s="170">
+        <f t="shared" ref="G30:G32" si="11">IF(F30 &gt; 4, (F30 - 1), F30)</f>
+        <v>4</v>
+      </c>
+      <c r="H30" s="185" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="192" t="str">
-        <f t="shared" ref="K30" ca="1" si="12">IF(C30 = "TBD", "TBD", IF(B30 = "", "IDK!!", IF(TODAY() &gt; B30, "Passed", IF(TODAY() = B30, "Today!!", "Upcoming"))))</f>
+      <c r="K30" s="42" t="str">
+        <f t="shared" ref="K30:K32" ca="1" si="12">IF(C30 = "TBD", "TBD", IF(B30 = "", "IDK!!", IF(TODAY() &gt; B30, "Passed", IF(TODAY() = B30, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B31" s="124">
+    <row r="31" spans="2:11">
+      <c r="B31" s="324">
+        <v>46275</v>
+      </c>
+      <c r="C31" s="325" t="str">
+        <f t="shared" si="9"/>
+        <v>Thu</v>
+      </c>
+      <c r="D31" s="326">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E31" s="326">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F31" s="327">
+        <f t="shared" si="10"/>
+        <v>0.99999999999999911</v>
+      </c>
+      <c r="G31" s="325">
+        <f t="shared" si="11"/>
+        <v>0.99999999999999911</v>
+      </c>
+      <c r="H31" s="328" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="329" t="s">
+        <v>28</v>
+      </c>
+      <c r="J31" s="330" t="s">
+        <v>73</v>
+      </c>
+      <c r="K31" s="67" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B32" s="318">
+        <v>46275</v>
+      </c>
+      <c r="C32" s="319" t="str">
+        <f t="shared" si="9"/>
+        <v>Thu</v>
+      </c>
+      <c r="D32" s="320">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E32" s="320">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F32" s="321">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="G32" s="319">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="H32" s="322" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="J32" s="323" t="s">
+        <v>73</v>
+      </c>
+      <c r="K32" s="60" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B33" s="124">
         <v>46353</v>
       </c>
-      <c r="C31" s="173" t="str">
+      <c r="C33" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D31" s="155">
+      <c r="D33" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E31" s="155">
+      <c r="E33" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F31" s="226">
+      <c r="F33" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G31" s="173">
+      <c r="G33" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H31" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I31" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="269" t="s">
+      <c r="H33" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="K31" s="192" t="str">
+      <c r="K33" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B32" s="112">
+    <row r="34" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B34" s="112">
         <v>46380</v>
       </c>
-      <c r="C32" s="264" t="str">
+      <c r="C34" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D32" s="262">
+      <c r="D34" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E32" s="262">
+      <c r="E34" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F32" s="263">
+      <c r="F34" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G32" s="264">
+      <c r="G34" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H32" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="266" t="s">
+      <c r="H34" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I34" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="K32" s="42" t="str">
+      <c r="K34" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B33" s="120">
+    <row r="35" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B35" s="120">
         <v>46384</v>
       </c>
-      <c r="C33" s="274" t="str">
+      <c r="C35" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D33" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E33" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F33" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G33" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H33" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="K33" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B34" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C34" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
-      <c r="D34" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E34" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F34" s="276">
-        <f t="shared" ref="F34:F36" si="13">((E34 - D34) * 24)</f>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G34" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H34" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I34" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="273" t="s">
-        <v>60</v>
-      </c>
-      <c r="K34" s="193" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="270">
-        <v>46386</v>
-      </c>
-      <c r="C35" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Wed</v>
-      </c>
       <c r="D35" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -4792,34 +4816,34 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F35" s="276">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G35" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H35" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="273" t="s">
+      <c r="H35" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="K35" s="193" t="str">
+      <c r="K35" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="36" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B36" s="113">
-        <v>46387</v>
+      <c r="B36" s="270">
+        <v>46385</v>
       </c>
       <c r="C36" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Tue</v>
       </c>
       <c r="D36" s="275">
         <v>0.29166666666666669</v>
@@ -4828,20 +4852,20 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F36" s="276">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="F36:F38" si="13">((E36 - D36) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G36" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H36" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I36" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="268" t="s">
+      <c r="H36" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="273" t="s">
         <v>60</v>
       </c>
       <c r="K36" s="193" t="str">
@@ -4850,85 +4874,157 @@
       </c>
     </row>
     <row r="37" spans="2:11">
-      <c r="B37" s="102"/>
-      <c r="C37" s="165" t="str">
-        <f t="shared" ref="C37:C38" si="14">IF(ISNUMBER(FIND("?", B37, 1)), "TBD", TEXT(B37, "ddd"))</f>
+      <c r="B37" s="270">
+        <v>46386</v>
+      </c>
+      <c r="C37" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Wed</v>
+      </c>
+      <c r="D37" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E37" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F37" s="276">
+        <f t="shared" si="13"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G37" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H37" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I37" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="273" t="s">
+        <v>60</v>
+      </c>
+      <c r="K37" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B38" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C38" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D38" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E38" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F38" s="276">
+        <f t="shared" si="13"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G38" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H38" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="K38" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39" s="102"/>
+      <c r="C39" s="165" t="str">
+        <f t="shared" ref="C39:C40" si="14">IF(ISNUMBER(FIND("?", B39, 1)), "TBD", TEXT(B39, "ddd"))</f>
         <v>Sat</v>
       </c>
-      <c r="D37" s="157"/>
-      <c r="E37" s="157"/>
-      <c r="F37" s="220">
-        <f t="shared" ref="F37:F38" si="15">((E37 - D37) * 24)</f>
+      <c r="D39" s="157"/>
+      <c r="E39" s="157"/>
+      <c r="F39" s="220">
+        <f t="shared" ref="F39:F40" si="15">((E39 - D39) * 24)</f>
         <v>0</v>
       </c>
-      <c r="G37" s="217">
-        <f t="shared" ref="G37:G38" si="16">IF(F37 &gt; 4, (F37 - 1), F37)</f>
+      <c r="G39" s="217">
+        <f t="shared" ref="G39:G40" si="16">IF(F39 &gt; 4, (F39 - 1), F39)</f>
         <v>0</v>
       </c>
-      <c r="H37" s="180"/>
-      <c r="I37" s="197" t="s">
+      <c r="H39" s="180"/>
+      <c r="I39" s="197" t="s">
         <v>67</v>
       </c>
-      <c r="J37" s="205"/>
-      <c r="K37" s="252" t="str">
-        <f t="shared" ref="K37:K38" ca="1" si="17">IF(C37 = "TBD", "TBD", IF(B37 = "", "IDK!!", IF(TODAY() &gt; B37, "Passed", IF(TODAY() = B37, "Today!!", "Upcoming"))))</f>
+      <c r="J39" s="205"/>
+      <c r="K39" s="252" t="str">
+        <f t="shared" ref="K39:K40" ca="1" si="17">IF(C39 = "TBD", "TBD", IF(B39 = "", "IDK!!", IF(TODAY() &gt; B39, "Passed", IF(TODAY() = B39, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B38" s="259"/>
-      <c r="C38" s="253" t="str">
+    <row r="40" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B40" s="259"/>
+      <c r="C40" s="253" t="str">
         <f t="shared" si="14"/>
         <v>Sat</v>
       </c>
-      <c r="D38" s="260"/>
-      <c r="E38" s="260"/>
-      <c r="F38" s="261">
+      <c r="D40" s="260"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="261">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G38" s="253">
+      <c r="G40" s="253">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H38" s="254"/>
-      <c r="I38" s="202" t="s">
+      <c r="H40" s="254"/>
+      <c r="I40" s="202" t="s">
         <v>67</v>
       </c>
-      <c r="J38" s="255"/>
-      <c r="K38" s="251" t="str">
+      <c r="J40" s="255"/>
+      <c r="K40" s="251" t="str">
         <f t="shared" ca="1" si="17"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="39" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B39" s="86" t="s">
+    <row r="41" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B41" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="311"/>
-      <c r="D39" s="312"/>
-      <c r="E39" s="313"/>
-      <c r="F39" s="228">
-        <f>SUM(F14:F38)</f>
-        <v>143</v>
-      </c>
-      <c r="G39" s="256">
-        <f>SUM(G14:G38)</f>
-        <v>121</v>
-      </c>
-      <c r="H39" s="309"/>
-      <c r="I39" s="310"/>
-      <c r="J39" s="310"/>
-      <c r="K39" s="310"/>
+      <c r="C41" s="305"/>
+      <c r="D41" s="306"/>
+      <c r="E41" s="307"/>
+      <c r="F41" s="228">
+        <f>SUM(F14:F40)</f>
+        <v>147</v>
+      </c>
+      <c r="G41" s="256">
+        <f>SUM(G14:G40)</f>
+        <v>125</v>
+      </c>
+      <c r="H41" s="303"/>
+      <c r="I41" s="304"/>
+      <c r="J41" s="304"/>
+      <c r="K41" s="304"/>
     </row>
   </sheetData>
-  <autoFilter ref="B13:J39" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
-  <conditionalFormatting sqref="B14:K38">
+  <autoFilter ref="B13:J41" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <conditionalFormatting sqref="B14:K40">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F38 K14:K38">
+  <conditionalFormatting sqref="C14:F40 K14:K40">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -4943,7 +5039,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I38">
+  <conditionalFormatting sqref="I14:I40">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EB71FA-E5F8-4716-839A-4CB1EFB46EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000AFBB8-A795-4D7E-B4C9-CEF3EBF9C31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="435" windowWidth="34875" windowHeight="19860" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="1305" yWindow="0" windowWidth="28800" windowHeight="20985" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="73">
   <si>
     <t>Total</t>
   </si>
@@ -262,9 +262,6 @@
     <t>Christmas --&gt; New Years</t>
   </si>
   <si>
-    <t>Splash Village (???)</t>
-  </si>
-  <si>
     <t>Not sick / Elli to Fox</t>
   </si>
   <si>
@@ -1410,7 +1407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="331">
+  <cellXfs count="342">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2225,17 +2222,11 @@
     <xf numFmtId="165" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="18" fontId="0" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2356,7 +2347,7 @@
     <xf numFmtId="18" fontId="0" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2366,13 +2357,69 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2613,7 +2660,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>557335</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>114767</xdr:rowOff>
+      <xdr:rowOff>159591</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2701,7 +2748,7 @@
       <xdr:col>25</xdr:col>
       <xdr:colOff>446143</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>39711</xdr:rowOff>
+      <xdr:rowOff>84535</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2738,13 +2785,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>458322</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3832,7 +3879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:K41"/>
+  <dimension ref="B1:K42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -3871,11 +3918,11 @@
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H40, "PTO", G14:G40)</f>
-        <v>19.5</v>
+        <f ca="1">C3 - C6 - SUMIF(H14:H41, "PTO", G14:G41)</f>
+        <v>15.5</v>
       </c>
       <c r="J3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename",A2),LEN(CELL("filename",A2))-SEARCH("]",CELL("filename",A2)))) + 1</f>
@@ -3903,11 +3950,11 @@
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
-        <v>18.625</v>
+        <v>19.125</v>
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>2.4375</v>
+        <v>1.9375</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -3922,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H40, "Sick", G14:G40)</f>
+        <f>C6 - SUMIF(H14:H41, "Sick", G14:G41)</f>
         <v>40</v>
       </c>
     </row>
@@ -3955,7 +4002,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H40, "Be You", G14:G40)</f>
+        <f>C8 - SUMIF(H14:H41, "Be You", G14:G41)</f>
         <v>0</v>
       </c>
       <c r="J8" s="51"/>
@@ -3989,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H40, "Volunteer", G14:G40)</f>
+        <f>C10 - SUMIF(H14:H41, "Volunteer", G14:G41)</f>
         <v>4</v>
       </c>
       <c r="J10" s="36"/>
@@ -4050,7 +4097,7 @@
         <v>46059</v>
       </c>
       <c r="C14" s="240" t="str">
-        <f t="shared" ref="C14:C20" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
+        <f t="shared" ref="C14:C21" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D14" s="241">
@@ -4064,7 +4111,7 @@
         <v>5</v>
       </c>
       <c r="G14" s="240">
-        <f t="shared" ref="G14:G20" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
+        <f t="shared" ref="G14:G21" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
         <v>4</v>
       </c>
       <c r="H14" s="242" t="s">
@@ -4074,43 +4121,43 @@
         <v>20</v>
       </c>
       <c r="J14" s="243" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K14" s="42" t="str">
-        <f t="shared" ref="K14:K20" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="K14:K21" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B15" s="308">
+      <c r="B15" s="306">
         <v>46080</v>
       </c>
-      <c r="C15" s="309" t="str">
+      <c r="C15" s="307" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D15" s="310">
+      <c r="D15" s="308">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E15" s="310">
+      <c r="E15" s="308">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F15" s="311">
+      <c r="F15" s="309">
         <f>((E15 - D15) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G15" s="309">
+      <c r="G15" s="307">
         <f>IF(F15 &gt; 4, (F15 - 1), F15)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H15" s="312" t="s">
+      <c r="H15" s="310" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="311" t="s">
         <v>69</v>
-      </c>
-      <c r="I15" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="313" t="s">
-        <v>70</v>
       </c>
       <c r="K15" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4118,35 +4165,35 @@
       </c>
     </row>
     <row r="16" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B16" s="284">
+      <c r="B16" s="282">
         <v>46093</v>
       </c>
-      <c r="C16" s="314" t="str">
+      <c r="C16" s="312" t="str">
         <f t="shared" ref="C16" si="3">IF(ISNUMBER(FIND("?", B16, 1)), "TBD", TEXT(B16, "ddd"))</f>
         <v>Thu</v>
       </c>
-      <c r="D16" s="315">
+      <c r="D16" s="313">
         <v>0.625</v>
       </c>
-      <c r="E16" s="315">
+      <c r="E16" s="313">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F16" s="316">
+      <c r="F16" s="314">
         <f>((E16 - D16) * 24)</f>
         <v>0.99999999999999911</v>
       </c>
-      <c r="G16" s="314">
+      <c r="G16" s="312">
         <f>IF(F16 &gt; 4, (F16 - 1), F16)</f>
         <v>0.99999999999999911</v>
       </c>
-      <c r="H16" s="317" t="s">
-        <v>69</v>
+      <c r="H16" s="315" t="s">
+        <v>68</v>
       </c>
       <c r="I16" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="290" t="s">
-        <v>71</v>
+      <c r="J16" s="288" t="s">
+        <v>70</v>
       </c>
       <c r="K16" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4161,17 +4208,17 @@
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D17" s="293">
+      <c r="D17" s="291">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E17" s="293">
+      <c r="E17" s="291">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F17" s="294">
-        <f t="shared" ref="F17:F20" si="4">((E17 - D17) * 24)</f>
+      <c r="F17" s="292">
+        <f t="shared" ref="F17:F21" si="4">((E17 - D17) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G17" s="292">
+      <c r="G17" s="290">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -4189,193 +4236,193 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="15.75" thickBot="1">
+    <row r="18" spans="2:11">
       <c r="B18" s="279">
-        <v>46213</v>
+        <v>46226</v>
       </c>
       <c r="C18" s="217" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="D18" s="280">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E18" s="280">
+        <v>Thu</v>
+      </c>
+      <c r="D18" s="157">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E18" s="157">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F18" s="283">
+      <c r="F18" s="220">
         <f t="shared" si="4"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G18" s="165">
+        <v>5</v>
+      </c>
+      <c r="G18" s="217">
         <f t="shared" si="1"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H18" s="281" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="280" t="s">
         <v>4</v>
       </c>
       <c r="I18" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="282" t="s">
-        <v>61</v>
-      </c>
-      <c r="K18" s="47" t="str">
+        <v>20</v>
+      </c>
+      <c r="J18" s="281" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B19" s="122">
-        <v>46237</v>
-      </c>
-      <c r="C19" s="240" t="str">
+    <row r="19" spans="2:11">
+      <c r="B19" s="337">
+        <v>46227</v>
+      </c>
+      <c r="C19" s="338" t="str">
+        <f>IF(ISNUMBER(FIND("?", B19, 1)), "TBD", TEXT(B19, "ddd"))</f>
+        <v>Fri</v>
+      </c>
+      <c r="D19" s="339">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E19" s="339">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F19" s="221">
+        <f>((E19 - D19) * 24)</f>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G19" s="338">
+        <f>IF(F19 &gt; 4, (F19 - 1), F19)</f>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H19" s="340" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="341" t="s">
+        <v>46</v>
+      </c>
+      <c r="K19" s="59" t="str">
+        <f ca="1">IF(C19 = "TBD", "TBD", IF(B19 = "", "IDK!!", IF(TODAY() &gt; B19, "Passed", IF(TODAY() = B19, "Today!!", "Upcoming"))))</f>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="140">
+        <v>46232</v>
+      </c>
+      <c r="C20" s="166" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
-      </c>
-      <c r="D19" s="241">
+        <v>Wed</v>
+      </c>
+      <c r="D20" s="158">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E19" s="241">
+      <c r="E20" s="158">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F19" s="257">
+      <c r="F20" s="221">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G19" s="240">
+      <c r="G20" s="166">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H19" s="242" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="243" t="s">
+      <c r="H20" s="181" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="K19" s="252" t="str">
+      <c r="K20" s="329" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B20" s="123">
-        <v>46238</v>
-      </c>
-      <c r="C20" s="245" t="str">
+    <row r="21" spans="2:11">
+      <c r="B21" s="140">
+        <v>46233</v>
+      </c>
+      <c r="C21" s="166" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
-      </c>
-      <c r="D20" s="246">
+        <v>Thu</v>
+      </c>
+      <c r="D21" s="158">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E20" s="246">
+      <c r="E21" s="158">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F20" s="258">
+      <c r="F21" s="221">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G20" s="245">
+      <c r="G21" s="166">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H20" s="247" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="248" t="s">
+      <c r="H21" s="181" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="K20" s="59" t="str">
+      <c r="K21" s="329" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B21" s="249">
-        <v>46239</v>
-      </c>
-      <c r="C21" s="245" t="str">
-        <f t="shared" ref="C21:C38" si="5">IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
-        <v>Wed</v>
-      </c>
-      <c r="D21" s="246">
+    <row r="22" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B22" s="330">
+        <v>46234</v>
+      </c>
+      <c r="C22" s="331" t="str">
+        <f t="shared" ref="C22:C39" si="5">IF(ISNUMBER(FIND("?", B22, 1)), "TBD", TEXT(B22, "ddd"))</f>
+        <v>Fri</v>
+      </c>
+      <c r="D22" s="332">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E21" s="246">
+      <c r="E22" s="332">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F21" s="258">
-        <f t="shared" ref="F21:F35" si="6">((E21 - D21) * 24)</f>
+      <c r="F22" s="333">
+        <f t="shared" ref="F22:F36" si="6">((E22 - D22) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G21" s="245">
-        <f t="shared" ref="G21:G38" si="7">IF(F21 &gt; 4, (F21 - 1), F21)</f>
-        <v>4</v>
-      </c>
-      <c r="H21" s="247" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="248" t="s">
+      <c r="G22" s="331">
+        <f t="shared" ref="G22:G39" si="7">IF(F22 &gt; 4, (F22 - 1), F22)</f>
+        <v>4</v>
+      </c>
+      <c r="H22" s="334" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="335" t="s">
         <v>59</v>
       </c>
-      <c r="K21" s="59" t="str">
-        <f t="shared" ref="K21:K38" ca="1" si="8">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
+      <c r="K22" s="336" t="str">
+        <f t="shared" ref="K22:K39" ca="1" si="8">IF(C22 = "TBD", "TBD", IF(B22 = "", "IDK!!", IF(TODAY() &gt; B22, "Passed", IF(TODAY() = B22, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B22" s="249">
+    <row r="23" spans="2:11">
+      <c r="B23" s="123">
         <v>46240</v>
       </c>
-      <c r="C22" s="245" t="str">
+      <c r="C23" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
-      </c>
-      <c r="D22" s="246">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E22" s="246">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F22" s="258">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="G22" s="245">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="H22" s="247" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="248" t="s">
-        <v>59</v>
-      </c>
-      <c r="K22" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B23" s="249">
-        <v>46241</v>
-      </c>
-      <c r="C23" s="245" t="str">
-        <f t="shared" si="5"/>
-        <v>Fri</v>
       </c>
       <c r="D23" s="246">
         <v>0.45833333333333331</v>
@@ -4407,11 +4454,11 @@
     </row>
     <row r="24" spans="2:11" ht="15.75" thickBot="1">
       <c r="B24" s="249">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="C24" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="D24" s="246">
         <v>0.45833333333333331</v>
@@ -4434,7 +4481,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="248" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="K24" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -4443,11 +4490,11 @@
     </row>
     <row r="25" spans="2:11" ht="15.75" thickBot="1">
       <c r="B25" s="249">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="C25" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Tue</v>
+        <v>Mon</v>
       </c>
       <c r="D25" s="246">
         <v>0.45833333333333331</v>
@@ -4479,11 +4526,11 @@
     </row>
     <row r="26" spans="2:11" ht="15.75" thickBot="1">
       <c r="B26" s="249">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="C26" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D26" s="246">
         <v>0.45833333333333331</v>
@@ -4514,12 +4561,12 @@
       </c>
     </row>
     <row r="27" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B27" s="250">
-        <v>46247</v>
+      <c r="B27" s="249">
+        <v>46246</v>
       </c>
       <c r="C27" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D27" s="246">
         <v>0.45833333333333331</v>
@@ -4549,13 +4596,13 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="28" spans="2:11">
+    <row r="28" spans="2:11" ht="15.75" thickBot="1">
       <c r="B28" s="250">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="C28" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="D28" s="246">
         <v>0.45833333333333331</v>
@@ -4585,19 +4632,19 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="15.75" thickBot="1">
+    <row r="29" spans="2:11">
       <c r="B29" s="250">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="C29" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Fri</v>
       </c>
       <c r="D29" s="246">
-        <v>0.29166666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E29" s="246">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F29" s="258">
         <f t="shared" si="6"/>
@@ -4614,237 +4661,237 @@
         <v>20</v>
       </c>
       <c r="J29" s="248" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="K29" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="105">
+    <row r="30" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B30" s="250">
+        <v>46253</v>
+      </c>
+      <c r="C30" s="245" t="str">
+        <f t="shared" si="5"/>
+        <v>Wed</v>
+      </c>
+      <c r="D30" s="246">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E30" s="246">
+        <v>0.5</v>
+      </c>
+      <c r="F30" s="258">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G30" s="245">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H30" s="247" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="248" t="s">
+        <v>71</v>
+      </c>
+      <c r="K30" s="59" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="105">
         <v>46269</v>
       </c>
-      <c r="C30" s="170" t="str">
-        <f t="shared" ref="C30:C32" si="9">IF(ISNUMBER(FIND("?", B30, 1)), "TBD", TEXT(B30, "ddd"))</f>
+      <c r="C31" s="170" t="str">
+        <f t="shared" ref="C31:C33" si="9">IF(ISNUMBER(FIND("?", B31, 1)), "TBD", TEXT(B31, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D30" s="160">
+      <c r="D31" s="160">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E30" s="160">
+      <c r="E31" s="160">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F30" s="224">
-        <f t="shared" ref="F30:F32" si="10">((E30 - D30) * 24)</f>
+      <c r="F31" s="224">
+        <f t="shared" ref="F31:F33" si="10">((E31 - D31) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G30" s="170">
-        <f t="shared" ref="G30:G32" si="11">IF(F30 &gt; 4, (F30 - 1), F30)</f>
-        <v>4</v>
-      </c>
-      <c r="H30" s="185" t="s">
-        <v>4</v>
-      </c>
-      <c r="I30" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="210" t="s">
+      <c r="G31" s="170">
+        <f t="shared" ref="G31:G33" si="11">IF(F31 &gt; 4, (F31 - 1), F31)</f>
+        <v>4</v>
+      </c>
+      <c r="H31" s="185" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="42" t="str">
-        <f t="shared" ref="K30:K32" ca="1" si="12">IF(C30 = "TBD", "TBD", IF(B30 = "", "IDK!!", IF(TODAY() &gt; B30, "Passed", IF(TODAY() = B30, "Today!!", "Upcoming"))))</f>
+      <c r="K31" s="42" t="str">
+        <f t="shared" ref="K31:K33" ca="1" si="12">IF(C31 = "TBD", "TBD", IF(B31 = "", "IDK!!", IF(TODAY() &gt; B31, "Passed", IF(TODAY() = B31, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="324">
+    <row r="32" spans="2:11">
+      <c r="B32" s="322">
         <v>46275</v>
       </c>
-      <c r="C31" s="325" t="str">
+      <c r="C32" s="323" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D31" s="326">
+      <c r="D32" s="324">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E31" s="326">
+      <c r="E32" s="324">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F31" s="327">
+      <c r="F32" s="325">
         <f t="shared" si="10"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="G31" s="325">
+      <c r="G32" s="323">
         <f t="shared" si="11"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="H31" s="328" t="s">
-        <v>4</v>
-      </c>
-      <c r="I31" s="329" t="s">
-        <v>28</v>
-      </c>
-      <c r="J31" s="330" t="s">
-        <v>73</v>
-      </c>
-      <c r="K31" s="67" t="str">
+      <c r="H32" s="326" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="328" t="s">
+        <v>72</v>
+      </c>
+      <c r="K32" s="67" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B32" s="318">
+    <row r="33" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B33" s="316">
         <v>46275</v>
       </c>
-      <c r="C32" s="319" t="str">
+      <c r="C33" s="317" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D32" s="320">
+      <c r="D33" s="318">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E32" s="320">
+      <c r="E33" s="318">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F32" s="321">
+      <c r="F33" s="319">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="G32" s="319">
+      <c r="G33" s="317">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="H32" s="322" t="s">
+      <c r="H33" s="320" t="s">
         <v>10</v>
       </c>
-      <c r="I32" s="244" t="s">
-        <v>28</v>
-      </c>
-      <c r="J32" s="323" t="s">
-        <v>73</v>
-      </c>
-      <c r="K32" s="60" t="str">
+      <c r="I33" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="321" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="60" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B33" s="124">
+    <row r="34" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B34" s="124">
         <v>46353</v>
       </c>
-      <c r="C33" s="173" t="str">
+      <c r="C34" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D33" s="155">
+      <c r="D34" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E33" s="155">
+      <c r="E34" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F33" s="226">
+      <c r="F34" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G33" s="173">
+      <c r="G34" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H33" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="269" t="s">
+      <c r="H34" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I34" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="192" t="str">
+      <c r="K34" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B34" s="112">
+    <row r="35" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B35" s="112">
         <v>46380</v>
       </c>
-      <c r="C34" s="264" t="str">
+      <c r="C35" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D34" s="262">
+      <c r="D35" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E34" s="262">
+      <c r="E35" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F34" s="263">
+      <c r="F35" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G34" s="264">
+      <c r="G35" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H34" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I34" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="266" t="s">
+      <c r="H35" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="K34" s="42" t="str">
+      <c r="K35" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B35" s="120">
+    <row r="36" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B36" s="120">
         <v>46384</v>
       </c>
-      <c r="C35" s="274" t="str">
+      <c r="C36" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D35" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E35" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F35" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G35" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H35" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="K35" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B36" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C36" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
       <c r="D36" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -4852,34 +4899,34 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F36" s="276">
-        <f t="shared" ref="F36:F38" si="13">((E36 - D36) * 24)</f>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G36" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H36" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I36" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="273" t="s">
+      <c r="H36" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="K36" s="193" t="str">
+      <c r="K36" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="37" spans="2:11">
+    <row r="37" spans="2:11" ht="15.75" thickBot="1">
       <c r="B37" s="270">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C37" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D37" s="275">
         <v>0.29166666666666669</v>
@@ -4888,7 +4935,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F37" s="276">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="F37:F39" si="13">((E37 - D37) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G37" s="274">
@@ -4909,13 +4956,13 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B38" s="113">
-        <v>46387</v>
+    <row r="38" spans="2:11">
+      <c r="B38" s="270">
+        <v>46386</v>
       </c>
       <c r="C38" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D38" s="275">
         <v>0.29166666666666669</v>
@@ -4931,13 +4978,13 @@
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H38" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I38" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="268" t="s">
+      <c r="H38" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="273" t="s">
         <v>60</v>
       </c>
       <c r="K38" s="193" t="str">
@@ -4945,105 +4992,141 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="102"/>
-      <c r="C39" s="165" t="str">
-        <f t="shared" ref="C39:C40" si="14">IF(ISNUMBER(FIND("?", B39, 1)), "TBD", TEXT(B39, "ddd"))</f>
+    <row r="39" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B39" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C39" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D39" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E39" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F39" s="276">
+        <f t="shared" si="13"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G39" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H39" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I39" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="K39" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
+      <c r="B40" s="102"/>
+      <c r="C40" s="165" t="str">
+        <f t="shared" ref="C40:C41" si="14">IF(ISNUMBER(FIND("?", B40, 1)), "TBD", TEXT(B40, "ddd"))</f>
         <v>Sat</v>
       </c>
-      <c r="D39" s="157"/>
-      <c r="E39" s="157"/>
-      <c r="F39" s="220">
-        <f t="shared" ref="F39:F40" si="15">((E39 - D39) * 24)</f>
+      <c r="D40" s="157"/>
+      <c r="E40" s="157"/>
+      <c r="F40" s="220">
+        <f t="shared" ref="F40:F41" si="15">((E40 - D40) * 24)</f>
         <v>0</v>
       </c>
-      <c r="G39" s="217">
-        <f t="shared" ref="G39:G40" si="16">IF(F39 &gt; 4, (F39 - 1), F39)</f>
+      <c r="G40" s="217">
+        <f t="shared" ref="G40:G41" si="16">IF(F40 &gt; 4, (F40 - 1), F40)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="180"/>
-      <c r="I39" s="197" t="s">
-        <v>67</v>
-      </c>
-      <c r="J39" s="205"/>
-      <c r="K39" s="252" t="str">
-        <f t="shared" ref="K39:K40" ca="1" si="17">IF(C39 = "TBD", "TBD", IF(B39 = "", "IDK!!", IF(TODAY() &gt; B39, "Passed", IF(TODAY() = B39, "Today!!", "Upcoming"))))</f>
+      <c r="H40" s="180"/>
+      <c r="I40" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="J40" s="205"/>
+      <c r="K40" s="252" t="str">
+        <f t="shared" ref="K40:K41" ca="1" si="17">IF(C40 = "TBD", "TBD", IF(B40 = "", "IDK!!", IF(TODAY() &gt; B40, "Passed", IF(TODAY() = B40, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="40" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B40" s="259"/>
-      <c r="C40" s="253" t="str">
+    <row r="41" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B41" s="259"/>
+      <c r="C41" s="253" t="str">
         <f t="shared" si="14"/>
         <v>Sat</v>
       </c>
-      <c r="D40" s="260"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="261">
+      <c r="D41" s="260"/>
+      <c r="E41" s="260"/>
+      <c r="F41" s="261">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G40" s="253">
+      <c r="G41" s="253">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H40" s="254"/>
-      <c r="I40" s="202" t="s">
-        <v>67</v>
-      </c>
-      <c r="J40" s="255"/>
-      <c r="K40" s="251" t="str">
+      <c r="H41" s="254"/>
+      <c r="I41" s="202" t="s">
+        <v>66</v>
+      </c>
+      <c r="J41" s="255"/>
+      <c r="K41" s="251" t="str">
         <f t="shared" ca="1" si="17"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="41" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B41" s="86" t="s">
+    <row r="42" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B42" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="305"/>
-      <c r="D41" s="306"/>
-      <c r="E41" s="307"/>
-      <c r="F41" s="228">
-        <f>SUM(F14:F40)</f>
-        <v>147</v>
-      </c>
-      <c r="G41" s="256">
-        <f>SUM(G14:G40)</f>
-        <v>125</v>
-      </c>
-      <c r="H41" s="303"/>
-      <c r="I41" s="304"/>
-      <c r="J41" s="304"/>
-      <c r="K41" s="304"/>
+      <c r="C42" s="303"/>
+      <c r="D42" s="304"/>
+      <c r="E42" s="305"/>
+      <c r="F42" s="228">
+        <f>SUM(F14:F41)</f>
+        <v>152</v>
+      </c>
+      <c r="G42" s="256">
+        <f>SUM(G14:G41)</f>
+        <v>129</v>
+      </c>
+      <c r="H42" s="301"/>
+      <c r="I42" s="302"/>
+      <c r="J42" s="302"/>
+      <c r="K42" s="302"/>
     </row>
   </sheetData>
-  <autoFilter ref="B13:J41" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
-  <conditionalFormatting sqref="B14:K40">
-    <cfRule type="expression" dxfId="20" priority="2">
+  <autoFilter ref="B13:J42" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <conditionalFormatting sqref="B14:K41">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F40 K14:K40">
-    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
+  <conditionalFormatting sqref="K14:K41 C14:F41">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="18" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I40">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+  <conditionalFormatting sqref="I14:I41">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6023,22 +6106,22 @@
   </sheetData>
   <autoFilter ref="B13:G44" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="C14:C43 H14:H43">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="9" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F43">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6904,7 +6987,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="212" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K31" s="193" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -6940,7 +7023,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="212" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K32" s="193" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -7092,35 +7175,35 @@
       </c>
     </row>
     <row r="37" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B37" s="284">
+      <c r="B37" s="282">
         <v>45936</v>
       </c>
-      <c r="C37" s="285" t="str">
+      <c r="C37" s="283" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="D37" s="286">
+      <c r="D37" s="284">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E37" s="286">
+      <c r="E37" s="284">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F37" s="287">
+      <c r="F37" s="285">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G37" s="285">
+      <c r="G37" s="283">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H37" s="288" t="s">
+      <c r="H37" s="286" t="s">
         <v>32</v>
       </c>
-      <c r="I37" s="289" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="290" t="s">
-        <v>64</v>
+      <c r="I37" s="287" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="288" t="s">
+        <v>63</v>
       </c>
       <c r="K37" s="67" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -7128,34 +7211,34 @@
       </c>
     </row>
     <row r="38" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B38" s="291">
+      <c r="B38" s="289">
         <v>45989</v>
       </c>
-      <c r="C38" s="292" t="str">
+      <c r="C38" s="290" t="str">
         <f t="shared" ref="C38" si="8">IF(ISNUMBER(FIND("?", B38, 1)), "TBD", TEXT(B38, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D38" s="293">
+      <c r="D38" s="291">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E38" s="293">
+      <c r="E38" s="291">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F38" s="294">
+      <c r="F38" s="292">
         <f>((E38 - D38) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G38" s="292">
+      <c r="G38" s="290">
         <f>IF(F38 &gt; 4, (F38 - 1), F38)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H38" s="295" t="s">
+      <c r="H38" s="293" t="s">
         <v>4</v>
       </c>
       <c r="I38" s="197" t="s">
         <v>20</v>
       </c>
-      <c r="J38" s="296" t="s">
+      <c r="J38" s="294" t="s">
         <v>14</v>
       </c>
       <c r="K38" s="47" t="str">
@@ -7164,35 +7247,35 @@
       </c>
     </row>
     <row r="39" spans="2:11">
-      <c r="B39" s="297">
+      <c r="B39" s="295">
         <v>45999</v>
       </c>
-      <c r="C39" s="298" t="str">
+      <c r="C39" s="296" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="D39" s="299">
+      <c r="D39" s="297">
         <v>0.60416666666666663</v>
       </c>
-      <c r="E39" s="299">
+      <c r="E39" s="297">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F39" s="300">
+      <c r="F39" s="298">
         <f>((E39 - D39) * 24)</f>
         <v>1.5</v>
       </c>
-      <c r="G39" s="298">
+      <c r="G39" s="296">
         <f>IF(F39 &gt; 4, (F39 - 1), F39)</f>
         <v>1.5</v>
       </c>
-      <c r="H39" s="301" t="s">
+      <c r="H39" s="299" t="s">
         <v>32</v>
       </c>
       <c r="I39" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="J39" s="302" t="s">
-        <v>62</v>
+      <c r="J39" s="300" t="s">
+        <v>61</v>
       </c>
       <c r="K39" s="42" t="str">
         <f ca="1">IF(C39 = "TBD", "TBD", IF(B39 = "", "IDK!!", IF(TODAY() &gt; B39, "Passed", IF(TODAY() = B39, "Today!!", "Upcoming"))))</f>
@@ -7228,7 +7311,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="239" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K40" s="59" t="str">
         <f t="shared" ref="K40" ca="1" si="10">IF(C40 = "TBD", "TBD", IF(B40 = "", "IDK!!", IF(TODAY() &gt; B40, "Passed", IF(TODAY() = B40, "Today!!", "Upcoming"))))</f>
@@ -7264,7 +7347,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="239" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K41" s="59" t="str">
         <f t="shared" ref="K41" ca="1" si="12">IF(C41 = "TBD", "TBD", IF(B41 = "", "IDK!!", IF(TODAY() &gt; B41, "Passed", IF(TODAY() = B41, "Today!!", "Upcoming"))))</f>
@@ -7510,27 +7593,27 @@
   </sheetData>
   <autoFilter ref="B13:J48" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="B14:K47">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:F47 K14:K47">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I47">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8378,17 +8461,17 @@
   </sheetData>
   <autoFilter ref="B12:G43" xr:uid="{25002DC1-579B-4118-A464-8DA972BBC903}"/>
   <conditionalFormatting sqref="E3:E4">
-    <cfRule type="cellIs" dxfId="5" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E10">
-    <cfRule type="cellIs" dxfId="4" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="15" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E42">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8681,17 +8764,17 @@
   </sheetData>
   <autoFilter ref="B13:G13" xr:uid="{3C8D74E6-E2F4-497A-863D-7746D04C8BB1}"/>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E15">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000AFBB8-A795-4D7E-B4C9-CEF3EBF9C31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9426A46-EFCE-47A3-A82F-F280F815F247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="0" windowWidth="28800" windowHeight="20985" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="3420" yWindow="0" windowWidth="32970" windowHeight="20985" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="75">
   <si>
     <t>Total</t>
   </si>
@@ -297,6 +297,12 @@
   <si>
     <t>Doctor (split across PTO &amp; Be You)</t>
   </si>
+  <si>
+    <t>05/??/2026</t>
+  </si>
+  <si>
+    <t>Rubi to Fox (brakes)</t>
+  </si>
 </sst>
 </file>
 
@@ -1407,7 +1413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="342">
+  <cellXfs count="345">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2398,28 +2404,20 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <font>
         <b/>
@@ -2660,7 +2658,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>557335</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>159591</xdr:rowOff>
+      <xdr:rowOff>170796</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2748,7 +2746,7 @@
       <xdr:col>25</xdr:col>
       <xdr:colOff>446143</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>84535</xdr:rowOff>
+      <xdr:rowOff>95741</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2785,13 +2783,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>458322</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3879,7 +3877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:K42"/>
+  <dimension ref="B1:K43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -3918,11 +3916,11 @@
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H41, "PTO", G14:G41)</f>
-        <v>15.5</v>
+        <f ca="1">C3 - C6 - SUMIF(H14:H42, "PTO", G14:G42)</f>
+        <v>7.5</v>
       </c>
       <c r="J3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename",A2),LEN(CELL("filename",A2))-SEARCH("]",CELL("filename",A2)))) + 1</f>
@@ -3950,11 +3948,11 @@
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
-        <v>19.125</v>
+        <v>20.125</v>
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>1.9375</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -3969,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H41, "Sick", G14:G41)</f>
+        <f>C6 - SUMIF(H14:H42, "Sick", G14:G42)</f>
         <v>40</v>
       </c>
     </row>
@@ -4002,7 +4000,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H41, "Be You", G14:G41)</f>
+        <f>C8 - SUMIF(H14:H42, "Be You", G14:G42)</f>
         <v>0</v>
       </c>
       <c r="J8" s="51"/>
@@ -4036,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H41, "Volunteer", G14:G41)</f>
+        <f>C10 - SUMIF(H14:H42, "Volunteer", G14:G42)</f>
         <v>4</v>
       </c>
       <c r="J10" s="36"/>
@@ -4097,7 +4095,7 @@
         <v>46059</v>
       </c>
       <c r="C14" s="240" t="str">
-        <f t="shared" ref="C14:C21" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
+        <f t="shared" ref="C14:C22" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D14" s="241">
@@ -4111,7 +4109,7 @@
         <v>5</v>
       </c>
       <c r="G14" s="240">
-        <f t="shared" ref="G14:G21" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
+        <f t="shared" ref="G14:G22" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
         <v>4</v>
       </c>
       <c r="H14" s="242" t="s">
@@ -4124,7 +4122,7 @@
         <v>67</v>
       </c>
       <c r="K14" s="42" t="str">
-        <f t="shared" ref="K14:K21" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="K14:K22" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
@@ -4200,157 +4198,157 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B17" s="112">
+    <row r="17" spans="2:11">
+      <c r="B17" s="112" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="264" t="str">
+        <f>IF(ISNUMBER(FIND("?", B17, 1)), "TBD", TEXT(B17, "ddd"))</f>
+        <v>TBD</v>
+      </c>
+      <c r="D17" s="262">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E17" s="262">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F17" s="40">
+        <f>((E17 - D17) * 24)</f>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G17" s="264">
+        <f>IF(F17 &gt; 4, (F17 - 1), F17)</f>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H17" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="196" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="266" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" s="42" t="str">
+        <f ca="1">IF(C17 = "TBD", "TBD", IF(B17 = "", "IDK!!", IF(TODAY() &gt; B17, "Passed", IF(TODAY() = B17, "Today!!", "Upcoming"))))</f>
+        <v>TBD</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B18" s="113">
         <v>46164</v>
       </c>
-      <c r="C17" s="264" t="str">
+      <c r="C18" s="342" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D17" s="291">
+      <c r="D18" s="343">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E17" s="291">
+      <c r="E18" s="343">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F17" s="292">
-        <f t="shared" ref="F17:F21" si="4">((E17 - D17) * 24)</f>
+      <c r="F18" s="344">
+        <f t="shared" ref="F18:F22" si="4">((E18 - D18) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G17" s="290">
+      <c r="G18" s="342">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H17" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="266" t="s">
+      <c r="H18" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="268" t="s">
         <v>42</v>
       </c>
-      <c r="K17" s="47" t="str">
+      <c r="K18" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="18" spans="2:11">
-      <c r="B18" s="279">
+    <row r="19" spans="2:11">
+      <c r="B19" s="279">
         <v>46226</v>
       </c>
-      <c r="C18" s="217" t="str">
+      <c r="C19" s="217" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="D18" s="157">
+      <c r="D19" s="157">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E18" s="157">
+      <c r="E19" s="157">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F18" s="220">
+      <c r="F19" s="220">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G18" s="217">
+      <c r="G19" s="217">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H18" s="280" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="281" t="s">
+      <c r="H19" s="280" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="281" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="42" t="str">
+      <c r="K19" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
-      <c r="B19" s="337">
+    <row r="20" spans="2:11">
+      <c r="B20" s="337">
         <v>46227</v>
       </c>
-      <c r="C19" s="338" t="str">
-        <f>IF(ISNUMBER(FIND("?", B19, 1)), "TBD", TEXT(B19, "ddd"))</f>
+      <c r="C20" s="338" t="str">
+        <f>IF(ISNUMBER(FIND("?", B20, 1)), "TBD", TEXT(B20, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D19" s="339">
+      <c r="D20" s="339">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E19" s="339">
+      <c r="E20" s="339">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F19" s="221">
-        <f>((E19 - D19) * 24)</f>
+      <c r="F20" s="221">
+        <f>((E20 - D20) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G19" s="338">
-        <f>IF(F19 &gt; 4, (F19 - 1), F19)</f>
+      <c r="G20" s="338">
+        <f>IF(F20 &gt; 4, (F20 - 1), F20)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H19" s="340" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="341" t="s">
+      <c r="H20" s="340" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="K19" s="59" t="str">
-        <f ca="1">IF(C19 = "TBD", "TBD", IF(B19 = "", "IDK!!", IF(TODAY() &gt; B19, "Passed", IF(TODAY() = B19, "Today!!", "Upcoming"))))</f>
+      <c r="K20" s="59" t="str">
+        <f ca="1">IF(C20 = "TBD", "TBD", IF(B20 = "", "IDK!!", IF(TODAY() &gt; B20, "Passed", IF(TODAY() = B20, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="20" spans="2:11">
-      <c r="B20" s="140">
+    <row r="21" spans="2:11">
+      <c r="B21" s="140">
         <v>46232</v>
       </c>
-      <c r="C20" s="166" t="str">
+      <c r="C21" s="166" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
-      </c>
-      <c r="D20" s="158">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E20" s="158">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F20" s="221">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="G20" s="166">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="H20" s="181" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="206" t="s">
-        <v>59</v>
-      </c>
-      <c r="K20" s="329" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="140">
-        <v>46233</v>
-      </c>
-      <c r="C21" s="166" t="str">
-        <f t="shared" si="0"/>
-        <v>Thu</v>
       </c>
       <c r="D21" s="158">
         <v>0.45833333333333331</v>
@@ -4380,85 +4378,85 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B22" s="330">
+    <row r="22" spans="2:11">
+      <c r="B22" s="140">
+        <v>46233</v>
+      </c>
+      <c r="C22" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="D22" s="158">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E22" s="158">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F22" s="221">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="G22" s="166">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H22" s="181" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="206" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22" s="329" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B23" s="330">
         <v>46234</v>
       </c>
-      <c r="C22" s="331" t="str">
-        <f t="shared" ref="C22:C39" si="5">IF(ISNUMBER(FIND("?", B22, 1)), "TBD", TEXT(B22, "ddd"))</f>
+      <c r="C23" s="331" t="str">
+        <f t="shared" ref="C23:C40" si="5">IF(ISNUMBER(FIND("?", B23, 1)), "TBD", TEXT(B23, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D22" s="332">
+      <c r="D23" s="332">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E22" s="332">
+      <c r="E23" s="332">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F22" s="333">
-        <f t="shared" ref="F22:F36" si="6">((E22 - D22) * 24)</f>
+      <c r="F23" s="333">
+        <f t="shared" ref="F23:F37" si="6">((E23 - D23) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G22" s="331">
-        <f t="shared" ref="G22:G39" si="7">IF(F22 &gt; 4, (F22 - 1), F22)</f>
-        <v>4</v>
-      </c>
-      <c r="H22" s="334" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="335" t="s">
+      <c r="G23" s="331">
+        <f t="shared" ref="G23:G40" si="7">IF(F23 &gt; 4, (F23 - 1), F23)</f>
+        <v>4</v>
+      </c>
+      <c r="H23" s="334" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="335" t="s">
         <v>59</v>
       </c>
-      <c r="K22" s="336" t="str">
-        <f t="shared" ref="K22:K39" ca="1" si="8">IF(C22 = "TBD", "TBD", IF(B22 = "", "IDK!!", IF(TODAY() &gt; B22, "Passed", IF(TODAY() = B22, "Today!!", "Upcoming"))))</f>
+      <c r="K23" s="336" t="str">
+        <f t="shared" ref="K23:K40" ca="1" si="8">IF(C23 = "TBD", "TBD", IF(B23 = "", "IDK!!", IF(TODAY() &gt; B23, "Passed", IF(TODAY() = B23, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="23" spans="2:11">
-      <c r="B23" s="123">
+    <row r="24" spans="2:11">
+      <c r="B24" s="123">
         <v>46240</v>
       </c>
-      <c r="C23" s="245" t="str">
+      <c r="C24" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
-      </c>
-      <c r="D23" s="246">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E23" s="246">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F23" s="258">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="G23" s="245">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="H23" s="247" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="248" t="s">
-        <v>59</v>
-      </c>
-      <c r="K23" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B24" s="249">
-        <v>46241</v>
-      </c>
-      <c r="C24" s="245" t="str">
-        <f t="shared" si="5"/>
-        <v>Fri</v>
       </c>
       <c r="D24" s="246">
         <v>0.45833333333333331</v>
@@ -4490,11 +4488,11 @@
     </row>
     <row r="25" spans="2:11" ht="15.75" thickBot="1">
       <c r="B25" s="249">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="C25" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="D25" s="246">
         <v>0.45833333333333331</v>
@@ -4517,7 +4515,7 @@
         <v>20</v>
       </c>
       <c r="J25" s="248" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="K25" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -4526,11 +4524,11 @@
     </row>
     <row r="26" spans="2:11" ht="15.75" thickBot="1">
       <c r="B26" s="249">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="C26" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Tue</v>
+        <v>Mon</v>
       </c>
       <c r="D26" s="246">
         <v>0.45833333333333331</v>
@@ -4562,11 +4560,11 @@
     </row>
     <row r="27" spans="2:11" ht="15.75" thickBot="1">
       <c r="B27" s="249">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="C27" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D27" s="246">
         <v>0.45833333333333331</v>
@@ -4597,12 +4595,12 @@
       </c>
     </row>
     <row r="28" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B28" s="250">
-        <v>46247</v>
+      <c r="B28" s="249">
+        <v>46246</v>
       </c>
       <c r="C28" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D28" s="246">
         <v>0.45833333333333331</v>
@@ -4632,13 +4630,13 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="29" spans="2:11">
+    <row r="29" spans="2:11" ht="15.75" thickBot="1">
       <c r="B29" s="250">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="C29" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="D29" s="246">
         <v>0.45833333333333331</v>
@@ -4668,19 +4666,19 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="15.75" thickBot="1">
+    <row r="30" spans="2:11">
       <c r="B30" s="250">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="C30" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Fri</v>
       </c>
       <c r="D30" s="246">
-        <v>0.29166666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E30" s="246">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F30" s="258">
         <f t="shared" si="6"/>
@@ -4697,237 +4695,237 @@
         <v>20</v>
       </c>
       <c r="J30" s="248" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="K30" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="105">
+    <row r="31" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B31" s="250">
+        <v>46253</v>
+      </c>
+      <c r="C31" s="245" t="str">
+        <f t="shared" si="5"/>
+        <v>Wed</v>
+      </c>
+      <c r="D31" s="246">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E31" s="246">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="258">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G31" s="245">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H31" s="247" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="248" t="s">
+        <v>71</v>
+      </c>
+      <c r="K31" s="59" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="105">
         <v>46269</v>
       </c>
-      <c r="C31" s="170" t="str">
-        <f t="shared" ref="C31:C33" si="9">IF(ISNUMBER(FIND("?", B31, 1)), "TBD", TEXT(B31, "ddd"))</f>
+      <c r="C32" s="170" t="str">
+        <f t="shared" ref="C32:C34" si="9">IF(ISNUMBER(FIND("?", B32, 1)), "TBD", TEXT(B32, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D31" s="160">
+      <c r="D32" s="160">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E31" s="160">
+      <c r="E32" s="160">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F31" s="224">
-        <f t="shared" ref="F31:F33" si="10">((E31 - D31) * 24)</f>
+      <c r="F32" s="224">
+        <f t="shared" ref="F32:F34" si="10">((E32 - D32) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G31" s="170">
-        <f t="shared" ref="G31:G33" si="11">IF(F31 &gt; 4, (F31 - 1), F31)</f>
-        <v>4</v>
-      </c>
-      <c r="H31" s="185" t="s">
-        <v>4</v>
-      </c>
-      <c r="I31" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="210" t="s">
+      <c r="G32" s="170">
+        <f t="shared" ref="G32:G34" si="11">IF(F32 &gt; 4, (F32 - 1), F32)</f>
+        <v>4</v>
+      </c>
+      <c r="H32" s="185" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="42" t="str">
-        <f t="shared" ref="K31:K33" ca="1" si="12">IF(C31 = "TBD", "TBD", IF(B31 = "", "IDK!!", IF(TODAY() &gt; B31, "Passed", IF(TODAY() = B31, "Today!!", "Upcoming"))))</f>
+      <c r="K32" s="42" t="str">
+        <f t="shared" ref="K32:K34" ca="1" si="12">IF(C32 = "TBD", "TBD", IF(B32 = "", "IDK!!", IF(TODAY() &gt; B32, "Passed", IF(TODAY() = B32, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="322">
+    <row r="33" spans="2:11">
+      <c r="B33" s="322">
         <v>46275</v>
       </c>
-      <c r="C32" s="323" t="str">
+      <c r="C33" s="323" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D32" s="324">
+      <c r="D33" s="324">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E32" s="324">
+      <c r="E33" s="324">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F32" s="325">
+      <c r="F33" s="325">
         <f t="shared" si="10"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="G32" s="323">
+      <c r="G33" s="323">
         <f t="shared" si="11"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="H32" s="326" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="328" t="s">
+      <c r="H33" s="326" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="328" t="s">
         <v>72</v>
       </c>
-      <c r="K32" s="67" t="str">
+      <c r="K33" s="67" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B33" s="316">
+    <row r="34" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B34" s="316">
         <v>46275</v>
       </c>
-      <c r="C33" s="317" t="str">
+      <c r="C34" s="317" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D33" s="318">
+      <c r="D34" s="318">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E33" s="318">
+      <c r="E34" s="318">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F33" s="319">
+      <c r="F34" s="319">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="G33" s="317">
+      <c r="G34" s="317">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="H33" s="320" t="s">
+      <c r="H34" s="320" t="s">
         <v>10</v>
       </c>
-      <c r="I33" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="321" t="s">
+      <c r="I34" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="321" t="s">
         <v>72</v>
       </c>
-      <c r="K33" s="60" t="str">
+      <c r="K34" s="60" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B34" s="124">
+    <row r="35" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B35" s="124">
         <v>46353</v>
       </c>
-      <c r="C34" s="173" t="str">
+      <c r="C35" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D34" s="155">
+      <c r="D35" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E34" s="155">
+      <c r="E35" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F34" s="226">
+      <c r="F35" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G34" s="173">
+      <c r="G35" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H34" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I34" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="269" t="s">
+      <c r="H35" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="K34" s="192" t="str">
+      <c r="K35" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B35" s="112">
+    <row r="36" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B36" s="112">
         <v>46380</v>
       </c>
-      <c r="C35" s="264" t="str">
+      <c r="C36" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D35" s="262">
+      <c r="D36" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E35" s="262">
+      <c r="E36" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F35" s="263">
+      <c r="F36" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G35" s="264">
+      <c r="G36" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H35" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="266" t="s">
+      <c r="H36" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="K35" s="42" t="str">
+      <c r="K36" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="36" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B36" s="120">
+    <row r="37" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B37" s="120">
         <v>46384</v>
       </c>
-      <c r="C36" s="274" t="str">
+      <c r="C37" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D36" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E36" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F36" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G36" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H36" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I36" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="K36" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B37" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C37" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
       <c r="D37" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -4935,34 +4933,34 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F37" s="276">
-        <f t="shared" ref="F37:F39" si="13">((E37 - D37) * 24)</f>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G37" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H37" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I37" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="273" t="s">
+      <c r="H37" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I37" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="K37" s="193" t="str">
+      <c r="K37" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="38" spans="2:11">
+    <row r="38" spans="2:11" ht="15.75" thickBot="1">
       <c r="B38" s="270">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C38" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D38" s="275">
         <v>0.29166666666666669</v>
@@ -4971,7 +4969,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F38" s="276">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="F38:F40" si="13">((E38 - D38) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G38" s="274">
@@ -4992,13 +4990,13 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="39" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B39" s="113">
-        <v>46387</v>
+    <row r="39" spans="2:11">
+      <c r="B39" s="270">
+        <v>46386</v>
       </c>
       <c r="C39" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D39" s="275">
         <v>0.29166666666666669</v>
@@ -5014,13 +5012,13 @@
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H39" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I39" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="268" t="s">
+      <c r="H39" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I39" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="273" t="s">
         <v>60</v>
       </c>
       <c r="K39" s="193" t="str">
@@ -5028,105 +5026,141 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="40" spans="2:11">
-      <c r="B40" s="102"/>
-      <c r="C40" s="165" t="str">
-        <f t="shared" ref="C40:C41" si="14">IF(ISNUMBER(FIND("?", B40, 1)), "TBD", TEXT(B40, "ddd"))</f>
+    <row r="40" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B40" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C40" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D40" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E40" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F40" s="276">
+        <f t="shared" si="13"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G40" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H40" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="K40" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41" s="102"/>
+      <c r="C41" s="165" t="str">
+        <f t="shared" ref="C41:C42" si="14">IF(ISNUMBER(FIND("?", B41, 1)), "TBD", TEXT(B41, "ddd"))</f>
         <v>Sat</v>
       </c>
-      <c r="D40" s="157"/>
-      <c r="E40" s="157"/>
-      <c r="F40" s="220">
-        <f t="shared" ref="F40:F41" si="15">((E40 - D40) * 24)</f>
+      <c r="D41" s="157"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="220">
+        <f t="shared" ref="F41:F42" si="15">((E41 - D41) * 24)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="217">
-        <f t="shared" ref="G40:G41" si="16">IF(F40 &gt; 4, (F40 - 1), F40)</f>
+      <c r="G41" s="217">
+        <f t="shared" ref="G41:G42" si="16">IF(F41 &gt; 4, (F41 - 1), F41)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="180"/>
-      <c r="I40" s="197" t="s">
+      <c r="H41" s="180"/>
+      <c r="I41" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="J40" s="205"/>
-      <c r="K40" s="252" t="str">
-        <f t="shared" ref="K40:K41" ca="1" si="17">IF(C40 = "TBD", "TBD", IF(B40 = "", "IDK!!", IF(TODAY() &gt; B40, "Passed", IF(TODAY() = B40, "Today!!", "Upcoming"))))</f>
+      <c r="J41" s="205"/>
+      <c r="K41" s="252" t="str">
+        <f t="shared" ref="K41:K42" ca="1" si="17">IF(C41 = "TBD", "TBD", IF(B41 = "", "IDK!!", IF(TODAY() &gt; B41, "Passed", IF(TODAY() = B41, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="41" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B41" s="259"/>
-      <c r="C41" s="253" t="str">
+    <row r="42" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B42" s="259"/>
+      <c r="C42" s="253" t="str">
         <f t="shared" si="14"/>
         <v>Sat</v>
       </c>
-      <c r="D41" s="260"/>
-      <c r="E41" s="260"/>
-      <c r="F41" s="261">
+      <c r="D42" s="260"/>
+      <c r="E42" s="260"/>
+      <c r="F42" s="261">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G41" s="253">
+      <c r="G42" s="253">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H41" s="254"/>
-      <c r="I41" s="202" t="s">
+      <c r="H42" s="254"/>
+      <c r="I42" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="J41" s="255"/>
-      <c r="K41" s="251" t="str">
+      <c r="J42" s="255"/>
+      <c r="K42" s="251" t="str">
         <f t="shared" ca="1" si="17"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B42" s="86" t="s">
+    <row r="43" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B43" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="303"/>
-      <c r="D42" s="304"/>
-      <c r="E42" s="305"/>
-      <c r="F42" s="228">
-        <f>SUM(F14:F41)</f>
-        <v>152</v>
-      </c>
-      <c r="G42" s="256">
-        <f>SUM(G14:G41)</f>
-        <v>129</v>
-      </c>
-      <c r="H42" s="301"/>
-      <c r="I42" s="302"/>
-      <c r="J42" s="302"/>
-      <c r="K42" s="302"/>
+      <c r="C43" s="303"/>
+      <c r="D43" s="304"/>
+      <c r="E43" s="305"/>
+      <c r="F43" s="228">
+        <f>SUM(F14:F42)</f>
+        <v>161</v>
+      </c>
+      <c r="G43" s="256">
+        <f>SUM(G14:G42)</f>
+        <v>137</v>
+      </c>
+      <c r="H43" s="301"/>
+      <c r="I43" s="302"/>
+      <c r="J43" s="302"/>
+      <c r="K43" s="302"/>
     </row>
   </sheetData>
-  <autoFilter ref="B13:J42" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
-  <conditionalFormatting sqref="B14:K41">
-    <cfRule type="expression" dxfId="22" priority="2">
+  <autoFilter ref="B13:J43" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <conditionalFormatting sqref="B14:K42">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K14:K41 C14:F41">
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+  <conditionalFormatting sqref="K14:K42 C14:F42">
+    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="19" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I41">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+  <conditionalFormatting sqref="I14:I42">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6106,22 +6140,22 @@
   </sheetData>
   <autoFilter ref="B13:G44" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="C14:C43 H14:H43">
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F43">
-    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7593,27 +7627,27 @@
   </sheetData>
   <autoFilter ref="B13:J48" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="B14:K47">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:F47 K14:K47">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I47">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8461,17 +8495,17 @@
   </sheetData>
   <autoFilter ref="B12:G43" xr:uid="{25002DC1-579B-4118-A464-8DA972BBC903}"/>
   <conditionalFormatting sqref="E3:E4">
-    <cfRule type="cellIs" dxfId="7" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E10">
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="15" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E42">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8764,17 +8798,17 @@
   </sheetData>
   <autoFilter ref="B13:G13" xr:uid="{3C8D74E6-E2F4-497A-863D-7746D04C8BB1}"/>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E15">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9426A46-EFCE-47A3-A82F-F280F815F247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54BB752-A123-4705-84F7-58B32DFB110F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="0" windowWidth="32970" windowHeight="20985" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="3840" yWindow="840" windowWidth="32970" windowHeight="18735" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="86">
   <si>
     <t>Total</t>
   </si>
@@ -298,10 +298,43 @@
     <t>Doctor (split across PTO &amp; Be You)</t>
   </si>
   <si>
-    <t>05/??/2026</t>
+    <t>Rubi to Fox (brakes)</t>
   </si>
   <si>
-    <t>Rubi to Fox (brakes)</t>
+    <t>Anniversary</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>1st - 02/12/2025</t>
+  </si>
+  <si>
+    <t>2nd - 02/14/2026</t>
+  </si>
+  <si>
+    <t>3rd - 02/14/2027</t>
+  </si>
+  <si>
+    <t>4th - 02/14/2028</t>
+  </si>
+  <si>
+    <t>5th - 02/14/2029</t>
+  </si>
+  <si>
+    <t>6th - 02/14/2030</t>
+  </si>
+  <si>
+    <t>7th - 02/14/2031</t>
+  </si>
+  <si>
+    <t>8th - 02/14/2032</t>
+  </si>
+  <si>
+    <t>9th - 02/14/2033</t>
+  </si>
+  <si>
+    <t>10th - 02/14/2034</t>
   </si>
 </sst>
 </file>
@@ -312,7 +345,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
     <numFmt numFmtId="165" formatCode="mm\/dd\/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,6 +378,20 @@
       <i/>
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1413,7 +1460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="345">
+  <cellXfs count="357">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2411,6 +2458,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2658,7 +2733,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>557335</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>170796</xdr:rowOff>
+      <xdr:rowOff>182002</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2700,7 +2775,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>465383</xdr:colOff>
+      <xdr:colOff>185236</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>190161</xdr:rowOff>
     </xdr:to>
@@ -2737,16 +2812,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>190499</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>67235</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>582704</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>446143</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>95741</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>558202</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>84535</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2769,8 +2844,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15725774" y="2248460"/>
-          <a:ext cx="5132445" cy="3515777"/>
+          <a:off x="16988116" y="2442882"/>
+          <a:ext cx="5096586" cy="3625594"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2788,7 +2863,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>458322</xdr:colOff>
+      <xdr:colOff>178175</xdr:colOff>
       <xdr:row>65</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
@@ -3877,7 +3952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:K43"/>
+  <dimension ref="B1:V43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -3886,9 +3961,14 @@
     <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
     <col min="10" max="10" width="57" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" customWidth="1"/>
+    <col min="20" max="20" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15.75" thickBot="1"/>
@@ -4198,13 +4278,13 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
-      <c r="B17" s="112" t="s">
-        <v>73</v>
+    <row r="17" spans="2:22">
+      <c r="B17" s="112">
+        <v>46150</v>
       </c>
       <c r="C17" s="264" t="str">
         <f>IF(ISNUMBER(FIND("?", B17, 1)), "TBD", TEXT(B17, "ddd"))</f>
-        <v>TBD</v>
+        <v>Fri</v>
       </c>
       <c r="D17" s="262">
         <v>0.29166666666666669</v>
@@ -4224,17 +4304,17 @@
         <v>4</v>
       </c>
       <c r="I17" s="196" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J17" s="266" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K17" s="42" t="str">
         <f ca="1">IF(C17 = "TBD", "TBD", IF(B17 = "", "IDK!!", IF(TODAY() &gt; B17, "Passed", IF(TODAY() = B17, "Today!!", "Upcoming"))))</f>
-        <v>TBD</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" ht="15.75" thickBot="1">
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="15.75" thickBot="1">
       <c r="B18" s="113">
         <v>46164</v>
       </c>
@@ -4270,7 +4350,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" spans="2:22">
       <c r="B19" s="279">
         <v>46226</v>
       </c>
@@ -4306,7 +4386,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="20" spans="2:11">
+    <row r="20" spans="2:22">
       <c r="B20" s="337">
         <v>46227</v>
       </c>
@@ -4342,7 +4422,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="21" spans="2:11">
+    <row r="21" spans="2:22">
       <c r="B21" s="140">
         <v>46232</v>
       </c>
@@ -4378,7 +4458,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="22" spans="2:11">
+    <row r="22" spans="2:22">
       <c r="B22" s="140">
         <v>46233</v>
       </c>
@@ -4414,7 +4494,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="15.75" thickBot="1">
+    <row r="23" spans="2:22" ht="15.75" thickBot="1">
       <c r="B23" s="330">
         <v>46234</v>
       </c>
@@ -4450,7 +4530,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="24" spans="2:11">
+    <row r="24" spans="2:22">
       <c r="B24" s="123">
         <v>46240</v>
       </c>
@@ -4486,7 +4566,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="15.75" thickBot="1">
+    <row r="25" spans="2:22" ht="15.75" thickBot="1">
       <c r="B25" s="249">
         <v>46241</v>
       </c>
@@ -4522,7 +4602,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15.75" thickBot="1">
+    <row r="26" spans="2:22" ht="15.75" thickBot="1">
       <c r="B26" s="249">
         <v>46244</v>
       </c>
@@ -4558,7 +4638,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="15.75" thickBot="1">
+    <row r="27" spans="2:22" ht="15.75" thickBot="1">
       <c r="B27" s="249">
         <v>46245</v>
       </c>
@@ -4594,7 +4674,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="15.75" thickBot="1">
+    <row r="28" spans="2:22" ht="15.75" thickBot="1">
       <c r="B28" s="249">
         <v>46246</v>
       </c>
@@ -4630,7 +4710,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="15.75" thickBot="1">
+    <row r="29" spans="2:22" ht="15.75" thickBot="1">
       <c r="B29" s="250">
         <v>46247</v>
       </c>
@@ -4666,7 +4746,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="30" spans="2:11">
+    <row r="30" spans="2:22" ht="15.75" thickBot="1">
       <c r="B30" s="250">
         <v>46248</v>
       </c>
@@ -4702,7 +4782,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="15.75" thickBot="1">
+    <row r="31" spans="2:22" ht="15.75" thickBot="1">
       <c r="B31" s="250">
         <v>46253</v>
       </c>
@@ -4737,8 +4817,17 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="32" spans="2:11">
+      <c r="T31" s="345" t="s">
+        <v>74</v>
+      </c>
+      <c r="U31" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="V31" s="200" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22">
       <c r="B32" s="105">
         <v>46269</v>
       </c>
@@ -4773,8 +4862,17 @@
         <f t="shared" ref="K32:K34" ca="1" si="12">IF(C32 = "TBD", "TBD", IF(B32 = "", "IDK!!", IF(TODAY() &gt; B32, "Passed", IF(TODAY() = B32, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="33" spans="2:11">
+      <c r="T32" s="351" t="s">
+        <v>76</v>
+      </c>
+      <c r="U32" s="352">
+        <v>2024</v>
+      </c>
+      <c r="V32" s="353">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22">
       <c r="B33" s="322">
         <v>46275</v>
       </c>
@@ -4809,8 +4907,18 @@
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1">
+      <c r="T33" s="354" t="s">
+        <v>77</v>
+      </c>
+      <c r="U33" s="355">
+        <f>U32+1</f>
+        <v>2025</v>
+      </c>
+      <c r="V33" s="356">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" ht="15.75" thickBot="1">
       <c r="B34" s="316">
         <v>46275</v>
       </c>
@@ -4845,8 +4953,18 @@
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" ht="15.75" thickBot="1">
+      <c r="T34" s="346" t="s">
+        <v>78</v>
+      </c>
+      <c r="U34" s="70">
+        <f>U33+1</f>
+        <v>2026</v>
+      </c>
+      <c r="V34" s="347">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" ht="15.75" thickBot="1">
       <c r="B35" s="124">
         <v>46353</v>
       </c>
@@ -4881,8 +4999,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="36" spans="2:11" ht="15.75" thickBot="1">
+      <c r="T35" s="346" t="s">
+        <v>79</v>
+      </c>
+      <c r="U35" s="70">
+        <f t="shared" ref="U35:U41" si="13">U34+1</f>
+        <v>2027</v>
+      </c>
+      <c r="V35" s="347">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22">
       <c r="B36" s="112">
         <v>46380</v>
       </c>
@@ -4917,8 +5045,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" ht="15.75" thickBot="1">
+      <c r="T36" s="346" t="s">
+        <v>80</v>
+      </c>
+      <c r="U36" s="70">
+        <f t="shared" si="13"/>
+        <v>2028</v>
+      </c>
+      <c r="V36" s="347">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22">
       <c r="B37" s="120">
         <v>46384</v>
       </c>
@@ -4953,8 +5091,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="38" spans="2:11" ht="15.75" thickBot="1">
+      <c r="T37" s="346" t="s">
+        <v>81</v>
+      </c>
+      <c r="U37" s="70">
+        <f t="shared" si="13"/>
+        <v>2029</v>
+      </c>
+      <c r="V37" s="347">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22">
       <c r="B38" s="270">
         <v>46385</v>
       </c>
@@ -4969,7 +5117,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F38" s="276">
-        <f t="shared" ref="F38:F40" si="13">((E38 - D38) * 24)</f>
+        <f t="shared" ref="F38:F40" si="14">((E38 - D38) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G38" s="274">
@@ -4989,8 +5137,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="39" spans="2:11">
+      <c r="T38" s="346" t="s">
+        <v>82</v>
+      </c>
+      <c r="U38" s="70">
+        <f t="shared" si="13"/>
+        <v>2030</v>
+      </c>
+      <c r="V38" s="347">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22">
       <c r="B39" s="270">
         <v>46386</v>
       </c>
@@ -5005,7 +5163,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F39" s="276">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G39" s="274">
@@ -5025,8 +5183,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="40" spans="2:11" ht="15.75" thickBot="1">
+      <c r="T39" s="346" t="s">
+        <v>83</v>
+      </c>
+      <c r="U39" s="70">
+        <f t="shared" si="13"/>
+        <v>2031</v>
+      </c>
+      <c r="V39" s="347">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" ht="15.75" thickBot="1">
       <c r="B40" s="113">
         <v>46387</v>
       </c>
@@ -5041,7 +5209,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F40" s="276">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G40" s="274">
@@ -5061,21 +5229,31 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-    </row>
-    <row r="41" spans="2:11">
+      <c r="T40" s="346" t="s">
+        <v>84</v>
+      </c>
+      <c r="U40" s="70">
+        <f t="shared" si="13"/>
+        <v>2032</v>
+      </c>
+      <c r="V40" s="347">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="2:22" ht="15.75" thickBot="1">
       <c r="B41" s="102"/>
       <c r="C41" s="165" t="str">
-        <f t="shared" ref="C41:C42" si="14">IF(ISNUMBER(FIND("?", B41, 1)), "TBD", TEXT(B41, "ddd"))</f>
+        <f t="shared" ref="C41:C42" si="15">IF(ISNUMBER(FIND("?", B41, 1)), "TBD", TEXT(B41, "ddd"))</f>
         <v>Sat</v>
       </c>
       <c r="D41" s="157"/>
       <c r="E41" s="157"/>
       <c r="F41" s="220">
-        <f t="shared" ref="F41:F42" si="15">((E41 - D41) * 24)</f>
+        <f t="shared" ref="F41:F42" si="16">((E41 - D41) * 24)</f>
         <v>0</v>
       </c>
       <c r="G41" s="217">
-        <f t="shared" ref="G41:G42" si="16">IF(F41 &gt; 4, (F41 - 1), F41)</f>
+        <f t="shared" ref="G41:G42" si="17">IF(F41 &gt; 4, (F41 - 1), F41)</f>
         <v>0</v>
       </c>
       <c r="H41" s="180"/>
@@ -5084,24 +5262,35 @@
       </c>
       <c r="J41" s="205"/>
       <c r="K41" s="252" t="str">
-        <f t="shared" ref="K41:K42" ca="1" si="17">IF(C41 = "TBD", "TBD", IF(B41 = "", "IDK!!", IF(TODAY() &gt; B41, "Passed", IF(TODAY() = B41, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="K41:K42" ca="1" si="18">IF(C41 = "TBD", "TBD", IF(B41 = "", "IDK!!", IF(TODAY() &gt; B41, "Passed", IF(TODAY() = B41, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" ht="15.75" thickBot="1">
+      <c r="T41" s="348" t="s">
+        <v>85</v>
+      </c>
+      <c r="U41" s="349">
+        <f t="shared" si="13"/>
+        <v>2033</v>
+      </c>
+      <c r="V41" s="350">
+        <f>192 + 10</f>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" ht="15.75" thickBot="1">
       <c r="B42" s="259"/>
       <c r="C42" s="253" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Sat</v>
       </c>
       <c r="D42" s="260"/>
       <c r="E42" s="260"/>
       <c r="F42" s="261">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G42" s="253">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H42" s="254"/>
@@ -5110,11 +5299,11 @@
       </c>
       <c r="J42" s="255"/>
       <c r="K42" s="251" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="43" spans="2:11" ht="15.75" thickBot="1">
+    <row r="43" spans="2:22" ht="15.75" thickBot="1">
       <c r="B43" s="86" t="s">
         <v>11</v>
       </c>
@@ -5136,12 +5325,13 @@
     </row>
   </sheetData>
   <autoFilter ref="B13:J43" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B14:K42">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K14:K42 C14:F42">
+  <conditionalFormatting sqref="C14:F42 K14:K42">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -8514,7 +8704,7 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Nope!" error="Uh, oh... looks like you've provide an invalid input. Shame on you and your dog." xr:uid="{D8F0CFBC-8354-4D2C-B6BC-37D8763F407D}">
           <x14:formula1>
             <xm:f>Template!$B$19:$B$22</xm:f>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54BB752-A123-4705-84F7-58B32DFB110F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652EB422-6975-4F82-9263-675A33AE675F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="840" windowWidth="32970" windowHeight="18735" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="1200" yWindow="0" windowWidth="32970" windowHeight="20985" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="87">
   <si>
     <t>Total</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>10th - 02/14/2034</t>
+  </si>
+  <si>
+    <t>Fieldtrip / Friday before Memorial Day</t>
   </si>
 </sst>
 </file>
@@ -3996,11 +3999,11 @@
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
-        <v>161</v>
+        <v>164.5</v>
       </c>
       <c r="E3" s="1">
         <f ca="1">C3 - C6 - SUMIF(H14:H42, "PTO", G14:G42)</f>
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="J3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename",A2),LEN(CELL("filename",A2))-SEARCH("]",CELL("filename",A2)))) + 1</f>
@@ -4028,11 +4031,11 @@
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
-        <v>20.125</v>
+        <v>20.5625</v>
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>0.9375</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -4311,7 +4314,7 @@
       </c>
       <c r="K17" s="42" t="str">
         <f ca="1">IF(C17 = "TBD", "TBD", IF(B17 = "", "IDK!!", IF(TODAY() &gt; B17, "Passed", IF(TODAY() = B17, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="15.75" thickBot="1">
@@ -4319,22 +4322,22 @@
         <v>46164</v>
       </c>
       <c r="C18" s="342" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(FIND("?", B18, 1)), "TBD", TEXT(B18, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D18" s="343">
-        <v>0.45833333333333331</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="E18" s="343">
         <v>0.66666666666666663</v>
       </c>
       <c r="F18" s="344">
         <f t="shared" ref="F18:F22" si="4">((E18 - D18) * 24)</f>
-        <v>5</v>
+        <v>8.9999999999999982</v>
       </c>
       <c r="G18" s="342">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7.9999999999999982</v>
       </c>
       <c r="H18" s="267" t="s">
         <v>4</v>
@@ -4343,7 +4346,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="268" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="K18" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4427,22 +4430,22 @@
         <v>46232</v>
       </c>
       <c r="C21" s="166" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
         <v>Wed</v>
       </c>
       <c r="D21" s="158">
-        <v>0.45833333333333331</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="E21" s="158">
         <v>0.66666666666666663</v>
       </c>
       <c r="F21" s="221">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>3.4999999999999982</v>
       </c>
       <c r="G21" s="166">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.4999999999999982</v>
       </c>
       <c r="H21" s="181" t="s">
         <v>4</v>
@@ -5312,11 +5315,11 @@
       <c r="E43" s="305"/>
       <c r="F43" s="228">
         <f>SUM(F14:F42)</f>
-        <v>161</v>
+        <v>163.5</v>
       </c>
       <c r="G43" s="256">
         <f>SUM(G14:G42)</f>
-        <v>137</v>
+        <v>140.5</v>
       </c>
       <c r="H43" s="301"/>
       <c r="I43" s="302"/>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652EB422-6975-4F82-9263-675A33AE675F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188079D1-5DC8-4EE2-BFC5-BA8BE7E0C17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="0" windowWidth="32970" windowHeight="20985" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="1200" yWindow="420" windowWidth="32970" windowHeight="18735" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$K$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$L$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="88">
   <si>
     <t>Total</t>
   </si>
@@ -339,6 +339,10 @@
   <si>
     <t>Fieldtrip / Friday before Memorial Day</t>
   </si>
+  <si>
+    <t>UKG
+Approved?</t>
+  </si>
 </sst>
 </file>
 
@@ -1463,7 +1467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="357">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2454,12 +2458,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2490,6 +2488,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2727,14 +2740,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>104213</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>33058</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>557335</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>557336</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>182002</xdr:rowOff>
     </xdr:to>
@@ -2771,14 +2784,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>67235</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>185236</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>185237</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>190161</xdr:rowOff>
     </xdr:to>
@@ -2815,13 +2828,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>582704</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>56029</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>558202</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>84535</xdr:rowOff>
@@ -2859,14 +2872,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>178175</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>178174</xdr:colOff>
       <xdr:row>65</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
@@ -3955,7 +3968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:V43"/>
+  <dimension ref="B1:W43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -3966,16 +3979,17 @@
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="57" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.140625" customWidth="1"/>
-    <col min="20" max="20" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" customWidth="1"/>
+    <col min="21" max="21" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:11" ht="18" thickBot="1">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:12" ht="18" thickBot="1">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -3989,7 +4003,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:11">
+    <row r="3" spans="2:12">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -4005,12 +4019,12 @@
         <f ca="1">C3 - C6 - SUMIF(H14:H42, "PTO", G14:G42)</f>
         <v>4</v>
       </c>
-      <c r="J3" s="56" t="str" cm="1">
-        <f t="array" aca="1" ref="J3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename",A2),LEN(CELL("filename",A2))-SEARCH("]",CELL("filename",A2)))) + 1</f>
+      <c r="K3" s="56" t="str" cm="1">
+        <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename",A2),LEN(CELL("filename",A2))-SEARCH("]",CELL("filename",A2)))) + 1</f>
         <v>PTO Reset: 02/12/2027</v>
       </c>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="2:12">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -4021,7 +4035,7 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:11" ht="15.75" thickBot="1">
+    <row r="5" spans="2:12" ht="15.75" thickBot="1">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
@@ -4038,7 +4052,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="2:12">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -4054,7 +4068,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="15.75" thickBot="1">
+    <row r="7" spans="2:12" ht="15.75" thickBot="1">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
@@ -4071,7 +4085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="2:12">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -4086,9 +4100,9 @@
         <f>C8 - SUMIF(H14:H42, "Be You", G14:G42)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="51"/>
-    </row>
-    <row r="9" spans="2:11" ht="15.75" thickBot="1">
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="2:12" ht="15.75" thickBot="1">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -4105,7 +4119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="2:12">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -4120,9 +4134,9 @@
         <f>C10 - SUMIF(H14:H42, "Volunteer", G14:G42)</f>
         <v>4</v>
       </c>
-      <c r="J10" s="36"/>
-    </row>
-    <row r="11" spans="2:11" ht="15.75" thickBot="1">
+      <c r="K10" s="36"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
@@ -4138,10 +4152,10 @@
         <f>E10/8</f>
         <v>0.5</v>
       </c>
-      <c r="J11" s="36"/>
-    </row>
-    <row r="12" spans="2:11" ht="15.75" thickBot="1"/>
-    <row r="13" spans="2:11" ht="35.25" thickBot="1">
+      <c r="K11" s="36"/>
+    </row>
+    <row r="12" spans="2:12" ht="15.75" thickBot="1"/>
+    <row r="13" spans="2:12" ht="35.25" thickBot="1">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -4166,14 +4180,17 @@
       <c r="I13" s="195" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="203" t="s">
+      <c r="J13" s="195" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="K13" s="147" t="s">
+      <c r="L13" s="147" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="2:12">
       <c r="B14" s="122">
         <v>46059</v>
       </c>
@@ -4201,15 +4218,18 @@
       <c r="I14" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="243" t="s">
+      <c r="J14" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="243" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="42" t="str">
-        <f t="shared" ref="K14:K22" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
-        <v>Passed</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="15.75" thickBot="1">
+      <c r="L14" s="42" t="str">
+        <f t="shared" ref="L14:L22" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="15.75" thickBot="1">
       <c r="B15" s="306">
         <v>46080</v>
       </c>
@@ -4237,15 +4257,18 @@
       <c r="I15" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="311" t="s">
+      <c r="J15" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="311" t="s">
         <v>69</v>
       </c>
-      <c r="K15" s="60" t="str">
+      <c r="L15" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:11" ht="15.75" thickBot="1">
+    <row r="16" spans="2:12" ht="15.75" thickBot="1">
       <c r="B16" s="282">
         <v>46093</v>
       </c>
@@ -4273,15 +4296,18 @@
       <c r="I16" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="288" t="s">
+      <c r="J16" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="288" t="s">
         <v>70</v>
       </c>
-      <c r="K16" s="60" t="str">
+      <c r="L16" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:22">
+    <row r="17" spans="2:23">
       <c r="B17" s="112">
         <v>46150</v>
       </c>
@@ -4309,51 +4335,57 @@
       <c r="I17" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="266" t="s">
+      <c r="J17" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="266" t="s">
         <v>73</v>
       </c>
-      <c r="K17" s="42" t="str">
+      <c r="L17" s="42" t="str">
         <f ca="1">IF(C17 = "TBD", "TBD", IF(B17 = "", "IDK!!", IF(TODAY() &gt; B17, "Passed", IF(TODAY() = B17, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:22" ht="15.75" thickBot="1">
-      <c r="B18" s="113">
+    <row r="18" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B18" s="355">
         <v>46164</v>
       </c>
-      <c r="C18" s="342" t="str">
+      <c r="C18" s="356" t="str">
         <f>IF(ISNUMBER(FIND("?", B18, 1)), "TBD", TEXT(B18, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D18" s="343">
+      <c r="D18" s="357">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E18" s="343">
+      <c r="E18" s="357">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F18" s="344">
+      <c r="F18" s="342">
         <f t="shared" ref="F18:F22" si="4">((E18 - D18) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G18" s="342">
+      <c r="G18" s="356">
         <f t="shared" si="1"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H18" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="268" t="s">
+      <c r="H18" s="358" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="201" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="201" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="359" t="s">
         <v>86</v>
       </c>
-      <c r="K18" s="60" t="str">
+      <c r="L18" s="194" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="19" spans="2:22">
+    <row r="19" spans="2:23">
       <c r="B19" s="279">
         <v>46226</v>
       </c>
@@ -4381,15 +4413,18 @@
       <c r="I19" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="J19" s="281" t="s">
+      <c r="J19" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="281" t="s">
         <v>46</v>
       </c>
-      <c r="K19" s="42" t="str">
+      <c r="L19" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="20" spans="2:22">
+    <row r="20" spans="2:23">
       <c r="B20" s="337">
         <v>46227</v>
       </c>
@@ -4417,15 +4452,18 @@
       <c r="I20" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="341" t="s">
+      <c r="J20" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="K20" s="59" t="str">
+      <c r="L20" s="59" t="str">
         <f ca="1">IF(C20 = "TBD", "TBD", IF(B20 = "", "IDK!!", IF(TODAY() &gt; B20, "Passed", IF(TODAY() = B20, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="21" spans="2:22">
+    <row r="21" spans="2:23">
       <c r="B21" s="140">
         <v>46232</v>
       </c>
@@ -4453,15 +4491,18 @@
       <c r="I21" s="198" t="s">
         <v>20</v>
       </c>
-      <c r="J21" s="206" t="s">
+      <c r="J21" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="K21" s="329" t="str">
+      <c r="L21" s="329" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="22" spans="2:22">
+    <row r="22" spans="2:23">
       <c r="B22" s="140">
         <v>46233</v>
       </c>
@@ -4489,15 +4530,18 @@
       <c r="I22" s="198" t="s">
         <v>20</v>
       </c>
-      <c r="J22" s="206" t="s">
+      <c r="J22" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="K22" s="329" t="str">
+      <c r="L22" s="329" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="23" spans="2:22" ht="15.75" thickBot="1">
+    <row r="23" spans="2:23" ht="15.75" thickBot="1">
       <c r="B23" s="330">
         <v>46234</v>
       </c>
@@ -4525,15 +4569,18 @@
       <c r="I23" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="335" t="s">
+      <c r="J23" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="335" t="s">
         <v>59</v>
       </c>
-      <c r="K23" s="336" t="str">
-        <f t="shared" ref="K23:K40" ca="1" si="8">IF(C23 = "TBD", "TBD", IF(B23 = "", "IDK!!", IF(TODAY() &gt; B23, "Passed", IF(TODAY() = B23, "Today!!", "Upcoming"))))</f>
+      <c r="L23" s="336" t="str">
+        <f t="shared" ref="L23:L40" ca="1" si="8">IF(C23 = "TBD", "TBD", IF(B23 = "", "IDK!!", IF(TODAY() &gt; B23, "Passed", IF(TODAY() = B23, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="24" spans="2:22">
+    <row r="24" spans="2:23">
       <c r="B24" s="123">
         <v>46240</v>
       </c>
@@ -4561,15 +4608,18 @@
       <c r="I24" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J24" s="248" t="s">
+      <c r="J24" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="248" t="s">
         <v>59</v>
       </c>
-      <c r="K24" s="59" t="str">
+      <c r="L24" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="25" spans="2:22" ht="15.75" thickBot="1">
+    <row r="25" spans="2:23" ht="15.75" thickBot="1">
       <c r="B25" s="249">
         <v>46241</v>
       </c>
@@ -4597,15 +4647,18 @@
       <c r="I25" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J25" s="248" t="s">
+      <c r="J25" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="248" t="s">
         <v>59</v>
       </c>
-      <c r="K25" s="59" t="str">
+      <c r="L25" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="26" spans="2:22" ht="15.75" thickBot="1">
+    <row r="26" spans="2:23" ht="15.75" thickBot="1">
       <c r="B26" s="249">
         <v>46244</v>
       </c>
@@ -4633,15 +4686,18 @@
       <c r="I26" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="248" t="s">
+      <c r="J26" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="K26" s="59" t="str">
+      <c r="L26" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="27" spans="2:22" ht="15.75" thickBot="1">
+    <row r="27" spans="2:23" ht="15.75" thickBot="1">
       <c r="B27" s="249">
         <v>46245</v>
       </c>
@@ -4669,15 +4725,18 @@
       <c r="I27" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J27" s="248" t="s">
+      <c r="J27" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="K27" s="59" t="str">
+      <c r="L27" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="28" spans="2:22" ht="15.75" thickBot="1">
+    <row r="28" spans="2:23" ht="15.75" thickBot="1">
       <c r="B28" s="249">
         <v>46246</v>
       </c>
@@ -4705,15 +4764,18 @@
       <c r="I28" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J28" s="248" t="s">
+      <c r="J28" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="K28" s="59" t="str">
+      <c r="L28" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="29" spans="2:22" ht="15.75" thickBot="1">
+    <row r="29" spans="2:23" ht="15.75" thickBot="1">
       <c r="B29" s="250">
         <v>46247</v>
       </c>
@@ -4741,15 +4803,18 @@
       <c r="I29" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="248" t="s">
+      <c r="J29" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="K29" s="59" t="str">
+      <c r="L29" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="30" spans="2:22" ht="15.75" thickBot="1">
+    <row r="30" spans="2:23" ht="15.75" thickBot="1">
       <c r="B30" s="250">
         <v>46248</v>
       </c>
@@ -4777,15 +4842,18 @@
       <c r="I30" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="248" t="s">
+      <c r="J30" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="K30" s="59" t="str">
+      <c r="L30" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="31" spans="2:22" ht="15.75" thickBot="1">
+    <row r="31" spans="2:23" ht="15.75" thickBot="1">
       <c r="B31" s="250">
         <v>46253</v>
       </c>
@@ -4813,24 +4881,27 @@
       <c r="I31" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="248" t="s">
+      <c r="J31" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="248" t="s">
         <v>71</v>
       </c>
-      <c r="K31" s="59" t="str">
+      <c r="L31" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="T31" s="345" t="s">
+      <c r="U31" s="343" t="s">
         <v>74</v>
       </c>
-      <c r="U31" s="98" t="s">
+      <c r="V31" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="V31" s="200" t="s">
+      <c r="W31" s="200" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:22">
+    <row r="32" spans="2:23">
       <c r="B32" s="105">
         <v>46269</v>
       </c>
@@ -4858,24 +4929,27 @@
       <c r="I32" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="J32" s="210" t="s">
+      <c r="J32" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="42" t="str">
-        <f t="shared" ref="K32:K34" ca="1" si="12">IF(C32 = "TBD", "TBD", IF(B32 = "", "IDK!!", IF(TODAY() &gt; B32, "Passed", IF(TODAY() = B32, "Today!!", "Upcoming"))))</f>
+      <c r="L32" s="42" t="str">
+        <f t="shared" ref="L32:L34" ca="1" si="12">IF(C32 = "TBD", "TBD", IF(B32 = "", "IDK!!", IF(TODAY() &gt; B32, "Passed", IF(TODAY() = B32, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
-      <c r="T32" s="351" t="s">
+      <c r="U32" s="349" t="s">
         <v>76</v>
       </c>
-      <c r="U32" s="352">
+      <c r="V32" s="350">
         <v>2024</v>
       </c>
-      <c r="V32" s="353">
+      <c r="W32" s="351">
         <v>160</v>
       </c>
     </row>
-    <row r="33" spans="2:22">
+    <row r="33" spans="2:23">
       <c r="B33" s="322">
         <v>46275</v>
       </c>
@@ -4903,25 +4977,28 @@
       <c r="I33" s="327" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="328" t="s">
+      <c r="J33" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="328" t="s">
         <v>72</v>
       </c>
-      <c r="K33" s="67" t="str">
+      <c r="L33" s="67" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="T33" s="354" t="s">
+      <c r="U33" s="352" t="s">
         <v>77</v>
       </c>
-      <c r="U33" s="355">
-        <f>U32+1</f>
+      <c r="V33" s="353">
+        <f>V32+1</f>
         <v>2025</v>
       </c>
-      <c r="V33" s="356">
+      <c r="W33" s="354">
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="2:22" ht="15.75" thickBot="1">
+    <row r="34" spans="2:23" ht="15.75" thickBot="1">
       <c r="B34" s="316">
         <v>46275</v>
       </c>
@@ -4949,25 +5026,28 @@
       <c r="I34" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J34" s="321" t="s">
+      <c r="J34" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="321" t="s">
         <v>72</v>
       </c>
-      <c r="K34" s="60" t="str">
+      <c r="L34" s="60" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="T34" s="346" t="s">
+      <c r="U34" s="344" t="s">
         <v>78</v>
       </c>
-      <c r="U34" s="70">
-        <f>U33+1</f>
+      <c r="V34" s="70">
+        <f>V33+1</f>
         <v>2026</v>
       </c>
-      <c r="V34" s="347">
+      <c r="W34" s="345">
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="2:22" ht="15.75" thickBot="1">
+    <row r="35" spans="2:23" ht="15.75" thickBot="1">
       <c r="B35" s="124">
         <v>46353</v>
       </c>
@@ -4995,25 +5075,28 @@
       <c r="I35" s="200" t="s">
         <v>20</v>
       </c>
-      <c r="J35" s="269" t="s">
+      <c r="J35" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="K35" s="192" t="str">
+      <c r="L35" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="T35" s="346" t="s">
+      <c r="U35" s="344" t="s">
         <v>79</v>
       </c>
-      <c r="U35" s="70">
-        <f t="shared" ref="U35:U41" si="13">U34+1</f>
+      <c r="V35" s="70">
+        <f t="shared" ref="V35:V41" si="13">V34+1</f>
         <v>2027</v>
       </c>
-      <c r="V35" s="347">
+      <c r="W35" s="345">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="2:22">
+    <row r="36" spans="2:23">
       <c r="B36" s="112">
         <v>46380</v>
       </c>
@@ -5041,25 +5124,28 @@
       <c r="I36" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="J36" s="266" t="s">
+      <c r="J36" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="K36" s="42" t="str">
+      <c r="L36" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="T36" s="346" t="s">
+      <c r="U36" s="344" t="s">
         <v>80</v>
       </c>
-      <c r="U36" s="70">
+      <c r="V36" s="70">
         <f t="shared" si="13"/>
         <v>2028</v>
       </c>
-      <c r="V36" s="347">
+      <c r="W36" s="345">
         <v>176</v>
       </c>
     </row>
-    <row r="37" spans="2:22">
+    <row r="37" spans="2:23">
       <c r="B37" s="120">
         <v>46384</v>
       </c>
@@ -5087,25 +5173,28 @@
       <c r="I37" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="J37" s="278" t="s">
+      <c r="J37" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="K37" s="59" t="str">
+      <c r="L37" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="T37" s="346" t="s">
+      <c r="U37" s="344" t="s">
         <v>81</v>
       </c>
-      <c r="U37" s="70">
+      <c r="V37" s="70">
         <f t="shared" si="13"/>
         <v>2029</v>
       </c>
-      <c r="V37" s="347">
+      <c r="W37" s="345">
         <v>176</v>
       </c>
     </row>
-    <row r="38" spans="2:22">
+    <row r="38" spans="2:23">
       <c r="B38" s="270">
         <v>46385</v>
       </c>
@@ -5133,25 +5222,28 @@
       <c r="I38" s="198" t="s">
         <v>20</v>
       </c>
-      <c r="J38" s="273" t="s">
+      <c r="J38" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="273" t="s">
         <v>60</v>
       </c>
-      <c r="K38" s="193" t="str">
+      <c r="L38" s="193" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="T38" s="346" t="s">
+      <c r="U38" s="344" t="s">
         <v>82</v>
       </c>
-      <c r="U38" s="70">
+      <c r="V38" s="70">
         <f t="shared" si="13"/>
         <v>2030</v>
       </c>
-      <c r="V38" s="347">
+      <c r="W38" s="345">
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="2:22">
+    <row r="39" spans="2:23">
       <c r="B39" s="270">
         <v>46386</v>
       </c>
@@ -5179,25 +5271,28 @@
       <c r="I39" s="198" t="s">
         <v>20</v>
       </c>
-      <c r="J39" s="273" t="s">
+      <c r="J39" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="273" t="s">
         <v>60</v>
       </c>
-      <c r="K39" s="193" t="str">
+      <c r="L39" s="193" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="T39" s="346" t="s">
+      <c r="U39" s="344" t="s">
         <v>83</v>
       </c>
-      <c r="U39" s="70">
+      <c r="V39" s="70">
         <f t="shared" si="13"/>
         <v>2031</v>
       </c>
-      <c r="V39" s="347">
+      <c r="W39" s="345">
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="2:22" ht="15.75" thickBot="1">
+    <row r="40" spans="2:23" ht="15.75" thickBot="1">
       <c r="B40" s="113">
         <v>46387</v>
       </c>
@@ -5225,25 +5320,28 @@
       <c r="I40" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J40" s="268" t="s">
+      <c r="J40" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="268" t="s">
         <v>60</v>
       </c>
-      <c r="K40" s="193" t="str">
+      <c r="L40" s="193" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="T40" s="346" t="s">
+      <c r="U40" s="344" t="s">
         <v>84</v>
       </c>
-      <c r="U40" s="70">
+      <c r="V40" s="70">
         <f t="shared" si="13"/>
         <v>2032</v>
       </c>
-      <c r="V40" s="347">
+      <c r="W40" s="345">
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="2:22" ht="15.75" thickBot="1">
+    <row r="41" spans="2:23" ht="15.75" thickBot="1">
       <c r="B41" s="102"/>
       <c r="C41" s="165" t="str">
         <f t="shared" ref="C41:C42" si="15">IF(ISNUMBER(FIND("?", B41, 1)), "TBD", TEXT(B41, "ddd"))</f>
@@ -5263,24 +5361,27 @@
       <c r="I41" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="J41" s="205"/>
-      <c r="K41" s="252" t="str">
-        <f t="shared" ref="K41:K42" ca="1" si="18">IF(C41 = "TBD", "TBD", IF(B41 = "", "IDK!!", IF(TODAY() &gt; B41, "Passed", IF(TODAY() = B41, "Today!!", "Upcoming"))))</f>
+      <c r="J41" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="K41" s="205"/>
+      <c r="L41" s="252" t="str">
+        <f t="shared" ref="L41:L42" ca="1" si="18">IF(C41 = "TBD", "TBD", IF(B41 = "", "IDK!!", IF(TODAY() &gt; B41, "Passed", IF(TODAY() = B41, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
-      <c r="T41" s="348" t="s">
+      <c r="U41" s="346" t="s">
         <v>85</v>
       </c>
-      <c r="U41" s="349">
+      <c r="V41" s="347">
         <f t="shared" si="13"/>
         <v>2033</v>
       </c>
-      <c r="V41" s="350">
+      <c r="W41" s="348">
         <f>192 + 10</f>
         <v>202</v>
       </c>
     </row>
-    <row r="42" spans="2:22" ht="15.75" thickBot="1">
+    <row r="42" spans="2:23" ht="15.75" thickBot="1">
       <c r="B42" s="259"/>
       <c r="C42" s="253" t="str">
         <f t="shared" si="15"/>
@@ -5300,13 +5401,16 @@
       <c r="I42" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="J42" s="255"/>
-      <c r="K42" s="251" t="str">
+      <c r="J42" s="202" t="s">
+        <v>66</v>
+      </c>
+      <c r="K42" s="255"/>
+      <c r="L42" s="251" t="str">
         <f t="shared" ca="1" si="18"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="43" spans="2:22" ht="15.75" thickBot="1">
+    <row r="43" spans="2:23" ht="15.75" thickBot="1">
       <c r="B43" s="86" t="s">
         <v>11</v>
       </c>
@@ -5325,16 +5429,17 @@
       <c r="I43" s="302"/>
       <c r="J43" s="302"/>
       <c r="K43" s="302"/>
+      <c r="L43" s="302"/>
     </row>
   </sheetData>
-  <autoFilter ref="B13:J43" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <autoFilter ref="B13:K43" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B14:K42">
+  <conditionalFormatting sqref="B14:L42">
     <cfRule type="expression" dxfId="20" priority="2">
-      <formula>$K14="Passed"</formula>
+      <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F42 K14:K42">
+  <conditionalFormatting sqref="C14:F42 L14:L42">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -5349,7 +5454,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I42">
+  <conditionalFormatting sqref="I14:J42">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188079D1-5DC8-4EE2-BFC5-BA8BE7E0C17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64221748-09CB-406D-9C66-F92EAFE4D9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="420" windowWidth="32970" windowHeight="18735" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="3135" yWindow="1620" windowWidth="32970" windowHeight="18735" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$L$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="89">
   <si>
     <t>Total</t>
   </si>
@@ -343,6 +343,9 @@
     <t>UKG
 Approved?</t>
   </si>
+  <si>
+    <t>Garage door replacement quote</t>
+  </si>
 </sst>
 </file>
 
@@ -1467,7 +1470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="359">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2458,9 +2461,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2489,20 +2489,20 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2837,7 +2837,7 @@
       <xdr:col>25</xdr:col>
       <xdr:colOff>558202</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>84535</xdr:rowOff>
+      <xdr:rowOff>95741</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2874,13 +2874,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>178174</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3968,7 +3968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:W43"/>
+  <dimension ref="B1:W44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -4016,7 +4016,7 @@
         <v>164.5</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H42, "PTO", G14:G42)</f>
+        <f ca="1">C3 - C6 - SUMIF(H14:H43, "PTO", G14:G43)</f>
         <v>4</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
@@ -4064,7 +4064,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H42, "Sick", G14:G42)</f>
+        <f>C6 - SUMIF(H14:H43, "Sick", G14:G43)</f>
         <v>40</v>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H42, "Be You", G14:G42)</f>
+        <f>C8 - SUMIF(H14:H43, "Be You", G14:G43)</f>
         <v>0</v>
       </c>
       <c r="K8" s="51"/>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H42, "Volunteer", G14:G42)</f>
+        <f>C10 - SUMIF(H14:H43, "Volunteer", G14:G43)</f>
         <v>4</v>
       </c>
       <c r="K10" s="36"/>
@@ -4195,7 +4195,7 @@
         <v>46059</v>
       </c>
       <c r="C14" s="240" t="str">
-        <f t="shared" ref="C14:C22" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
+        <f t="shared" ref="C14:C23" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D14" s="241">
@@ -4209,7 +4209,7 @@
         <v>5</v>
       </c>
       <c r="G14" s="240">
-        <f t="shared" ref="G14:G22" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
+        <f t="shared" ref="G14:G23" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
         <v>4</v>
       </c>
       <c r="H14" s="242" t="s">
@@ -4225,7 +4225,7 @@
         <v>67</v>
       </c>
       <c r="L14" s="42" t="str">
-        <f t="shared" ref="L14:L22" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="L14:L23" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
@@ -4308,221 +4308,221 @@
       </c>
     </row>
     <row r="17" spans="2:23">
-      <c r="B17" s="112">
+      <c r="B17" s="289">
         <v>46150</v>
       </c>
-      <c r="C17" s="264" t="str">
+      <c r="C17" s="290" t="str">
         <f>IF(ISNUMBER(FIND("?", B17, 1)), "TBD", TEXT(B17, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D17" s="262">
+      <c r="D17" s="291">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E17" s="262">
+      <c r="E17" s="291">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="136">
         <f>((E17 - D17) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G17" s="264">
+      <c r="G17" s="290">
         <f>IF(F17 &gt; 4, (F17 - 1), F17)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H17" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="266" t="s">
+      <c r="H17" s="293" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="197" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="197" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="294" t="s">
         <v>73</v>
       </c>
-      <c r="L17" s="42" t="str">
+      <c r="L17" s="47" t="str">
         <f ca="1">IF(C17 = "TBD", "TBD", IF(B17 = "", "IDK!!", IF(TODAY() &gt; B17, "Passed", IF(TODAY() = B17, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B18" s="355">
+    <row r="18" spans="2:23">
+      <c r="B18" s="270">
         <v>46164</v>
       </c>
-      <c r="C18" s="356" t="str">
+      <c r="C18" s="271" t="str">
         <f>IF(ISNUMBER(FIND("?", B18, 1)), "TBD", TEXT(B18, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D18" s="357">
+      <c r="D18" s="358">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E18" s="357">
+      <c r="E18" s="358">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F18" s="342">
-        <f t="shared" ref="F18:F22" si="4">((E18 - D18) * 24)</f>
+      <c r="F18" s="76">
+        <f t="shared" ref="F18:F23" si="4">((E18 - D18) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G18" s="356">
+      <c r="G18" s="271">
         <f t="shared" si="1"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H18" s="358" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="201" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="201" t="s">
-        <v>20</v>
-      </c>
-      <c r="K18" s="359" t="s">
+      <c r="H18" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="273" t="s">
         <v>86</v>
       </c>
-      <c r="L18" s="194" t="str">
+      <c r="L18" s="193" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B19" s="121">
+        <v>46168</v>
+      </c>
+      <c r="C19" s="354" t="str">
+        <f>IF(ISNUMBER(FIND("?", B19, 1)), "TBD", TEXT(B19, "ddd"))</f>
+        <v>Tue</v>
+      </c>
+      <c r="D19" s="355">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E19" s="355">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F19" s="76">
+        <f>((E19 - D19) * 24)</f>
+        <v>0.49999999999999822</v>
+      </c>
+      <c r="G19" s="271">
+        <f>IF(F19 &gt; 4, (F19 - 1), F19)</f>
+        <v>0.49999999999999822</v>
+      </c>
+      <c r="H19" s="356" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="357" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="67" t="str">
+        <f ca="1">IF(C19 = "TBD", "TBD", IF(B19 = "", "IDK!!", IF(TODAY() &gt; B19, "Passed", IF(TODAY() = B19, "Today!!", "Upcoming"))))</f>
+        <v>Today!!</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23">
+      <c r="B20" s="279">
+        <v>46226</v>
+      </c>
+      <c r="C20" s="217" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="D20" s="157">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E20" s="157">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F20" s="220">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="G20" s="217">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H20" s="280" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="281" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="19" spans="2:23">
-      <c r="B19" s="279">
-        <v>46226</v>
-      </c>
-      <c r="C19" s="217" t="str">
-        <f t="shared" si="0"/>
-        <v>Thu</v>
-      </c>
-      <c r="D19" s="157">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E19" s="157">
+    <row r="21" spans="2:23">
+      <c r="B21" s="337">
+        <v>46227</v>
+      </c>
+      <c r="C21" s="338" t="str">
+        <f>IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
+        <v>Fri</v>
+      </c>
+      <c r="D21" s="339">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E21" s="339">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F19" s="220">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="G19" s="217">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="H19" s="280" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="281" t="s">
+      <c r="F21" s="221">
+        <f>((E21 - D21) * 24)</f>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G21" s="338">
+        <f>IF(F21 &gt; 4, (F21 - 1), F21)</f>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H21" s="340" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="L19" s="42" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="20" spans="2:23">
-      <c r="B20" s="337">
-        <v>46227</v>
-      </c>
-      <c r="C20" s="338" t="str">
-        <f>IF(ISNUMBER(FIND("?", B20, 1)), "TBD", TEXT(B20, "ddd"))</f>
-        <v>Fri</v>
-      </c>
-      <c r="D20" s="339">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E20" s="339">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F20" s="221">
-        <f>((E20 - D20) * 24)</f>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G20" s="338">
-        <f>IF(F20 &gt; 4, (F20 - 1), F20)</f>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H20" s="340" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="341" t="s">
-        <v>46</v>
-      </c>
-      <c r="L20" s="59" t="str">
-        <f ca="1">IF(C20 = "TBD", "TBD", IF(B20 = "", "IDK!!", IF(TODAY() &gt; B20, "Passed", IF(TODAY() = B20, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="21" spans="2:23">
-      <c r="B21" s="140">
-        <v>46232</v>
-      </c>
-      <c r="C21" s="166" t="str">
-        <f>IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
-        <v>Wed</v>
-      </c>
-      <c r="D21" s="158">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E21" s="158">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F21" s="221">
-        <f t="shared" si="4"/>
-        <v>3.4999999999999982</v>
-      </c>
-      <c r="G21" s="166">
-        <f t="shared" si="1"/>
-        <v>3.4999999999999982</v>
-      </c>
-      <c r="H21" s="181" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" s="206" t="s">
-        <v>59</v>
-      </c>
-      <c r="L21" s="329" t="str">
-        <f t="shared" ca="1" si="2"/>
+      <c r="L21" s="59" t="str">
+        <f ca="1">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
     <row r="22" spans="2:23">
       <c r="B22" s="140">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="C22" s="166" t="str">
-        <f t="shared" si="0"/>
-        <v>Thu</v>
+        <f>IF(ISNUMBER(FIND("?", B22, 1)), "TBD", TEXT(B22, "ddd"))</f>
+        <v>Wed</v>
       </c>
       <c r="D22" s="158">
-        <v>0.45833333333333331</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E22" s="158">
         <v>0.66666666666666663</v>
       </c>
       <c r="F22" s="221">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="166">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="181" t="s">
         <v>4</v>
@@ -4541,91 +4541,91 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="23" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B23" s="330">
+    <row r="23" spans="2:23">
+      <c r="B23" s="140">
+        <v>46233</v>
+      </c>
+      <c r="C23" s="166" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="D23" s="158">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E23" s="158">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F23" s="221">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="G23" s="166">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H23" s="181" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="206" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="329" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B24" s="330">
         <v>46234</v>
       </c>
-      <c r="C23" s="331" t="str">
-        <f t="shared" ref="C23:C40" si="5">IF(ISNUMBER(FIND("?", B23, 1)), "TBD", TEXT(B23, "ddd"))</f>
+      <c r="C24" s="331" t="str">
+        <f t="shared" ref="C24:C41" si="5">IF(ISNUMBER(FIND("?", B24, 1)), "TBD", TEXT(B24, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D23" s="332">
+      <c r="D24" s="332">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E23" s="332">
+      <c r="E24" s="332">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F23" s="333">
-        <f t="shared" ref="F23:F37" si="6">((E23 - D23) * 24)</f>
+      <c r="F24" s="333">
+        <f t="shared" ref="F24:F38" si="6">((E24 - D24) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G23" s="331">
-        <f t="shared" ref="G23:G40" si="7">IF(F23 &gt; 4, (F23 - 1), F23)</f>
-        <v>4</v>
-      </c>
-      <c r="H23" s="334" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="335" t="s">
+      <c r="G24" s="331">
+        <f t="shared" ref="G24:G41" si="7">IF(F24 &gt; 4, (F24 - 1), F24)</f>
+        <v>4</v>
+      </c>
+      <c r="H24" s="334" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="335" t="s">
         <v>59</v>
       </c>
-      <c r="L23" s="336" t="str">
-        <f t="shared" ref="L23:L40" ca="1" si="8">IF(C23 = "TBD", "TBD", IF(B23 = "", "IDK!!", IF(TODAY() &gt; B23, "Passed", IF(TODAY() = B23, "Today!!", "Upcoming"))))</f>
+      <c r="L24" s="336" t="str">
+        <f t="shared" ref="L24:L41" ca="1" si="8">IF(C24 = "TBD", "TBD", IF(B24 = "", "IDK!!", IF(TODAY() &gt; B24, "Passed", IF(TODAY() = B24, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="24" spans="2:23">
-      <c r="B24" s="123">
+    <row r="25" spans="2:23">
+      <c r="B25" s="123">
         <v>46240</v>
       </c>
-      <c r="C24" s="245" t="str">
+      <c r="C25" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
-      </c>
-      <c r="D24" s="246">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E24" s="246">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F24" s="258">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="G24" s="245">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="H24" s="247" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K24" s="248" t="s">
-        <v>59</v>
-      </c>
-      <c r="L24" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="25" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B25" s="249">
-        <v>46241</v>
-      </c>
-      <c r="C25" s="245" t="str">
-        <f t="shared" si="5"/>
-        <v>Fri</v>
       </c>
       <c r="D25" s="246">
         <v>0.45833333333333331</v>
@@ -4660,11 +4660,11 @@
     </row>
     <row r="26" spans="2:23" ht="15.75" thickBot="1">
       <c r="B26" s="249">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="C26" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="D26" s="246">
         <v>0.45833333333333331</v>
@@ -4690,7 +4690,7 @@
         <v>20</v>
       </c>
       <c r="K26" s="248" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L26" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -4699,11 +4699,11 @@
     </row>
     <row r="27" spans="2:23" ht="15.75" thickBot="1">
       <c r="B27" s="249">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="C27" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Tue</v>
+        <v>Mon</v>
       </c>
       <c r="D27" s="246">
         <v>0.45833333333333331</v>
@@ -4738,11 +4738,11 @@
     </row>
     <row r="28" spans="2:23" ht="15.75" thickBot="1">
       <c r="B28" s="249">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="C28" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D28" s="246">
         <v>0.45833333333333331</v>
@@ -4776,12 +4776,12 @@
       </c>
     </row>
     <row r="29" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B29" s="250">
-        <v>46247</v>
+      <c r="B29" s="249">
+        <v>46246</v>
       </c>
       <c r="C29" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D29" s="246">
         <v>0.45833333333333331</v>
@@ -4816,11 +4816,11 @@
     </row>
     <row r="30" spans="2:23" ht="15.75" thickBot="1">
       <c r="B30" s="250">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="C30" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="D30" s="246">
         <v>0.45833333333333331</v>
@@ -4855,17 +4855,17 @@
     </row>
     <row r="31" spans="2:23" ht="15.75" thickBot="1">
       <c r="B31" s="250">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="C31" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Fri</v>
       </c>
       <c r="D31" s="246">
-        <v>0.29166666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E31" s="246">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F31" s="258">
         <f t="shared" si="6"/>
@@ -4885,323 +4885,313 @@
         <v>20</v>
       </c>
       <c r="K31" s="248" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="L31" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U31" s="343" t="s">
+    </row>
+    <row r="32" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B32" s="250">
+        <v>46253</v>
+      </c>
+      <c r="C32" s="245" t="str">
+        <f t="shared" si="5"/>
+        <v>Wed</v>
+      </c>
+      <c r="D32" s="246">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E32" s="246">
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="258">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G32" s="245">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H32" s="247" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="248" t="s">
+        <v>71</v>
+      </c>
+      <c r="L32" s="59" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="U32" s="342" t="s">
         <v>74</v>
       </c>
-      <c r="V31" s="98" t="s">
+      <c r="V32" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="W31" s="200" t="s">
+      <c r="W32" s="200" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:23">
-      <c r="B32" s="105">
+    <row r="33" spans="2:23">
+      <c r="B33" s="105">
         <v>46269</v>
       </c>
-      <c r="C32" s="170" t="str">
-        <f t="shared" ref="C32:C34" si="9">IF(ISNUMBER(FIND("?", B32, 1)), "TBD", TEXT(B32, "ddd"))</f>
+      <c r="C33" s="170" t="str">
+        <f t="shared" ref="C33:C35" si="9">IF(ISNUMBER(FIND("?", B33, 1)), "TBD", TEXT(B33, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D32" s="160">
+      <c r="D33" s="160">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E32" s="160">
+      <c r="E33" s="160">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F32" s="224">
-        <f t="shared" ref="F32:F34" si="10">((E32 - D32) * 24)</f>
+      <c r="F33" s="224">
+        <f t="shared" ref="F33:F35" si="10">((E33 - D33) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G32" s="170">
-        <f t="shared" ref="G32:G34" si="11">IF(F32 &gt; 4, (F32 - 1), F32)</f>
-        <v>4</v>
-      </c>
-      <c r="H32" s="185" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="210" t="s">
+      <c r="G33" s="170">
+        <f t="shared" ref="G33:G35" si="11">IF(F33 &gt; 4, (F33 - 1), F33)</f>
+        <v>4</v>
+      </c>
+      <c r="H33" s="185" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="L32" s="42" t="str">
-        <f t="shared" ref="L32:L34" ca="1" si="12">IF(C32 = "TBD", "TBD", IF(B32 = "", "IDK!!", IF(TODAY() &gt; B32, "Passed", IF(TODAY() = B32, "Today!!", "Upcoming"))))</f>
+      <c r="L33" s="42" t="str">
+        <f t="shared" ref="L33:L35" ca="1" si="12">IF(C33 = "TBD", "TBD", IF(B33 = "", "IDK!!", IF(TODAY() &gt; B33, "Passed", IF(TODAY() = B33, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
-      <c r="U32" s="349" t="s">
+      <c r="U33" s="348" t="s">
         <v>76</v>
       </c>
-      <c r="V32" s="350">
+      <c r="V33" s="349">
         <v>2024</v>
       </c>
-      <c r="W32" s="351">
+      <c r="W33" s="350">
         <v>160</v>
       </c>
     </row>
-    <row r="33" spans="2:23">
-      <c r="B33" s="322">
+    <row r="34" spans="2:23">
+      <c r="B34" s="322">
         <v>46275</v>
       </c>
-      <c r="C33" s="323" t="str">
+      <c r="C34" s="323" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D33" s="324">
+      <c r="D34" s="324">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E33" s="324">
+      <c r="E34" s="324">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F33" s="325">
+      <c r="F34" s="325">
         <f t="shared" si="10"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="G33" s="323">
+      <c r="G34" s="323">
         <f t="shared" si="11"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="H33" s="326" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="328" t="s">
+      <c r="H34" s="326" t="s">
+        <v>4</v>
+      </c>
+      <c r="I34" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="328" t="s">
         <v>72</v>
       </c>
-      <c r="L33" s="67" t="str">
+      <c r="L34" s="67" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="U33" s="352" t="s">
+      <c r="U34" s="351" t="s">
         <v>77</v>
       </c>
-      <c r="V33" s="353">
-        <f>V32+1</f>
+      <c r="V34" s="352">
+        <f>V33+1</f>
         <v>2025</v>
       </c>
-      <c r="W33" s="354">
+      <c r="W34" s="353">
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B34" s="316">
+    <row r="35" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B35" s="316">
         <v>46275</v>
       </c>
-      <c r="C34" s="317" t="str">
+      <c r="C35" s="317" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D34" s="318">
+      <c r="D35" s="318">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E34" s="318">
+      <c r="E35" s="318">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F34" s="319">
+      <c r="F35" s="319">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="G34" s="317">
+      <c r="G35" s="317">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="H34" s="320" t="s">
+      <c r="H35" s="320" t="s">
         <v>10</v>
       </c>
-      <c r="I34" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" s="321" t="s">
+      <c r="I35" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="321" t="s">
         <v>72</v>
       </c>
-      <c r="L34" s="60" t="str">
+      <c r="L35" s="60" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="U34" s="344" t="s">
+      <c r="U35" s="343" t="s">
         <v>78</v>
       </c>
-      <c r="V34" s="70">
-        <f>V33+1</f>
+      <c r="V35" s="70">
+        <f>V34+1</f>
         <v>2026</v>
       </c>
-      <c r="W34" s="345">
+      <c r="W35" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B35" s="124">
+    <row r="36" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B36" s="124">
         <v>46353</v>
       </c>
-      <c r="C35" s="173" t="str">
+      <c r="C36" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D35" s="155">
+      <c r="D36" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E35" s="155">
+      <c r="E36" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F35" s="226">
+      <c r="F36" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G35" s="173">
+      <c r="G36" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H35" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="269" t="s">
+      <c r="H36" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="L35" s="192" t="str">
+      <c r="L36" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U35" s="344" t="s">
+      <c r="U36" s="343" t="s">
         <v>79</v>
       </c>
-      <c r="V35" s="70">
-        <f t="shared" ref="V35:V41" si="13">V34+1</f>
+      <c r="V36" s="70">
+        <f t="shared" ref="V36:V42" si="13">V35+1</f>
         <v>2027</v>
       </c>
-      <c r="W35" s="345">
+      <c r="W36" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="2:23">
-      <c r="B36" s="112">
+    <row r="37" spans="2:23">
+      <c r="B37" s="112">
         <v>46380</v>
       </c>
-      <c r="C36" s="264" t="str">
+      <c r="C37" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D36" s="262">
+      <c r="D37" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E36" s="262">
+      <c r="E37" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F36" s="263">
+      <c r="F37" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G36" s="264">
+      <c r="G37" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H36" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I36" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="266" t="s">
+      <c r="H37" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I37" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="L36" s="42" t="str">
+      <c r="L37" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U36" s="344" t="s">
+      <c r="U37" s="343" t="s">
         <v>80</v>
       </c>
-      <c r="V36" s="70">
+      <c r="V37" s="70">
         <f t="shared" si="13"/>
         <v>2028</v>
       </c>
-      <c r="W36" s="345">
+      <c r="W37" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="37" spans="2:23">
-      <c r="B37" s="120">
+    <row r="38" spans="2:23">
+      <c r="B38" s="120">
         <v>46384</v>
       </c>
-      <c r="C37" s="274" t="str">
+      <c r="C38" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D37" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E37" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F37" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G37" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H37" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I37" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="L37" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="U37" s="344" t="s">
-        <v>81</v>
-      </c>
-      <c r="V37" s="70">
-        <f t="shared" si="13"/>
-        <v>2029</v>
-      </c>
-      <c r="W37" s="345">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="38" spans="2:23">
-      <c r="B38" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C38" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
       <c r="D38" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -5209,47 +5199,47 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F38" s="276">
-        <f t="shared" ref="F38:F40" si="14">((E38 - D38) * 24)</f>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G38" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H38" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I38" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="273" t="s">
+      <c r="H38" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="L38" s="193" t="str">
+      <c r="L38" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U38" s="344" t="s">
-        <v>82</v>
+      <c r="U38" s="343" t="s">
+        <v>81</v>
       </c>
       <c r="V38" s="70">
         <f t="shared" si="13"/>
-        <v>2030</v>
-      </c>
-      <c r="W38" s="345">
+        <v>2029</v>
+      </c>
+      <c r="W38" s="344">
         <v>176</v>
       </c>
     </row>
     <row r="39" spans="2:23">
       <c r="B39" s="270">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C39" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D39" s="275">
         <v>0.29166666666666669</v>
@@ -5258,7 +5248,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F39" s="276">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="F39:F41" si="14">((E39 - D39) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G39" s="274">
@@ -5281,24 +5271,24 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U39" s="344" t="s">
-        <v>83</v>
+      <c r="U39" s="343" t="s">
+        <v>82</v>
       </c>
       <c r="V39" s="70">
         <f t="shared" si="13"/>
-        <v>2031</v>
-      </c>
-      <c r="W39" s="345">
+        <v>2030</v>
+      </c>
+      <c r="W39" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B40" s="113">
-        <v>46387</v>
+    <row r="40" spans="2:23">
+      <c r="B40" s="270">
+        <v>46386</v>
       </c>
       <c r="C40" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D40" s="275">
         <v>0.29166666666666669</v>
@@ -5314,132 +5304,181 @@
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H40" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="268" t="s">
+      <c r="H40" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="273" t="s">
         <v>60</v>
       </c>
       <c r="L40" s="193" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U40" s="344" t="s">
-        <v>84</v>
+      <c r="U40" s="343" t="s">
+        <v>83</v>
       </c>
       <c r="V40" s="70">
         <f t="shared" si="13"/>
+        <v>2031</v>
+      </c>
+      <c r="W40" s="344">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B41" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C41" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D41" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E41" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="276">
+        <f t="shared" si="14"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G41" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H41" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="L41" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="U41" s="343" t="s">
+        <v>84</v>
+      </c>
+      <c r="V41" s="70">
+        <f t="shared" si="13"/>
         <v>2032</v>
       </c>
-      <c r="W40" s="345">
+      <c r="W41" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B41" s="102"/>
-      <c r="C41" s="165" t="str">
-        <f t="shared" ref="C41:C42" si="15">IF(ISNUMBER(FIND("?", B41, 1)), "TBD", TEXT(B41, "ddd"))</f>
+    <row r="42" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B42" s="102"/>
+      <c r="C42" s="165" t="str">
+        <f t="shared" ref="C42:C43" si="15">IF(ISNUMBER(FIND("?", B42, 1)), "TBD", TEXT(B42, "ddd"))</f>
         <v>Sat</v>
       </c>
-      <c r="D41" s="157"/>
-      <c r="E41" s="157"/>
-      <c r="F41" s="220">
-        <f t="shared" ref="F41:F42" si="16">((E41 - D41) * 24)</f>
+      <c r="D42" s="157"/>
+      <c r="E42" s="157"/>
+      <c r="F42" s="220">
+        <f t="shared" ref="F42:F43" si="16">((E42 - D42) * 24)</f>
         <v>0</v>
       </c>
-      <c r="G41" s="217">
-        <f t="shared" ref="G41:G42" si="17">IF(F41 &gt; 4, (F41 - 1), F41)</f>
+      <c r="G42" s="217">
+        <f t="shared" ref="G42:G43" si="17">IF(F42 &gt; 4, (F42 - 1), F42)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="180"/>
-      <c r="I41" s="197" t="s">
+      <c r="H42" s="180"/>
+      <c r="I42" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="J41" s="197" t="s">
+      <c r="J42" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="K41" s="205"/>
-      <c r="L41" s="252" t="str">
-        <f t="shared" ref="L41:L42" ca="1" si="18">IF(C41 = "TBD", "TBD", IF(B41 = "", "IDK!!", IF(TODAY() &gt; B41, "Passed", IF(TODAY() = B41, "Today!!", "Upcoming"))))</f>
+      <c r="K42" s="205"/>
+      <c r="L42" s="252" t="str">
+        <f t="shared" ref="L42:L43" ca="1" si="18">IF(C42 = "TBD", "TBD", IF(B42 = "", "IDK!!", IF(TODAY() &gt; B42, "Passed", IF(TODAY() = B42, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
-      <c r="U41" s="346" t="s">
+      <c r="U42" s="345" t="s">
         <v>85</v>
       </c>
-      <c r="V41" s="347">
+      <c r="V42" s="346">
         <f t="shared" si="13"/>
         <v>2033</v>
       </c>
-      <c r="W41" s="348">
+      <c r="W42" s="347">
         <f>192 + 10</f>
         <v>202</v>
       </c>
     </row>
-    <row r="42" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B42" s="259"/>
-      <c r="C42" s="253" t="str">
+    <row r="43" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B43" s="259"/>
+      <c r="C43" s="253" t="str">
         <f t="shared" si="15"/>
         <v>Sat</v>
       </c>
-      <c r="D42" s="260"/>
-      <c r="E42" s="260"/>
-      <c r="F42" s="261">
+      <c r="D43" s="260"/>
+      <c r="E43" s="260"/>
+      <c r="F43" s="261">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="253">
+      <c r="G43" s="253">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H42" s="254"/>
-      <c r="I42" s="202" t="s">
+      <c r="H43" s="254"/>
+      <c r="I43" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="J42" s="202" t="s">
+      <c r="J43" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="K42" s="255"/>
-      <c r="L42" s="251" t="str">
+      <c r="K43" s="255"/>
+      <c r="L43" s="251" t="str">
         <f t="shared" ca="1" si="18"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="43" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B43" s="86" t="s">
+    <row r="44" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B44" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="303"/>
-      <c r="D43" s="304"/>
-      <c r="E43" s="305"/>
-      <c r="F43" s="228">
-        <f>SUM(F14:F42)</f>
+      <c r="C44" s="303"/>
+      <c r="D44" s="304"/>
+      <c r="E44" s="305"/>
+      <c r="F44" s="228">
+        <f>SUM(F14:F43)</f>
         <v>163.5</v>
       </c>
-      <c r="G43" s="256">
-        <f>SUM(G14:G42)</f>
+      <c r="G44" s="256">
+        <f>SUM(G14:G43)</f>
         <v>140.5</v>
       </c>
-      <c r="H43" s="301"/>
-      <c r="I43" s="302"/>
-      <c r="J43" s="302"/>
-      <c r="K43" s="302"/>
-      <c r="L43" s="302"/>
+      <c r="H44" s="301"/>
+      <c r="I44" s="302"/>
+      <c r="J44" s="302"/>
+      <c r="K44" s="302"/>
+      <c r="L44" s="302"/>
     </row>
   </sheetData>
-  <autoFilter ref="B13:K43" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <autoFilter ref="B13:K44" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B14:L42">
+  <conditionalFormatting sqref="B14:L43">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F42 L14:L42">
+  <conditionalFormatting sqref="C14:F43 L14:L43">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -5454,7 +5493,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J42">
+  <conditionalFormatting sqref="I14:J43">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64221748-09CB-406D-9C66-F92EAFE4D9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5C2DAC-7F0A-4925-8B42-BC13FBB1363F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="1620" windowWidth="32970" windowHeight="18735" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="3060" yWindow="1260" windowWidth="32970" windowHeight="18735" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="L19" s="67" t="str">
         <f ca="1">IF(C19 = "TBD", "TBD", IF(B19 = "", "IDK!!", IF(TODAY() &gt; B19, "Passed", IF(TODAY() = B19, "Today!!", "Upcoming"))))</f>
-        <v>Today!!</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="20" spans="2:23">

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,23 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5C2DAC-7F0A-4925-8B42-BC13FBB1363F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C292985E-4C33-4937-B096-05A2D31EE800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="1260" windowWidth="32970" windowHeight="18735" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="4485" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="7" r:id="rId1"/>
-    <sheet name="2025_Original" sheetId="5" state="hidden" r:id="rId2"/>
-    <sheet name="2025" sheetId="6" r:id="rId3"/>
-    <sheet name="2024" sheetId="1" r:id="rId4"/>
-    <sheet name="Template" sheetId="2" r:id="rId5"/>
+    <sheet name="2027" sheetId="8" r:id="rId1"/>
+    <sheet name="2026" sheetId="7" r:id="rId2"/>
+    <sheet name="2025_Original" sheetId="5" state="hidden" r:id="rId3"/>
+    <sheet name="2025" sheetId="6" r:id="rId4"/>
+    <sheet name="2024" sheetId="1" r:id="rId5"/>
+    <sheet name="Template" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2024'!$B$12:$G$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025'!$B$13:$K$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$13:$L$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Template!$B$13:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024'!$B$12:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025'!$B$13:$K$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$L$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2027'!$B$13:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="90">
   <si>
     <t>Total</t>
   </si>
@@ -346,6 +348,9 @@
   <si>
     <t>Garage door replacement quote</t>
   </si>
+  <si>
+    <t>KY / Ark</t>
+  </si>
 </sst>
 </file>
 
@@ -1470,7 +1475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="359">
+  <cellXfs count="364">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2504,11 +2509,26 @@
     <xf numFmtId="18" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="4" borderId="45" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="27">
     <dxf>
       <font>
         <b/>
@@ -2723,6 +2743,65 @@
         <color theme="0" tint="-0.34998626667073579"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2737,6 +2816,193 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>104213</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>33058</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>557336</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>81149</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E248C3E9-F834-4D64-929C-81E8E2BE83A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15296588" y="233083"/>
+          <a:ext cx="2891523" cy="7473669"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>67235</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>185237</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>190161</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D7895A9-0321-4EFE-9908-89A3382607E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18307610" y="190499"/>
+          <a:ext cx="6471177" cy="1590337"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>582704</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>558202</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>129358</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C659B168-469E-49AB-8991-18598CE095FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18213479" y="2437279"/>
+          <a:ext cx="5109473" cy="3611587"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>89648</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>178174</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>5603</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9823C333-C0F8-45D6-BD73-FF613F4B6C91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17720423" y="9378203"/>
+          <a:ext cx="6441701" cy="3714750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2923,7 +3189,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3110,7 +3376,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3297,7 +3563,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3484,7 +3750,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3967,6 +4233,492 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2671213-B148-403C-9F48-0EB30902282E}">
+  <dimension ref="B1:W20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" customWidth="1"/>
+    <col min="21" max="21" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:12" ht="18" thickBot="1">
+      <c r="B2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3">
+        <f ca="1">160+C4</f>
+        <v>204</v>
+      </c>
+      <c r="D3" s="3">
+        <f ca="1">C3-E3</f>
+        <v>56</v>
+      </c>
+      <c r="E3" s="1">
+        <f ca="1">C3 - C6 - SUMIF(H14:H19, "PTO", G14:G19)</f>
+        <v>148</v>
+      </c>
+      <c r="K3" s="56" t="str" cm="1">
+        <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename", A2),LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) + 1</f>
+        <v>PTO Reset: 02/12/2028</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" cm="1">
+        <f t="array" aca="1" ref="C4" ca="1">IF((RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) &lt;&gt; "Template", (INDIRECT("'" &amp; (RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) - 1 &amp; "'!E3")) + (INDIRECT("'" &amp; (RIGHT(CELL("filename", A3), LEN(CELL("filename", A3)) - SEARCH("]", CELL("filename",A3)))) - 1 &amp; "'!E6")), 0)</f>
+        <v>44</v>
+      </c>
+      <c r="D4" s="74"/>
+      <c r="E4" s="75"/>
+    </row>
+    <row r="5" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7">
+        <f ca="1">C3/8</f>
+        <v>25.5</v>
+      </c>
+      <c r="D5" s="7">
+        <f ca="1">D3/8</f>
+        <v>7</v>
+      </c>
+      <c r="E5" s="8">
+        <f ca="1">E3/8</f>
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="10">
+        <v>40</v>
+      </c>
+      <c r="D6" s="10">
+        <f>C6-E6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <f>C6 - SUMIF(H14:H19, "Sick", G14:G19)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="13">
+        <f>C6/8</f>
+        <v>5</v>
+      </c>
+      <c r="D7" s="13">
+        <f>D6/8</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
+        <f>E6/8</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2">
+        <f>C8-E8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <f>C8 - SUMIF(H14:H19, "Be You", G14:G19)</f>
+        <v>16</v>
+      </c>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7">
+        <f>C8/8</f>
+        <v>2</v>
+      </c>
+      <c r="D9" s="7">
+        <f>D8/8</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <f>E8/8</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="127" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="128">
+        <v>4</v>
+      </c>
+      <c r="D10" s="128">
+        <f>C10-E10</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="129">
+        <f>C10 - SUMIF(H14:H19, "Volunteer", G14:G19)</f>
+        <v>4</v>
+      </c>
+      <c r="K10" s="36"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B11" s="130" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="131">
+        <f>C10/8</f>
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="131">
+        <f>D10/8</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="132">
+        <f>E10/8</f>
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="36"/>
+    </row>
+    <row r="12" spans="2:12" ht="15.75" thickBot="1"/>
+    <row r="13" spans="2:12" ht="35.25" thickBot="1">
+      <c r="B13" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="163" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="146" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="146" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="218" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="163" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="178" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="195" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="195" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="203" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="147" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="122"/>
+      <c r="C14" s="240" t="str">
+        <f t="shared" ref="C14:C19" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
+        <v>Sat</v>
+      </c>
+      <c r="D14" s="241"/>
+      <c r="E14" s="241"/>
+      <c r="F14" s="257">
+        <f>((E14 - D14) * 24)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="240">
+        <f t="shared" ref="G14:G19" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="242"/>
+      <c r="I14" s="196" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="196" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="243"/>
+      <c r="L14" s="42" t="str">
+        <f t="shared" ref="L14:L19" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
+        <v>IDK!!</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B15" s="306"/>
+      <c r="C15" s="307" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="D15" s="308"/>
+      <c r="E15" s="308"/>
+      <c r="F15" s="309">
+        <f>((E15 - D15) * 24)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="307">
+        <f>IF(F15 &gt; 4, (F15 - 1), F15)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="310"/>
+      <c r="I15" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" s="311"/>
+      <c r="L15" s="60" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>IDK!!</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="282">
+        <v>46717</v>
+      </c>
+      <c r="C16" s="359" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="D16" s="360">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E16" s="360">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F16" s="361">
+        <f>((E16 - D16) * 24)</f>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G16" s="359">
+        <f>IF(F16 &gt; 4, (F16 - 1), F16)</f>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H16" s="362" t="s">
+        <v>4</v>
+      </c>
+      <c r="I16" s="202" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="327" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="288" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" s="251" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B17" s="104">
+        <v>46720</v>
+      </c>
+      <c r="C17" s="312" t="str">
+        <f>IF(ISNUMBER(FIND("?", B17, 1)), "TBD", TEXT(B17, "ddd"))</f>
+        <v>Mon</v>
+      </c>
+      <c r="D17" s="313">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E17" s="313">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F17" s="361">
+        <f>((E17 - D17) * 24)</f>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G17" s="312">
+        <f>IF(F17 &gt; 4, (F17 - 1), F17)</f>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H17" s="315" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="363" t="s">
+        <v>89</v>
+      </c>
+      <c r="L17" s="60" t="str">
+        <f ca="1">IF(C17 = "TBD", "TBD", IF(B17 = "", "IDK!!", IF(TODAY() &gt; B17, "Passed", IF(TODAY() = B17, "Today!!", "Upcoming"))))</f>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="18" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B18" s="102"/>
+      <c r="C18" s="165" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="220">
+        <f t="shared" ref="F18:F19" si="3">((E18 - D18) * 24)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="217">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="180"/>
+      <c r="I18" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="K18" s="205"/>
+      <c r="L18" s="252" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>IDK!!</v>
+      </c>
+      <c r="U18" s="345" t="s">
+        <v>85</v>
+      </c>
+      <c r="V18" s="346" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W18" s="347">
+        <f>192 + 10</f>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B19" s="259"/>
+      <c r="C19" s="253" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="D19" s="260"/>
+      <c r="E19" s="260"/>
+      <c r="F19" s="261">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="253">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="254"/>
+      <c r="I19" s="202" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="202" t="s">
+        <v>66</v>
+      </c>
+      <c r="K19" s="255"/>
+      <c r="L19" s="251" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>IDK!!</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B20" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="303"/>
+      <c r="D20" s="304"/>
+      <c r="E20" s="305"/>
+      <c r="F20" s="228">
+        <f>SUM(F14:F19)</f>
+        <v>17.999999999999996</v>
+      </c>
+      <c r="G20" s="256">
+        <f>SUM(G14:G19)</f>
+        <v>15.999999999999996</v>
+      </c>
+      <c r="H20" s="301"/>
+      <c r="I20" s="302"/>
+      <c r="J20" s="302"/>
+      <c r="K20" s="302"/>
+      <c r="L20" s="302"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B13:K20" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <conditionalFormatting sqref="B14:L19">
+    <cfRule type="expression" dxfId="26" priority="2">
+      <formula>$L14="Passed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L14:L19 C14:F19">
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
+      <formula>"TBD"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3 E5">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3 E5:E11">
+    <cfRule type="cellIs" dxfId="23" priority="6" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I14:J19">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
   <dimension ref="B1:W44"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5507,7 +6259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD57EB3B-515A-4E94-895F-88D262D477C2}">
   <dimension ref="B1:H44"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6502,7 +7254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D12B9BF-3416-48A7-87E4-2977D80A472D}">
   <dimension ref="B1:K48"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7994,7 +8746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25002DC1-579B-4118-A464-8DA972BBC903}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:G43"/>
@@ -8864,7 +9616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8D74E6-E2F4-497A-863D-7746D04C8BB1}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:G22"/>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C292985E-4C33-4937-B096-05A2D31EE800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDABBB5-8DD6-42BB-84A5-5DEC991A2E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="3900" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$L$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$L$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2027'!$B$13:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="91">
   <si>
     <t>Total</t>
   </si>
@@ -351,6 +351,9 @@
   <si>
     <t>KY / Ark</t>
   </si>
+  <si>
+    <t>Barn garage door operator replacement</t>
+  </si>
 </sst>
 </file>
 
@@ -1475,7 +1478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="367">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2494,34 +2497,43 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="18" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="4" borderId="45" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="4" borderId="45" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3103,7 +3115,7 @@
       <xdr:col>25</xdr:col>
       <xdr:colOff>558202</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>95741</xdr:rowOff>
+      <xdr:rowOff>106947</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3140,13 +3152,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>178174</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4275,7 +4287,7 @@
       </c>
       <c r="C3" s="3">
         <f ca="1">160+C4</f>
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
@@ -4283,7 +4295,7 @@
       </c>
       <c r="E3" s="1">
         <f ca="1">C3 - C6 - SUMIF(H14:H19, "PTO", G14:G19)</f>
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename", A2),LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) + 1</f>
@@ -4296,7 +4308,7 @@
       </c>
       <c r="C4" s="2" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">IF((RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) &lt;&gt; "Template", (INDIRECT("'" &amp; (RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) - 1 &amp; "'!E3")) + (INDIRECT("'" &amp; (RIGHT(CELL("filename", A3), LEN(CELL("filename", A3)) - SEARCH("]", CELL("filename",A3)))) - 1 &amp; "'!E6")), 0)</f>
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
@@ -4307,7 +4319,7 @@
       </c>
       <c r="C5" s="7">
         <f ca="1">C3/8</f>
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
@@ -4315,7 +4327,7 @@
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -4518,25 +4530,25 @@
       <c r="B16" s="282">
         <v>46717</v>
       </c>
-      <c r="C16" s="359" t="str">
+      <c r="C16" s="355" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D16" s="360">
+      <c r="D16" s="356">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E16" s="360">
+      <c r="E16" s="356">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F16" s="361">
+      <c r="F16" s="357">
         <f>((E16 - D16) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G16" s="359">
+      <c r="G16" s="355">
         <f>IF(F16 &gt; 4, (F16 - 1), F16)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H16" s="362" t="s">
+      <c r="H16" s="358" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="202" t="s">
@@ -4567,7 +4579,7 @@
       <c r="E17" s="313">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F17" s="361">
+      <c r="F17" s="357">
         <f>((E17 - D17) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
@@ -4584,7 +4596,7 @@
       <c r="J17" s="244" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="363" t="s">
+      <c r="K17" s="359" t="s">
         <v>89</v>
       </c>
       <c r="L17" s="60" t="str">
@@ -4689,7 +4701,7 @@
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L14:L19 C14:F19">
+  <conditionalFormatting sqref="C14:F19 L14:L19">
     <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -4720,7 +4732,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:W44"/>
+  <dimension ref="B1:W46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -4765,11 +4777,11 @@
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
-        <v>164.5</v>
+        <v>168.5</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H43, "PTO", G14:G43)</f>
-        <v>4</v>
+        <f ca="1">C3 - C6 - SUMIF(H14:H45, "PTO", G14:G45)</f>
+        <v>0</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename",A2),LEN(CELL("filename",A2))-SEARCH("]",CELL("filename",A2)))) + 1</f>
@@ -4797,11 +4809,11 @@
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
-        <v>20.5625</v>
+        <v>21.0625</v>
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -4813,11 +4825,11 @@
       </c>
       <c r="D6" s="10">
         <f>C6-E6</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H43, "Sick", G14:G43)</f>
-        <v>40</v>
+        <f>C6 - SUMIF(H14:H45, "Sick", G14:G45)</f>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15.75" thickBot="1">
@@ -4830,11 +4842,11 @@
       </c>
       <c r="D7" s="13">
         <f>D6/8</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="14">
         <f>E6/8</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -4849,7 +4861,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H43, "Be You", G14:G43)</f>
+        <f>C8 - SUMIF(H14:H45, "Be You", G14:G45)</f>
         <v>0</v>
       </c>
       <c r="K8" s="51"/>
@@ -4883,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H43, "Volunteer", G14:G43)</f>
+        <f>C10 - SUMIF(H14:H45, "Volunteer", G14:G45)</f>
         <v>4</v>
       </c>
       <c r="K10" s="36"/>
@@ -4947,7 +4959,7 @@
         <v>46059</v>
       </c>
       <c r="C14" s="240" t="str">
-        <f t="shared" ref="C14:C23" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
+        <f t="shared" ref="C14:C25" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D14" s="241">
@@ -4961,7 +4973,7 @@
         <v>5</v>
       </c>
       <c r="G14" s="240">
-        <f t="shared" ref="G14:G23" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
+        <f t="shared" ref="G14:G25" si="1">IF(F14 &gt; 4, (F14 - 1), F14)</f>
         <v>4</v>
       </c>
       <c r="H14" s="242" t="s">
@@ -4977,7 +4989,7 @@
         <v>67</v>
       </c>
       <c r="L14" s="42" t="str">
-        <f t="shared" ref="L14:L23" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="L14:L25" ca="1" si="2">IF(C14 = "TBD", "TBD", IF(B14 = "", "IDK!!", IF(TODAY() &gt; B14, "Passed", IF(TODAY() = B14, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
@@ -5059,7 +5071,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:23">
+    <row r="17" spans="2:12">
       <c r="B17" s="289">
         <v>46150</v>
       </c>
@@ -5098,7 +5110,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:23">
+    <row r="18" spans="2:12">
       <c r="B18" s="270">
         <v>46164</v>
       </c>
@@ -5106,14 +5118,14 @@
         <f>IF(ISNUMBER(FIND("?", B18, 1)), "TBD", TEXT(B18, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D18" s="358">
+      <c r="D18" s="354">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E18" s="358">
+      <c r="E18" s="354">
         <v>0.66666666666666663</v>
       </c>
       <c r="F18" s="76">
-        <f t="shared" ref="F18:F23" si="4">((E18 - D18) * 24)</f>
+        <f t="shared" ref="F18:F25" si="4">((E18 - D18) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G18" s="271">
@@ -5137,325 +5149,325 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="19" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B19" s="121">
+    <row r="19" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B19" s="113">
         <v>46168</v>
       </c>
-      <c r="C19" s="354" t="str">
+      <c r="C19" s="360" t="str">
         <f>IF(ISNUMBER(FIND("?", B19, 1)), "TBD", TEXT(B19, "ddd"))</f>
         <v>Tue</v>
       </c>
-      <c r="D19" s="355">
+      <c r="D19" s="361">
         <v>0.64583333333333337</v>
       </c>
-      <c r="E19" s="355">
+      <c r="E19" s="361">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F19" s="76">
+      <c r="F19" s="33">
         <f>((E19 - D19) * 24)</f>
         <v>0.49999999999999822</v>
       </c>
-      <c r="G19" s="271">
+      <c r="G19" s="360">
         <f>IF(F19 &gt; 4, (F19 - 1), F19)</f>
         <v>0.49999999999999822</v>
       </c>
-      <c r="H19" s="356" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="357" t="s">
+      <c r="H19" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="268" t="s">
         <v>88</v>
       </c>
-      <c r="L19" s="67" t="str">
+      <c r="L19" s="60" t="str">
         <f ca="1">IF(C19 = "TBD", "TBD", IF(B19 = "", "IDK!!", IF(TODAY() &gt; B19, "Passed", IF(TODAY() = B19, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:23">
-      <c r="B20" s="279">
+    <row r="20" spans="2:12">
+      <c r="B20" s="103">
+        <v>46196</v>
+      </c>
+      <c r="C20" s="362" t="str">
+        <f>IF(ISNUMBER(FIND("?", B20, 1)), "TBD", TEXT(B20, "ddd"))</f>
+        <v>Tue</v>
+      </c>
+      <c r="D20" s="363">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E20" s="363">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F20" s="364">
+        <f>((E20 - D20) * 24)</f>
+        <v>3.9999999999999991</v>
+      </c>
+      <c r="G20" s="362">
+        <f>IF(F20 &gt; 4, (F20 - 1), F20)</f>
+        <v>3.9999999999999991</v>
+      </c>
+      <c r="H20" s="365" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="196" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="366" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" s="42" t="str">
+        <f ca="1">IF(C20 = "TBD", "TBD", IF(B20 = "", "IDK!!", IF(TODAY() &gt; B20, "Passed", IF(TODAY() = B20, "Today!!", "Upcoming"))))</f>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B21" s="282">
+        <v>46196</v>
+      </c>
+      <c r="C21" s="283" t="str">
+        <f>IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
+        <v>Tue</v>
+      </c>
+      <c r="D21" s="284">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="284">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F21" s="232">
+        <f>((E21 - D21) * 24)</f>
+        <v>3.9999999999999991</v>
+      </c>
+      <c r="G21" s="230">
+        <f>IF(F21 &gt; 4, (F21 - 1), F21)</f>
+        <v>3.9999999999999991</v>
+      </c>
+      <c r="H21" s="286" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="327" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21" s="288" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" s="67" t="str">
+        <f ca="1">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="279">
         <v>46226</v>
       </c>
-      <c r="C20" s="217" t="str">
+      <c r="C22" s="217" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="D20" s="157">
+      <c r="D22" s="157">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E20" s="157">
+      <c r="E22" s="157">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F20" s="220">
+      <c r="F22" s="220">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G20" s="217">
+      <c r="G22" s="217">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H20" s="280" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="281" t="s">
+      <c r="H22" s="280" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="281" t="s">
         <v>46</v>
       </c>
-      <c r="L20" s="42" t="str">
+      <c r="L22" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="21" spans="2:23">
-      <c r="B21" s="337">
+    <row r="23" spans="2:12">
+      <c r="B23" s="337">
         <v>46227</v>
       </c>
-      <c r="C21" s="338" t="str">
-        <f>IF(ISNUMBER(FIND("?", B21, 1)), "TBD", TEXT(B21, "ddd"))</f>
+      <c r="C23" s="338" t="str">
+        <f>IF(ISNUMBER(FIND("?", B23, 1)), "TBD", TEXT(B23, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D21" s="339">
+      <c r="D23" s="339">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E21" s="339">
+      <c r="E23" s="339">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F21" s="221">
-        <f>((E21 - D21) * 24)</f>
+      <c r="F23" s="221">
+        <f>((E23 - D23) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G21" s="338">
-        <f>IF(F21 &gt; 4, (F21 - 1), F21)</f>
+      <c r="G23" s="338">
+        <f>IF(F23 &gt; 4, (F23 - 1), F23)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H21" s="340" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" s="341" t="s">
+      <c r="H23" s="340" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="L21" s="59" t="str">
-        <f ca="1">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
+      <c r="L23" s="59" t="str">
+        <f ca="1">IF(C23 = "TBD", "TBD", IF(B23 = "", "IDK!!", IF(TODAY() &gt; B23, "Passed", IF(TODAY() = B23, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="22" spans="2:23">
-      <c r="B22" s="140">
+    <row r="24" spans="2:12">
+      <c r="B24" s="140">
         <v>46232</v>
       </c>
-      <c r="C22" s="166" t="str">
-        <f>IF(ISNUMBER(FIND("?", B22, 1)), "TBD", TEXT(B22, "ddd"))</f>
+      <c r="C24" s="166" t="str">
+        <f>IF(ISNUMBER(FIND("?", B24, 1)), "TBD", TEXT(B24, "ddd"))</f>
         <v>Wed</v>
       </c>
-      <c r="D22" s="158">
+      <c r="D24" s="158">
         <v>0.54166666666666663</v>
       </c>
-      <c r="E22" s="158">
+      <c r="E24" s="158">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F22" s="221">
+      <c r="F24" s="221">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="G22" s="166">
+      <c r="G24" s="166">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="H22" s="181" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="206" t="s">
+      <c r="H24" s="181" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="L22" s="329" t="str">
+      <c r="L24" s="329" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="23" spans="2:23">
-      <c r="B23" s="140">
+    <row r="25" spans="2:12">
+      <c r="B25" s="140">
         <v>46233</v>
       </c>
-      <c r="C23" s="166" t="str">
+      <c r="C25" s="166" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="D23" s="158">
+      <c r="D25" s="158">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E23" s="158">
+      <c r="E25" s="158">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F23" s="221">
+      <c r="F25" s="221">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G23" s="166">
+      <c r="G25" s="166">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H23" s="181" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="206" t="s">
+      <c r="H25" s="181" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="L23" s="329" t="str">
+      <c r="L25" s="329" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="24" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B24" s="330">
+    <row r="26" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B26" s="330">
         <v>46234</v>
       </c>
-      <c r="C24" s="331" t="str">
-        <f t="shared" ref="C24:C41" si="5">IF(ISNUMBER(FIND("?", B24, 1)), "TBD", TEXT(B24, "ddd"))</f>
+      <c r="C26" s="331" t="str">
+        <f t="shared" ref="C26:C43" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D24" s="332">
+      <c r="D26" s="332">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E24" s="332">
+      <c r="E26" s="332">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F24" s="333">
-        <f t="shared" ref="F24:F38" si="6">((E24 - D24) * 24)</f>
+      <c r="F26" s="333">
+        <f t="shared" ref="F26:F40" si="6">((E26 - D26) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G24" s="331">
-        <f t="shared" ref="G24:G41" si="7">IF(F24 &gt; 4, (F24 - 1), F24)</f>
-        <v>4</v>
-      </c>
-      <c r="H24" s="334" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K24" s="335" t="s">
+      <c r="G26" s="331">
+        <f t="shared" ref="G26:G43" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
+        <v>4</v>
+      </c>
+      <c r="H26" s="334" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="335" t="s">
         <v>59</v>
       </c>
-      <c r="L24" s="336" t="str">
-        <f t="shared" ref="L24:L41" ca="1" si="8">IF(C24 = "TBD", "TBD", IF(B24 = "", "IDK!!", IF(TODAY() &gt; B24, "Passed", IF(TODAY() = B24, "Today!!", "Upcoming"))))</f>
+      <c r="L26" s="336" t="str">
+        <f t="shared" ref="L26:L43" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="25" spans="2:23">
-      <c r="B25" s="123">
+    <row r="27" spans="2:12">
+      <c r="B27" s="123">
         <v>46240</v>
       </c>
-      <c r="C25" s="245" t="str">
+      <c r="C27" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
-      </c>
-      <c r="D25" s="246">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E25" s="246">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F25" s="258">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="G25" s="245">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="H25" s="247" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="248" t="s">
-        <v>59</v>
-      </c>
-      <c r="L25" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="26" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B26" s="249">
-        <v>46241</v>
-      </c>
-      <c r="C26" s="245" t="str">
-        <f t="shared" si="5"/>
-        <v>Fri</v>
-      </c>
-      <c r="D26" s="246">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E26" s="246">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F26" s="258">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="G26" s="245">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="H26" s="247" t="s">
-        <v>4</v>
-      </c>
-      <c r="I26" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" s="248" t="s">
-        <v>59</v>
-      </c>
-      <c r="L26" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="27" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B27" s="249">
-        <v>46244</v>
-      </c>
-      <c r="C27" s="245" t="str">
-        <f t="shared" si="5"/>
-        <v>Mon</v>
       </c>
       <c r="D27" s="246">
         <v>0.45833333333333331</v>
@@ -5481,20 +5493,20 @@
         <v>20</v>
       </c>
       <c r="K27" s="248" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L27" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="28" spans="2:23" ht="15.75" thickBot="1">
+    <row r="28" spans="2:12" ht="15.75" thickBot="1">
       <c r="B28" s="249">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="C28" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Tue</v>
+        <v>Fri</v>
       </c>
       <c r="D28" s="246">
         <v>0.45833333333333331</v>
@@ -5520,20 +5532,20 @@
         <v>20</v>
       </c>
       <c r="K28" s="248" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L28" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="29" spans="2:23" ht="15.75" thickBot="1">
+    <row r="29" spans="2:12" ht="15.75" thickBot="1">
       <c r="B29" s="249">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="C29" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Mon</v>
       </c>
       <c r="D29" s="246">
         <v>0.45833333333333331</v>
@@ -5566,13 +5578,13 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="30" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B30" s="250">
-        <v>46247</v>
+    <row r="30" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B30" s="249">
+        <v>46245</v>
       </c>
       <c r="C30" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Tue</v>
       </c>
       <c r="D30" s="246">
         <v>0.45833333333333331</v>
@@ -5605,13 +5617,13 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="31" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B31" s="250">
-        <v>46248</v>
+    <row r="31" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B31" s="249">
+        <v>46246</v>
       </c>
       <c r="C31" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="D31" s="246">
         <v>0.45833333333333331</v>
@@ -5644,19 +5656,19 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="32" spans="2:23" ht="15.75" thickBot="1">
+    <row r="32" spans="2:12" ht="15.75" thickBot="1">
       <c r="B32" s="250">
-        <v>46253</v>
+        <v>46247</v>
       </c>
       <c r="C32" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="D32" s="246">
-        <v>0.29166666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E32" s="246">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F32" s="258">
         <f t="shared" si="6"/>
@@ -5676,372 +5688,352 @@
         <v>20</v>
       </c>
       <c r="K32" s="248" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="L32" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U32" s="342" t="s">
+    </row>
+    <row r="33" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B33" s="250">
+        <v>46248</v>
+      </c>
+      <c r="C33" s="245" t="str">
+        <f t="shared" si="5"/>
+        <v>Fri</v>
+      </c>
+      <c r="D33" s="246">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E33" s="246">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F33" s="258">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G33" s="245">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H33" s="247" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="248" t="s">
+        <v>39</v>
+      </c>
+      <c r="L33" s="59" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B34" s="250">
+        <v>46253</v>
+      </c>
+      <c r="C34" s="245" t="str">
+        <f t="shared" si="5"/>
+        <v>Wed</v>
+      </c>
+      <c r="D34" s="246">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E34" s="246">
+        <v>0.5</v>
+      </c>
+      <c r="F34" s="258">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G34" s="245">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H34" s="247" t="s">
+        <v>4</v>
+      </c>
+      <c r="I34" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="248" t="s">
+        <v>71</v>
+      </c>
+      <c r="L34" s="59" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="U34" s="342" t="s">
         <v>74</v>
       </c>
-      <c r="V32" s="98" t="s">
+      <c r="V34" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="W32" s="200" t="s">
+      <c r="W34" s="200" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:23">
-      <c r="B33" s="105">
+    <row r="35" spans="2:23">
+      <c r="B35" s="105">
         <v>46269</v>
       </c>
-      <c r="C33" s="170" t="str">
-        <f t="shared" ref="C33:C35" si="9">IF(ISNUMBER(FIND("?", B33, 1)), "TBD", TEXT(B33, "ddd"))</f>
+      <c r="C35" s="170" t="str">
+        <f t="shared" ref="C35:C37" si="9">IF(ISNUMBER(FIND("?", B35, 1)), "TBD", TEXT(B35, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D33" s="160">
+      <c r="D35" s="160">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E33" s="160">
+      <c r="E35" s="160">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F33" s="224">
-        <f t="shared" ref="F33:F35" si="10">((E33 - D33) * 24)</f>
+      <c r="F35" s="224">
+        <f t="shared" ref="F35:F37" si="10">((E35 - D35) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G33" s="170">
-        <f t="shared" ref="G33:G35" si="11">IF(F33 &gt; 4, (F33 - 1), F33)</f>
-        <v>4</v>
-      </c>
-      <c r="H33" s="185" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="210" t="s">
+      <c r="G35" s="170">
+        <f t="shared" ref="G35:G37" si="11">IF(F35 &gt; 4, (F35 - 1), F35)</f>
+        <v>4</v>
+      </c>
+      <c r="H35" s="185" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="42" t="str">
-        <f t="shared" ref="L33:L35" ca="1" si="12">IF(C33 = "TBD", "TBD", IF(B33 = "", "IDK!!", IF(TODAY() &gt; B33, "Passed", IF(TODAY() = B33, "Today!!", "Upcoming"))))</f>
+      <c r="L35" s="42" t="str">
+        <f t="shared" ref="L35:L37" ca="1" si="12">IF(C35 = "TBD", "TBD", IF(B35 = "", "IDK!!", IF(TODAY() &gt; B35, "Passed", IF(TODAY() = B35, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
-      <c r="U33" s="348" t="s">
+      <c r="U35" s="348" t="s">
         <v>76</v>
       </c>
-      <c r="V33" s="349">
+      <c r="V35" s="349">
         <v>2024</v>
       </c>
-      <c r="W33" s="350">
+      <c r="W35" s="350">
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="2:23">
-      <c r="B34" s="322">
+    <row r="36" spans="2:23">
+      <c r="B36" s="322">
         <v>46275</v>
       </c>
-      <c r="C34" s="323" t="str">
+      <c r="C36" s="323" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D34" s="324">
+      <c r="D36" s="324">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E34" s="324">
+      <c r="E36" s="324">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F34" s="325">
+      <c r="F36" s="325">
         <f t="shared" si="10"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="G34" s="323">
+      <c r="G36" s="323">
         <f t="shared" si="11"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="H34" s="326" t="s">
-        <v>4</v>
-      </c>
-      <c r="I34" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" s="328" t="s">
+      <c r="H36" s="326" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="328" t="s">
         <v>72</v>
       </c>
-      <c r="L34" s="67" t="str">
+      <c r="L36" s="67" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="U34" s="351" t="s">
+      <c r="U36" s="351" t="s">
         <v>77</v>
       </c>
-      <c r="V34" s="352">
-        <f>V33+1</f>
+      <c r="V36" s="352">
+        <f>V35+1</f>
         <v>2025</v>
       </c>
-      <c r="W34" s="353">
+      <c r="W36" s="353">
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B35" s="316">
+    <row r="37" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B37" s="316">
         <v>46275</v>
       </c>
-      <c r="C35" s="317" t="str">
+      <c r="C37" s="317" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D35" s="318">
+      <c r="D37" s="318">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E35" s="318">
+      <c r="E37" s="318">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F35" s="319">
+      <c r="F37" s="319">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="G35" s="317">
+      <c r="G37" s="317">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="H35" s="320" t="s">
+      <c r="H37" s="320" t="s">
         <v>10</v>
       </c>
-      <c r="I35" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="321" t="s">
+      <c r="I37" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="321" t="s">
         <v>72</v>
       </c>
-      <c r="L35" s="60" t="str">
+      <c r="L37" s="60" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="U35" s="343" t="s">
+      <c r="U37" s="343" t="s">
         <v>78</v>
       </c>
-      <c r="V35" s="70">
-        <f>V34+1</f>
+      <c r="V37" s="70">
+        <f>V36+1</f>
         <v>2026</v>
       </c>
-      <c r="W35" s="344">
+      <c r="W37" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B36" s="124">
+    <row r="38" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B38" s="124">
         <v>46353</v>
       </c>
-      <c r="C36" s="173" t="str">
+      <c r="C38" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D36" s="155">
+      <c r="D38" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E36" s="155">
+      <c r="E38" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F36" s="226">
+      <c r="F38" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G36" s="173">
+      <c r="G38" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H36" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I36" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="269" t="s">
+      <c r="H38" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="L36" s="192" t="str">
+      <c r="L38" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U36" s="343" t="s">
+      <c r="U38" s="343" t="s">
         <v>79</v>
       </c>
-      <c r="V36" s="70">
-        <f t="shared" ref="V36:V42" si="13">V35+1</f>
+      <c r="V38" s="70">
+        <f t="shared" ref="V38:V44" si="13">V37+1</f>
         <v>2027</v>
       </c>
-      <c r="W36" s="344">
+      <c r="W38" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="37" spans="2:23">
-      <c r="B37" s="112">
+    <row r="39" spans="2:23">
+      <c r="B39" s="112">
         <v>46380</v>
       </c>
-      <c r="C37" s="264" t="str">
+      <c r="C39" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D37" s="262">
+      <c r="D39" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E37" s="262">
+      <c r="E39" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F37" s="263">
+      <c r="F39" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G37" s="264">
+      <c r="G39" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H37" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I37" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="266" t="s">
+      <c r="H39" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I39" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="L37" s="42" t="str">
+      <c r="L39" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U37" s="343" t="s">
+      <c r="U39" s="343" t="s">
         <v>80</v>
       </c>
-      <c r="V37" s="70">
+      <c r="V39" s="70">
         <f t="shared" si="13"/>
         <v>2028</v>
       </c>
-      <c r="W37" s="344">
+      <c r="W39" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="38" spans="2:23">
-      <c r="B38" s="120">
+    <row r="40" spans="2:23">
+      <c r="B40" s="120">
         <v>46384</v>
       </c>
-      <c r="C38" s="274" t="str">
+      <c r="C40" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D38" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E38" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F38" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G38" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H38" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I38" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="L38" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="U38" s="343" t="s">
-        <v>81</v>
-      </c>
-      <c r="V38" s="70">
-        <f t="shared" si="13"/>
-        <v>2029</v>
-      </c>
-      <c r="W38" s="344">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23">
-      <c r="B39" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C39" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
-      <c r="D39" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E39" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F39" s="276">
-        <f t="shared" ref="F39:F41" si="14">((E39 - D39) * 24)</f>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G39" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H39" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I39" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="273" t="s">
-        <v>60</v>
-      </c>
-      <c r="L39" s="193" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="U39" s="343" t="s">
-        <v>82</v>
-      </c>
-      <c r="V39" s="70">
-        <f t="shared" si="13"/>
-        <v>2030</v>
-      </c>
-      <c r="W39" s="344">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40" spans="2:23">
-      <c r="B40" s="270">
-        <v>46386</v>
-      </c>
-      <c r="C40" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Wed</v>
-      </c>
       <c r="D40" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -6049,47 +6041,47 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F40" s="276">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G40" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H40" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="273" t="s">
+      <c r="H40" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="L40" s="193" t="str">
+      <c r="L40" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
       <c r="U40" s="343" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V40" s="70">
         <f t="shared" si="13"/>
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="W40" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B41" s="113">
-        <v>46387</v>
+    <row r="41" spans="2:23">
+      <c r="B41" s="270">
+        <v>46385</v>
       </c>
       <c r="C41" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Tue</v>
       </c>
       <c r="D41" s="275">
         <v>0.29166666666666669</v>
@@ -6098,23 +6090,23 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F41" s="276">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="F41:F43" si="14">((E41 - D41) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G41" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H41" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="268" t="s">
+      <c r="H41" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="273" t="s">
         <v>60</v>
       </c>
       <c r="L41" s="193" t="str">
@@ -6122,115 +6114,213 @@
         <v>Upcoming</v>
       </c>
       <c r="U41" s="343" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="V41" s="70">
         <f t="shared" si="13"/>
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="W41" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="42" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B42" s="102"/>
-      <c r="C42" s="165" t="str">
-        <f t="shared" ref="C42:C43" si="15">IF(ISNUMBER(FIND("?", B42, 1)), "TBD", TEXT(B42, "ddd"))</f>
+    <row r="42" spans="2:23">
+      <c r="B42" s="270">
+        <v>46386</v>
+      </c>
+      <c r="C42" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Wed</v>
+      </c>
+      <c r="D42" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E42" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F42" s="276">
+        <f t="shared" si="14"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G42" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H42" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="273" t="s">
+        <v>60</v>
+      </c>
+      <c r="L42" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="U42" s="343" t="s">
+        <v>83</v>
+      </c>
+      <c r="V42" s="70">
+        <f t="shared" si="13"/>
+        <v>2031</v>
+      </c>
+      <c r="W42" s="344">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B43" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C43" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D43" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E43" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F43" s="276">
+        <f t="shared" si="14"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G43" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H43" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="L43" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="U43" s="343" t="s">
+        <v>84</v>
+      </c>
+      <c r="V43" s="70">
+        <f t="shared" si="13"/>
+        <v>2032</v>
+      </c>
+      <c r="W43" s="344">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B44" s="102"/>
+      <c r="C44" s="165" t="str">
+        <f t="shared" ref="C44:C45" si="15">IF(ISNUMBER(FIND("?", B44, 1)), "TBD", TEXT(B44, "ddd"))</f>
         <v>Sat</v>
       </c>
-      <c r="D42" s="157"/>
-      <c r="E42" s="157"/>
-      <c r="F42" s="220">
-        <f t="shared" ref="F42:F43" si="16">((E42 - D42) * 24)</f>
+      <c r="D44" s="157"/>
+      <c r="E44" s="157"/>
+      <c r="F44" s="220">
+        <f t="shared" ref="F44:F45" si="16">((E44 - D44) * 24)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="217">
-        <f t="shared" ref="G42:G43" si="17">IF(F42 &gt; 4, (F42 - 1), F42)</f>
+      <c r="G44" s="217">
+        <f t="shared" ref="G44:G45" si="17">IF(F44 &gt; 4, (F44 - 1), F44)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="180"/>
-      <c r="I42" s="197" t="s">
+      <c r="H44" s="180"/>
+      <c r="I44" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="J42" s="197" t="s">
+      <c r="J44" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="K42" s="205"/>
-      <c r="L42" s="252" t="str">
-        <f t="shared" ref="L42:L43" ca="1" si="18">IF(C42 = "TBD", "TBD", IF(B42 = "", "IDK!!", IF(TODAY() &gt; B42, "Passed", IF(TODAY() = B42, "Today!!", "Upcoming"))))</f>
+      <c r="K44" s="205"/>
+      <c r="L44" s="252" t="str">
+        <f t="shared" ref="L44:L45" ca="1" si="18">IF(C44 = "TBD", "TBD", IF(B44 = "", "IDK!!", IF(TODAY() &gt; B44, "Passed", IF(TODAY() = B44, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
-      <c r="U42" s="345" t="s">
+      <c r="U44" s="345" t="s">
         <v>85</v>
       </c>
-      <c r="V42" s="346">
+      <c r="V44" s="346">
         <f t="shared" si="13"/>
         <v>2033</v>
       </c>
-      <c r="W42" s="347">
+      <c r="W44" s="347">
         <f>192 + 10</f>
         <v>202</v>
       </c>
     </row>
-    <row r="43" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B43" s="259"/>
-      <c r="C43" s="253" t="str">
+    <row r="45" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B45" s="259"/>
+      <c r="C45" s="253" t="str">
         <f t="shared" si="15"/>
         <v>Sat</v>
       </c>
-      <c r="D43" s="260"/>
-      <c r="E43" s="260"/>
-      <c r="F43" s="261">
+      <c r="D45" s="260"/>
+      <c r="E45" s="260"/>
+      <c r="F45" s="261">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G43" s="253">
+      <c r="G45" s="253">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H43" s="254"/>
-      <c r="I43" s="202" t="s">
+      <c r="H45" s="254"/>
+      <c r="I45" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="J43" s="202" t="s">
+      <c r="J45" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="K43" s="255"/>
-      <c r="L43" s="251" t="str">
+      <c r="K45" s="255"/>
+      <c r="L45" s="251" t="str">
         <f t="shared" ca="1" si="18"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="44" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B44" s="86" t="s">
+    <row r="46" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B46" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="303"/>
-      <c r="D44" s="304"/>
-      <c r="E44" s="305"/>
-      <c r="F44" s="228">
-        <f>SUM(F14:F43)</f>
-        <v>163.5</v>
-      </c>
-      <c r="G44" s="256">
-        <f>SUM(G14:G43)</f>
-        <v>140.5</v>
-      </c>
-      <c r="H44" s="301"/>
-      <c r="I44" s="302"/>
-      <c r="J44" s="302"/>
-      <c r="K44" s="302"/>
-      <c r="L44" s="302"/>
+      <c r="C46" s="303"/>
+      <c r="D46" s="304"/>
+      <c r="E46" s="305"/>
+      <c r="F46" s="228">
+        <f>SUM(F14:F45)</f>
+        <v>171.5</v>
+      </c>
+      <c r="G46" s="256">
+        <f>SUM(G14:G45)</f>
+        <v>148.5</v>
+      </c>
+      <c r="H46" s="301"/>
+      <c r="I46" s="302"/>
+      <c r="J46" s="302"/>
+      <c r="K46" s="302"/>
+      <c r="L46" s="302"/>
     </row>
   </sheetData>
-  <autoFilter ref="B13:K44" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <autoFilter ref="B13:K46" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B14:L43">
+  <conditionalFormatting sqref="B14:L45">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F43 L14:L43">
+  <conditionalFormatting sqref="C14:F45 L14:L45">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -6245,7 +6335,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J43">
+  <conditionalFormatting sqref="I14:J45">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDABBB5-8DD6-42BB-84A5-5DEC991A2E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C7E296-75F7-4937-B13C-071FCBDDA8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="-75" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$L$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$L$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2027'!$B$13:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="93">
   <si>
     <t>Total</t>
   </si>
@@ -352,7 +352,16 @@
     <t>KY / Ark</t>
   </si>
   <si>
-    <t>Barn garage door operator replacement</t>
+    <t>Barn garage door operator replacement
+(split request only in this tracker / one request in UKG)</t>
+  </si>
+  <si>
+    <t>Not sick / BTTB
+(split request only in this tracker / one request in UKG)</t>
+  </si>
+  <si>
+    <t>BTTB Main Event Week
+(split request only in this tracker / one request in UKG)</t>
   </si>
 </sst>
 </file>
@@ -3026,8 +3035,8 @@
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>557336</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>182002</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>36326</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3114,8 +3123,8 @@
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>558202</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>106947</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>118152</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3152,13 +3161,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>178174</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4287,7 +4296,7 @@
       </c>
       <c r="C3" s="3">
         <f ca="1">160+C4</f>
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
@@ -4295,7 +4304,7 @@
       </c>
       <c r="E3" s="1">
         <f ca="1">C3 - C6 - SUMIF(H14:H19, "PTO", G14:G19)</f>
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename", A2),LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) + 1</f>
@@ -4308,7 +4317,7 @@
       </c>
       <c r="C4" s="2" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">IF((RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) &lt;&gt; "Template", (INDIRECT("'" &amp; (RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) - 1 &amp; "'!E3")) + (INDIRECT("'" &amp; (RIGHT(CELL("filename", A3), LEN(CELL("filename", A3)) - SEARCH("]", CELL("filename",A3)))) - 1 &amp; "'!E6")), 0)</f>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
@@ -4319,7 +4328,7 @@
       </c>
       <c r="C5" s="7">
         <f ca="1">C3/8</f>
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
@@ -4327,7 +4336,7 @@
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>17.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -4732,7 +4741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:W46"/>
+  <dimension ref="B1:W47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -4780,7 +4789,7 @@
         <v>168.5</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H45, "PTO", G14:G45)</f>
+        <f ca="1">C3 - C6 - SUMIF(H14:H46, "PTO", G14:G46)</f>
         <v>0</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
@@ -4825,11 +4834,11 @@
       </c>
       <c r="D6" s="10">
         <f>C6-E6</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H45, "Sick", G14:G45)</f>
-        <v>36</v>
+        <f>C6 - SUMIF(H14:H46, "Sick", G14:G46)</f>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15.75" thickBot="1">
@@ -4842,11 +4851,11 @@
       </c>
       <c r="D7" s="13">
         <f>D6/8</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E7" s="14">
         <f>E6/8</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -4861,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H45, "Be You", G14:G45)</f>
+        <f>C8 - SUMIF(H14:H46, "Be You", G14:G46)</f>
         <v>0</v>
       </c>
       <c r="K8" s="51"/>
@@ -4895,7 +4904,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H45, "Volunteer", G14:G45)</f>
+        <f>C10 - SUMIF(H14:H46, "Volunteer", G14:G46)</f>
         <v>4</v>
       </c>
       <c r="K10" s="36"/>
@@ -5071,7 +5080,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:12" ht="15.75" thickBot="1">
       <c r="B17" s="289">
         <v>46150</v>
       </c>
@@ -5110,7 +5119,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:12" ht="15.75" thickBot="1">
       <c r="B18" s="270">
         <v>46164</v>
       </c>
@@ -5188,7 +5197,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
+    <row r="20" spans="2:12" ht="30.75" thickBot="1">
       <c r="B20" s="103">
         <v>46196</v>
       </c>
@@ -5217,17 +5226,17 @@
         <v>20</v>
       </c>
       <c r="J20" s="196" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K20" s="366" t="s">
         <v>90</v>
       </c>
       <c r="L20" s="42" t="str">
         <f ca="1">IF(C20 = "TBD", "TBD", IF(B20 = "", "IDK!!", IF(TODAY() &gt; B20, "Passed", IF(TODAY() = B20, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="15.75" thickBot="1">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="30.75" thickBot="1">
       <c r="B21" s="282">
         <v>46196</v>
       </c>
@@ -5256,14 +5265,14 @@
         <v>20</v>
       </c>
       <c r="J21" s="327" t="s">
-        <v>28</v>
-      </c>
-      <c r="K21" s="288" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="366" t="s">
         <v>90</v>
       </c>
       <c r="L21" s="67" t="str">
         <f ca="1">IF(C21 = "TBD", "TBD", IF(B21 = "", "IDK!!", IF(TODAY() &gt; B21, "Passed", IF(TODAY() = B21, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -5302,7 +5311,7 @@
       </c>
       <c r="L22" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -5341,7 +5350,7 @@
       </c>
       <c r="L23" s="59" t="str">
         <f ca="1">IF(C23 = "TBD", "TBD", IF(B23 = "", "IDK!!", IF(TODAY() &gt; B23, "Passed", IF(TODAY() = B23, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -5427,7 +5436,7 @@
         <v>46234</v>
       </c>
       <c r="C26" s="331" t="str">
-        <f t="shared" ref="C26:C43" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
+        <f t="shared" ref="C26:C44" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D26" s="332">
@@ -5437,11 +5446,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F26" s="333">
-        <f t="shared" ref="F26:F40" si="6">((E26 - D26) * 24)</f>
+        <f t="shared" ref="F26:F41" si="6">((E26 - D26) * 24)</f>
         <v>5</v>
       </c>
       <c r="G26" s="331">
-        <f t="shared" ref="G26:G43" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
+        <f t="shared" ref="G26:G44" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
         <v>4</v>
       </c>
       <c r="H26" s="334" t="s">
@@ -5457,7 +5466,7 @@
         <v>59</v>
       </c>
       <c r="L26" s="336" t="str">
-        <f t="shared" ref="L26:L43" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="L26:L44" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5500,7 +5509,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="28" spans="2:12" ht="15.75" thickBot="1">
+    <row r="28" spans="2:12">
       <c r="B28" s="249">
         <v>46241</v>
       </c>
@@ -5539,7 +5548,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="29" spans="2:12" ht="15.75" thickBot="1">
+    <row r="29" spans="2:12">
       <c r="B29" s="249">
         <v>46244</v>
       </c>
@@ -5578,7 +5587,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="15.75" thickBot="1">
+    <row r="30" spans="2:12">
       <c r="B30" s="249">
         <v>46245</v>
       </c>
@@ -5617,52 +5626,52 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="15.75" thickBot="1">
+    <row r="31" spans="2:12" ht="30">
       <c r="B31" s="249">
         <v>46246</v>
       </c>
       <c r="C31" s="245" t="str">
+        <f>IF(ISNUMBER(FIND("?", B31, 1)), "TBD", TEXT(B31, "ddd"))</f>
+        <v>Wed</v>
+      </c>
+      <c r="D31" s="246">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E31" s="246">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F31" s="258">
+        <f>((E31 - D31) * 24)</f>
+        <v>3.9999999999999991</v>
+      </c>
+      <c r="G31" s="245">
+        <f>IF(F31 &gt; 4, (F31 - 1), F31)</f>
+        <v>3.9999999999999991</v>
+      </c>
+      <c r="H31" s="247" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="K31" s="248" t="s">
+        <v>91</v>
+      </c>
+      <c r="L31" s="59" t="str">
+        <f ca="1">IF(C31 = "TBD", "TBD", IF(B31 = "", "IDK!!", IF(TODAY() &gt; B31, "Passed", IF(TODAY() = B31, "Today!!", "Upcoming"))))</f>
+        <v>Upcoming</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="30">
+      <c r="B32" s="249">
+        <v>46246</v>
+      </c>
+      <c r="C32" s="245" t="str">
         <f t="shared" si="5"/>
         <v>Wed</v>
-      </c>
-      <c r="D31" s="246">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E31" s="246">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F31" s="258">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="G31" s="245">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="H31" s="247" t="s">
-        <v>4</v>
-      </c>
-      <c r="I31" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="248" t="s">
-        <v>39</v>
-      </c>
-      <c r="L31" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="15.75" thickBot="1">
-      <c r="B32" s="250">
-        <v>46247</v>
-      </c>
-      <c r="C32" s="245" t="str">
-        <f t="shared" si="5"/>
-        <v>Thu</v>
       </c>
       <c r="D32" s="246">
         <v>0.45833333333333331</v>
@@ -5685,23 +5694,23 @@
         <v>20</v>
       </c>
       <c r="J32" s="199" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K32" s="248" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="L32" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="33" spans="2:23" ht="15.75" thickBot="1">
+    <row r="33" spans="2:23">
       <c r="B33" s="250">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="C33" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="D33" s="246">
         <v>0.45833333333333331</v>
@@ -5734,19 +5743,19 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="34" spans="2:23" ht="15.75" thickBot="1">
+    <row r="34" spans="2:23">
       <c r="B34" s="250">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="C34" s="245" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Fri</v>
       </c>
       <c r="D34" s="246">
-        <v>0.29166666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E34" s="246">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F34" s="258">
         <f t="shared" si="6"/>
@@ -5766,323 +5775,313 @@
         <v>20</v>
       </c>
       <c r="K34" s="248" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="L34" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U34" s="342" t="s">
+    </row>
+    <row r="35" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B35" s="250">
+        <v>46253</v>
+      </c>
+      <c r="C35" s="245" t="str">
+        <f t="shared" si="5"/>
+        <v>Wed</v>
+      </c>
+      <c r="D35" s="246">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E35" s="246">
+        <v>0.5</v>
+      </c>
+      <c r="F35" s="258">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G35" s="245">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H35" s="247" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="248" t="s">
+        <v>71</v>
+      </c>
+      <c r="L35" s="59" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="U35" s="342" t="s">
         <v>74</v>
       </c>
-      <c r="V34" s="98" t="s">
+      <c r="V35" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="W34" s="200" t="s">
+      <c r="W35" s="200" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="2:23">
-      <c r="B35" s="105">
+    <row r="36" spans="2:23">
+      <c r="B36" s="105">
         <v>46269</v>
       </c>
-      <c r="C35" s="170" t="str">
-        <f t="shared" ref="C35:C37" si="9">IF(ISNUMBER(FIND("?", B35, 1)), "TBD", TEXT(B35, "ddd"))</f>
+      <c r="C36" s="170" t="str">
+        <f t="shared" ref="C36:C38" si="9">IF(ISNUMBER(FIND("?", B36, 1)), "TBD", TEXT(B36, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D35" s="160">
+      <c r="D36" s="160">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E35" s="160">
+      <c r="E36" s="160">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F35" s="224">
-        <f t="shared" ref="F35:F37" si="10">((E35 - D35) * 24)</f>
+      <c r="F36" s="224">
+        <f t="shared" ref="F36:F38" si="10">((E36 - D36) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G35" s="170">
-        <f t="shared" ref="G35:G37" si="11">IF(F35 &gt; 4, (F35 - 1), F35)</f>
-        <v>4</v>
-      </c>
-      <c r="H35" s="185" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="210" t="s">
+      <c r="G36" s="170">
+        <f t="shared" ref="G36:G38" si="11">IF(F36 &gt; 4, (F36 - 1), F36)</f>
+        <v>4</v>
+      </c>
+      <c r="H36" s="185" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="42" t="str">
-        <f t="shared" ref="L35:L37" ca="1" si="12">IF(C35 = "TBD", "TBD", IF(B35 = "", "IDK!!", IF(TODAY() &gt; B35, "Passed", IF(TODAY() = B35, "Today!!", "Upcoming"))))</f>
+      <c r="L36" s="42" t="str">
+        <f t="shared" ref="L36:L38" ca="1" si="12">IF(C36 = "TBD", "TBD", IF(B36 = "", "IDK!!", IF(TODAY() &gt; B36, "Passed", IF(TODAY() = B36, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
-      <c r="U35" s="348" t="s">
+      <c r="U36" s="348" t="s">
         <v>76</v>
       </c>
-      <c r="V35" s="349">
+      <c r="V36" s="349">
         <v>2024</v>
       </c>
-      <c r="W35" s="350">
+      <c r="W36" s="350">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="2:23">
-      <c r="B36" s="322">
+    <row r="37" spans="2:23">
+      <c r="B37" s="322">
         <v>46275</v>
       </c>
-      <c r="C36" s="323" t="str">
+      <c r="C37" s="323" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D36" s="324">
+      <c r="D37" s="324">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E36" s="324">
+      <c r="E37" s="324">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F36" s="325">
+      <c r="F37" s="325">
         <f t="shared" si="10"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G37" s="323">
         <f t="shared" si="11"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="H36" s="326" t="s">
-        <v>4</v>
-      </c>
-      <c r="I36" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="328" t="s">
+      <c r="H37" s="326" t="s">
+        <v>4</v>
+      </c>
+      <c r="I37" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="327" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="328" t="s">
         <v>72</v>
       </c>
-      <c r="L36" s="67" t="str">
+      <c r="L37" s="67" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="U36" s="351" t="s">
+      <c r="U37" s="351" t="s">
         <v>77</v>
       </c>
-      <c r="V36" s="352">
-        <f>V35+1</f>
+      <c r="V37" s="352">
+        <f>V36+1</f>
         <v>2025</v>
       </c>
-      <c r="W36" s="353">
+      <c r="W37" s="353">
         <v>160</v>
       </c>
     </row>
-    <row r="37" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B37" s="316">
+    <row r="38" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B38" s="316">
         <v>46275</v>
       </c>
-      <c r="C37" s="317" t="str">
+      <c r="C38" s="317" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D37" s="318">
+      <c r="D38" s="318">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E37" s="318">
+      <c r="E38" s="318">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F37" s="319">
+      <c r="F38" s="319">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="G37" s="317">
+      <c r="G38" s="317">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="H37" s="320" t="s">
+      <c r="H38" s="320" t="s">
         <v>10</v>
       </c>
-      <c r="I37" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="321" t="s">
+      <c r="I38" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="321" t="s">
         <v>72</v>
       </c>
-      <c r="L37" s="60" t="str">
+      <c r="L38" s="60" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="U37" s="343" t="s">
+      <c r="U38" s="343" t="s">
         <v>78</v>
       </c>
-      <c r="V37" s="70">
-        <f>V36+1</f>
+      <c r="V38" s="70">
+        <f>V37+1</f>
         <v>2026</v>
       </c>
-      <c r="W37" s="344">
+      <c r="W38" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="38" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B38" s="124">
+    <row r="39" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B39" s="124">
         <v>46353</v>
       </c>
-      <c r="C38" s="173" t="str">
+      <c r="C39" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D38" s="155">
+      <c r="D39" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E38" s="155">
+      <c r="E39" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F38" s="226">
+      <c r="F39" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G38" s="173">
+      <c r="G39" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H38" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I38" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="269" t="s">
+      <c r="H39" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I39" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="L38" s="192" t="str">
+      <c r="L39" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U38" s="343" t="s">
+      <c r="U39" s="343" t="s">
         <v>79</v>
       </c>
-      <c r="V38" s="70">
-        <f t="shared" ref="V38:V44" si="13">V37+1</f>
+      <c r="V39" s="70">
+        <f t="shared" ref="V39:V45" si="13">V38+1</f>
         <v>2027</v>
       </c>
-      <c r="W38" s="344">
+      <c r="W39" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="2:23">
-      <c r="B39" s="112">
+    <row r="40" spans="2:23">
+      <c r="B40" s="112">
         <v>46380</v>
       </c>
-      <c r="C39" s="264" t="str">
+      <c r="C40" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D39" s="262">
+      <c r="D40" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E39" s="262">
+      <c r="E40" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F39" s="263">
+      <c r="F40" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G39" s="264">
+      <c r="G40" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H39" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I39" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="266" t="s">
+      <c r="H40" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="L39" s="42" t="str">
+      <c r="L40" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U39" s="343" t="s">
+      <c r="U40" s="343" t="s">
         <v>80</v>
       </c>
-      <c r="V39" s="70">
+      <c r="V40" s="70">
         <f t="shared" si="13"/>
         <v>2028</v>
       </c>
-      <c r="W39" s="344">
+      <c r="W40" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="2:23">
-      <c r="B40" s="120">
+    <row r="41" spans="2:23">
+      <c r="B41" s="120">
         <v>46384</v>
       </c>
-      <c r="C40" s="274" t="str">
+      <c r="C41" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D40" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E40" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F40" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G40" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H40" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="L40" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="U40" s="343" t="s">
-        <v>81</v>
-      </c>
-      <c r="V40" s="70">
-        <f t="shared" si="13"/>
-        <v>2029</v>
-      </c>
-      <c r="W40" s="344">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="41" spans="2:23">
-      <c r="B41" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C41" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
       <c r="D41" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -6090,35 +6089,35 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F41" s="276">
-        <f t="shared" ref="F41:F43" si="14">((E41 - D41) * 24)</f>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G41" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H41" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="273" t="s">
+      <c r="H41" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="L41" s="193" t="str">
+      <c r="L41" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
       <c r="U41" s="343" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V41" s="70">
         <f t="shared" si="13"/>
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="W41" s="344">
         <v>176</v>
@@ -6126,11 +6125,11 @@
     </row>
     <row r="42" spans="2:23">
       <c r="B42" s="270">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C42" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D42" s="275">
         <v>0.29166666666666669</v>
@@ -6139,7 +6138,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F42" s="276">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="F42:F44" si="14">((E42 - D42) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G42" s="274">
@@ -6163,23 +6162,23 @@
         <v>Upcoming</v>
       </c>
       <c r="U42" s="343" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V42" s="70">
         <f t="shared" si="13"/>
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="W42" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="43" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B43" s="113">
-        <v>46387</v>
+    <row r="43" spans="2:23">
+      <c r="B43" s="270">
+        <v>46386</v>
       </c>
       <c r="C43" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D43" s="275">
         <v>0.29166666666666669</v>
@@ -6195,16 +6194,16 @@
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H43" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="268" t="s">
+      <c r="H43" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="273" t="s">
         <v>60</v>
       </c>
       <c r="L43" s="193" t="str">
@@ -6212,115 +6211,164 @@
         <v>Upcoming</v>
       </c>
       <c r="U43" s="343" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V43" s="70">
         <f t="shared" si="13"/>
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="W43" s="344">
         <v>176</v>
       </c>
     </row>
     <row r="44" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B44" s="102"/>
-      <c r="C44" s="165" t="str">
-        <f t="shared" ref="C44:C45" si="15">IF(ISNUMBER(FIND("?", B44, 1)), "TBD", TEXT(B44, "ddd"))</f>
+      <c r="B44" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C44" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D44" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E44" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F44" s="276">
+        <f t="shared" si="14"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G44" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H44" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="L44" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="U44" s="343" t="s">
+        <v>84</v>
+      </c>
+      <c r="V44" s="70">
+        <f t="shared" si="13"/>
+        <v>2032</v>
+      </c>
+      <c r="W44" s="344">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B45" s="102"/>
+      <c r="C45" s="165" t="str">
+        <f t="shared" ref="C45:C46" si="15">IF(ISNUMBER(FIND("?", B45, 1)), "TBD", TEXT(B45, "ddd"))</f>
         <v>Sat</v>
       </c>
-      <c r="D44" s="157"/>
-      <c r="E44" s="157"/>
-      <c r="F44" s="220">
-        <f t="shared" ref="F44:F45" si="16">((E44 - D44) * 24)</f>
+      <c r="D45" s="157"/>
+      <c r="E45" s="157"/>
+      <c r="F45" s="220">
+        <f t="shared" ref="F45:F46" si="16">((E45 - D45) * 24)</f>
         <v>0</v>
       </c>
-      <c r="G44" s="217">
-        <f t="shared" ref="G44:G45" si="17">IF(F44 &gt; 4, (F44 - 1), F44)</f>
+      <c r="G45" s="217">
+        <f t="shared" ref="G45:G46" si="17">IF(F45 &gt; 4, (F45 - 1), F45)</f>
         <v>0</v>
       </c>
-      <c r="H44" s="180"/>
-      <c r="I44" s="197" t="s">
+      <c r="H45" s="180"/>
+      <c r="I45" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="J44" s="197" t="s">
+      <c r="J45" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="K44" s="205"/>
-      <c r="L44" s="252" t="str">
-        <f t="shared" ref="L44:L45" ca="1" si="18">IF(C44 = "TBD", "TBD", IF(B44 = "", "IDK!!", IF(TODAY() &gt; B44, "Passed", IF(TODAY() = B44, "Today!!", "Upcoming"))))</f>
+      <c r="K45" s="205"/>
+      <c r="L45" s="252" t="str">
+        <f t="shared" ref="L45:L46" ca="1" si="18">IF(C45 = "TBD", "TBD", IF(B45 = "", "IDK!!", IF(TODAY() &gt; B45, "Passed", IF(TODAY() = B45, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
-      <c r="U44" s="345" t="s">
+      <c r="U45" s="345" t="s">
         <v>85</v>
       </c>
-      <c r="V44" s="346">
+      <c r="V45" s="346">
         <f t="shared" si="13"/>
         <v>2033</v>
       </c>
-      <c r="W44" s="347">
+      <c r="W45" s="347">
         <f>192 + 10</f>
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B45" s="259"/>
-      <c r="C45" s="253" t="str">
+    <row r="46" spans="2:23">
+      <c r="B46" s="259"/>
+      <c r="C46" s="253" t="str">
         <f t="shared" si="15"/>
         <v>Sat</v>
       </c>
-      <c r="D45" s="260"/>
-      <c r="E45" s="260"/>
-      <c r="F45" s="261">
+      <c r="D46" s="260"/>
+      <c r="E46" s="260"/>
+      <c r="F46" s="261">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G45" s="253">
+      <c r="G46" s="253">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H45" s="254"/>
-      <c r="I45" s="202" t="s">
+      <c r="H46" s="254"/>
+      <c r="I46" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="J45" s="202" t="s">
+      <c r="J46" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="K45" s="255"/>
-      <c r="L45" s="251" t="str">
+      <c r="K46" s="255"/>
+      <c r="L46" s="251" t="str">
         <f t="shared" ca="1" si="18"/>
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="46" spans="2:23" ht="15.75" thickBot="1">
-      <c r="B46" s="86" t="s">
+    <row r="47" spans="2:23" ht="15.75" thickBot="1">
+      <c r="B47" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="303"/>
-      <c r="D46" s="304"/>
-      <c r="E46" s="305"/>
-      <c r="F46" s="228">
-        <f>SUM(F14:F45)</f>
-        <v>171.5</v>
-      </c>
-      <c r="G46" s="256">
-        <f>SUM(G14:G45)</f>
-        <v>148.5</v>
-      </c>
-      <c r="H46" s="301"/>
-      <c r="I46" s="302"/>
-      <c r="J46" s="302"/>
-      <c r="K46" s="302"/>
-      <c r="L46" s="302"/>
+      <c r="C47" s="303"/>
+      <c r="D47" s="304"/>
+      <c r="E47" s="305"/>
+      <c r="F47" s="228">
+        <f>SUM(F14:F46)</f>
+        <v>175.5</v>
+      </c>
+      <c r="G47" s="256">
+        <f>SUM(G14:G46)</f>
+        <v>152.5</v>
+      </c>
+      <c r="H47" s="301"/>
+      <c r="I47" s="302"/>
+      <c r="J47" s="302"/>
+      <c r="K47" s="302"/>
+      <c r="L47" s="302"/>
     </row>
   </sheetData>
-  <autoFilter ref="B13:K46" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <autoFilter ref="B13:K47" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B14:L45">
+  <conditionalFormatting sqref="B14:L46">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F45 L14:L45">
+  <conditionalFormatting sqref="C14:F46 L14:L46">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -6335,7 +6383,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J45">
+  <conditionalFormatting sqref="I14:J46">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C7E296-75F7-4937-B13C-071FCBDDA8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="1170" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C7E296-75F7-4937-B13C-071FCBDDA8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2529A5-686B-4025-8080-A58310022ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="2340" yWindow="0" windowWidth="30285" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$L$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$K$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2027'!$B$13:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
@@ -3034,9 +3034,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>557336</xdr:colOff>
+      <xdr:colOff>53071</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>36326</xdr:rowOff>
+      <xdr:rowOff>58737</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3124,7 +3124,7 @@
       <xdr:col>25</xdr:col>
       <xdr:colOff>558202</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>118152</xdr:rowOff>
+      <xdr:rowOff>140563</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3166,7 +3166,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>178174</xdr:colOff>
+      <xdr:colOff>178175</xdr:colOff>
       <xdr:row>69</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
@@ -4741,7 +4741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:W47"/>
+  <dimension ref="B1:P47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -4755,6 +4755,7 @@
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="57" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13.140625" customWidth="1"/>
     <col min="21" max="21" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -5080,7 +5081,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15.75" thickBot="1">
+    <row r="17" spans="2:12">
       <c r="B17" s="289">
         <v>46150</v>
       </c>
@@ -5119,7 +5120,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15.75" thickBot="1">
+    <row r="18" spans="2:12">
       <c r="B18" s="270">
         <v>46164</v>
       </c>
@@ -5389,7 +5390,7 @@
       </c>
       <c r="L24" s="329" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -5428,7 +5429,7 @@
       </c>
       <c r="L25" s="329" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="15.75" thickBot="1">
@@ -5467,7 +5468,7 @@
       </c>
       <c r="L26" s="336" t="str">
         <f t="shared" ref="L26:L44" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -5506,7 +5507,7 @@
       </c>
       <c r="L27" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -5545,7 +5546,7 @@
       </c>
       <c r="L28" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -5584,7 +5585,7 @@
       </c>
       <c r="L29" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -5623,7 +5624,7 @@
       </c>
       <c r="L30" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="31" spans="2:12" ht="30">
@@ -5655,14 +5656,14 @@
         <v>20</v>
       </c>
       <c r="J31" s="199" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K31" s="248" t="s">
         <v>91</v>
       </c>
       <c r="L31" s="59" t="str">
         <f ca="1">IF(C31 = "TBD", "TBD", IF(B31 = "", "IDK!!", IF(TODAY() &gt; B31, "Passed", IF(TODAY() = B31, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="30">
@@ -5694,17 +5695,17 @@
         <v>20</v>
       </c>
       <c r="J32" s="199" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K32" s="248" t="s">
         <v>92</v>
       </c>
       <c r="L32" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16">
       <c r="B33" s="250">
         <v>46247</v>
       </c>
@@ -5740,10 +5741,10 @@
       </c>
       <c r="L33" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16">
       <c r="B34" s="250">
         <v>46248</v>
       </c>
@@ -5779,10 +5780,10 @@
       </c>
       <c r="L34" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-    </row>
-    <row r="35" spans="2:23" ht="15.75" thickBot="1">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" ht="15.75" thickBot="1">
       <c r="B35" s="250">
         <v>46253</v>
       </c>
@@ -5818,19 +5819,10 @@
       </c>
       <c r="L35" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="U35" s="342" t="s">
-        <v>74</v>
-      </c>
-      <c r="V35" s="98" t="s">
-        <v>75</v>
-      </c>
-      <c r="W35" s="200" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:23">
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" ht="15.75" thickBot="1">
       <c r="B36" s="105">
         <v>46269</v>
       </c>
@@ -5868,17 +5860,8 @@
         <f t="shared" ref="L36:L38" ca="1" si="12">IF(C36 = "TBD", "TBD", IF(B36 = "", "IDK!!", IF(TODAY() &gt; B36, "Passed", IF(TODAY() = B36, "Today!!", "Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
-      <c r="U36" s="348" t="s">
-        <v>76</v>
-      </c>
-      <c r="V36" s="349">
-        <v>2024</v>
-      </c>
-      <c r="W36" s="350">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23">
+    </row>
+    <row r="37" spans="2:16" ht="15.75" thickBot="1">
       <c r="B37" s="322">
         <v>46275</v>
       </c>
@@ -5916,18 +5899,17 @@
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="U37" s="351" t="s">
-        <v>77</v>
-      </c>
-      <c r="V37" s="352">
-        <f>V36+1</f>
-        <v>2025</v>
-      </c>
-      <c r="W37" s="353">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="38" spans="2:23" ht="15.75" thickBot="1">
+      <c r="N37" s="342" t="s">
+        <v>74</v>
+      </c>
+      <c r="O37" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="P37" s="200" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" ht="15.75" thickBot="1">
       <c r="B38" s="316">
         <v>46275</v>
       </c>
@@ -5965,18 +5947,17 @@
         <f t="shared" ca="1" si="12"/>
         <v>Upcoming</v>
       </c>
-      <c r="U38" s="343" t="s">
-        <v>78</v>
-      </c>
-      <c r="V38" s="70">
-        <f>V37+1</f>
-        <v>2026</v>
-      </c>
-      <c r="W38" s="344">
+      <c r="N38" s="348" t="s">
+        <v>76</v>
+      </c>
+      <c r="O38" s="349">
+        <v>2024</v>
+      </c>
+      <c r="P38" s="350">
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="2:23" ht="15.75" thickBot="1">
+    <row r="39" spans="2:16" ht="15.75" thickBot="1">
       <c r="B39" s="124">
         <v>46353</v>
       </c>
@@ -6014,18 +5995,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U39" s="343" t="s">
-        <v>79</v>
-      </c>
-      <c r="V39" s="70">
-        <f t="shared" ref="V39:V45" si="13">V38+1</f>
-        <v>2027</v>
-      </c>
-      <c r="W39" s="344">
+      <c r="N39" s="351" t="s">
+        <v>77</v>
+      </c>
+      <c r="O39" s="352">
+        <f>O38+1</f>
+        <v>2025</v>
+      </c>
+      <c r="P39" s="353">
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="2:23">
+    <row r="40" spans="2:16">
       <c r="B40" s="112">
         <v>46380</v>
       </c>
@@ -6063,18 +6044,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U40" s="343" t="s">
-        <v>80</v>
-      </c>
-      <c r="V40" s="70">
-        <f t="shared" si="13"/>
-        <v>2028</v>
-      </c>
-      <c r="W40" s="344">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="41" spans="2:23">
+      <c r="N40" s="343" t="s">
+        <v>78</v>
+      </c>
+      <c r="O40" s="70">
+        <f>O39+1</f>
+        <v>2026</v>
+      </c>
+      <c r="P40" s="344">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16">
       <c r="B41" s="120">
         <v>46384</v>
       </c>
@@ -6112,18 +6093,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U41" s="343" t="s">
-        <v>81</v>
-      </c>
-      <c r="V41" s="70">
-        <f t="shared" si="13"/>
-        <v>2029</v>
-      </c>
-      <c r="W41" s="344">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23">
+      <c r="N41" s="343" t="s">
+        <v>79</v>
+      </c>
+      <c r="O41" s="70">
+        <f t="shared" ref="O41:O47" si="13">O40+1</f>
+        <v>2027</v>
+      </c>
+      <c r="P41" s="344">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16">
       <c r="B42" s="270">
         <v>46385</v>
       </c>
@@ -6161,18 +6142,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U42" s="343" t="s">
-        <v>82</v>
-      </c>
-      <c r="V42" s="70">
+      <c r="N42" s="343" t="s">
+        <v>80</v>
+      </c>
+      <c r="O42" s="70">
         <f t="shared" si="13"/>
-        <v>2030</v>
-      </c>
-      <c r="W42" s="344">
+        <v>2028</v>
+      </c>
+      <c r="P42" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="43" spans="2:23">
+    <row r="43" spans="2:16">
       <c r="B43" s="270">
         <v>46386</v>
       </c>
@@ -6210,18 +6191,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U43" s="343" t="s">
-        <v>83</v>
-      </c>
-      <c r="V43" s="70">
+      <c r="N43" s="343" t="s">
+        <v>81</v>
+      </c>
+      <c r="O43" s="70">
         <f t="shared" si="13"/>
-        <v>2031</v>
-      </c>
-      <c r="W43" s="344">
+        <v>2029</v>
+      </c>
+      <c r="P43" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="2:23" ht="15.75" thickBot="1">
+    <row r="44" spans="2:16" ht="15.75" thickBot="1">
       <c r="B44" s="113">
         <v>46387</v>
       </c>
@@ -6259,18 +6240,18 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="U44" s="343" t="s">
-        <v>84</v>
-      </c>
-      <c r="V44" s="70">
+      <c r="N44" s="343" t="s">
+        <v>82</v>
+      </c>
+      <c r="O44" s="70">
         <f t="shared" si="13"/>
-        <v>2032</v>
-      </c>
-      <c r="W44" s="344">
+        <v>2030</v>
+      </c>
+      <c r="P44" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="45" spans="2:23" ht="15.75" thickBot="1">
+    <row r="45" spans="2:16">
       <c r="B45" s="102"/>
       <c r="C45" s="165" t="str">
         <f t="shared" ref="C45:C46" si="15">IF(ISNUMBER(FIND("?", B45, 1)), "TBD", TEXT(B45, "ddd"))</f>
@@ -6298,19 +6279,18 @@
         <f t="shared" ref="L45:L46" ca="1" si="18">IF(C45 = "TBD", "TBD", IF(B45 = "", "IDK!!", IF(TODAY() &gt; B45, "Passed", IF(TODAY() = B45, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
-      <c r="U45" s="345" t="s">
-        <v>85</v>
-      </c>
-      <c r="V45" s="346">
+      <c r="N45" s="343" t="s">
+        <v>83</v>
+      </c>
+      <c r="O45" s="70">
         <f t="shared" si="13"/>
-        <v>2033</v>
-      </c>
-      <c r="W45" s="347">
-        <f>192 + 10</f>
-        <v>202</v>
-      </c>
-    </row>
-    <row r="46" spans="2:23">
+        <v>2031</v>
+      </c>
+      <c r="P45" s="344">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" ht="15.75" thickBot="1">
       <c r="B46" s="259"/>
       <c r="C46" s="253" t="str">
         <f t="shared" si="15"/>
@@ -6338,8 +6318,18 @@
         <f t="shared" ca="1" si="18"/>
         <v>IDK!!</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" ht="15.75" thickBot="1">
+      <c r="N46" s="343" t="s">
+        <v>84</v>
+      </c>
+      <c r="O46" s="70">
+        <f t="shared" si="13"/>
+        <v>2032</v>
+      </c>
+      <c r="P46" s="344">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" ht="15.75" thickBot="1">
       <c r="B47" s="86" t="s">
         <v>11</v>
       </c>
@@ -6359,6 +6349,17 @@
       <c r="J47" s="302"/>
       <c r="K47" s="302"/>
       <c r="L47" s="302"/>
+      <c r="N47" s="345" t="s">
+        <v>85</v>
+      </c>
+      <c r="O47" s="346">
+        <f t="shared" si="13"/>
+        <v>2033</v>
+      </c>
+      <c r="P47" s="347">
+        <f>192 + 10</f>
+        <v>202</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B13:K47" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2529A5-686B-4025-8080-A58310022ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC3FE87-81C3-4206-B704-97BB55D48CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="0" windowWidth="30285" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="3825" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$K$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2027'!$B$13:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="94">
   <si>
     <t>Total</t>
   </si>
@@ -363,6 +363,9 @@
     <t>BTTB Main Event Week
 (split request only in this tracker / one request in UKG)</t>
   </si>
+  <si>
+    <t>Sick (vomiting on way home from doc appt)</t>
+  </si>
 </sst>
 </file>
 
@@ -1487,7 +1490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="367">
+  <cellXfs count="368">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2544,6 +2547,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3161,13 +3167,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>178175</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4296,7 +4302,7 @@
       </c>
       <c r="C3" s="3">
         <f ca="1">160+C4</f>
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
@@ -4304,7 +4310,7 @@
       </c>
       <c r="E3" s="1">
         <f ca="1">C3 - C6 - SUMIF(H14:H19, "PTO", G14:G19)</f>
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename", A2),LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) + 1</f>
@@ -4317,7 +4323,7 @@
       </c>
       <c r="C4" s="2" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">IF((RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) &lt;&gt; "Template", (INDIRECT("'" &amp; (RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) - 1 &amp; "'!E3")) + (INDIRECT("'" &amp; (RIGHT(CELL("filename", A3), LEN(CELL("filename", A3)) - SEARCH("]", CELL("filename",A3)))) - 1 &amp; "'!E6")), 0)</f>
-        <v>32</v>
+        <v>28.000000000000004</v>
       </c>
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
@@ -4328,7 +4334,7 @@
       </c>
       <c r="C5" s="7">
         <f ca="1">C3/8</f>
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
@@ -4336,7 +4342,7 @@
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>17</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -4741,7 +4747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:P47"/>
+  <dimension ref="B1:P48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -4790,7 +4796,7 @@
         <v>168.5</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H46, "PTO", G14:G46)</f>
+        <f ca="1">C3 - C6 - SUMIF(H14:H47, "PTO", G14:G47)</f>
         <v>0</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
@@ -4835,11 +4841,11 @@
       </c>
       <c r="D6" s="10">
         <f>C6-E6</f>
-        <v>8</v>
+        <v>11.999999999999996</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H46, "Sick", G14:G46)</f>
-        <v>32</v>
+        <f>C6 - SUMIF(H14:H47, "Sick", G14:G47)</f>
+        <v>28.000000000000004</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15.75" thickBot="1">
@@ -4852,11 +4858,11 @@
       </c>
       <c r="D7" s="13">
         <f>D6/8</f>
-        <v>1</v>
+        <v>1.4999999999999996</v>
       </c>
       <c r="E7" s="14">
         <f>E6/8</f>
-        <v>4</v>
+        <v>3.5000000000000004</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -4871,7 +4877,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H46, "Be You", G14:G46)</f>
+        <f>C8 - SUMIF(H14:H47, "Be You", G14:G47)</f>
         <v>0</v>
       </c>
       <c r="K8" s="51"/>
@@ -4905,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H46, "Volunteer", G14:G46)</f>
+        <f>C10 - SUMIF(H14:H47, "Volunteer", G14:G47)</f>
         <v>4</v>
       </c>
       <c r="K10" s="36"/>
@@ -5437,7 +5443,7 @@
         <v>46234</v>
       </c>
       <c r="C26" s="331" t="str">
-        <f t="shared" ref="C26:C44" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
+        <f t="shared" ref="C26:C45" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D26" s="332">
@@ -5447,11 +5453,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F26" s="333">
-        <f t="shared" ref="F26:F41" si="6">((E26 - D26) * 24)</f>
+        <f t="shared" ref="F26:F42" si="6">((E26 - D26) * 24)</f>
         <v>5</v>
       </c>
       <c r="G26" s="331">
-        <f t="shared" ref="G26:G44" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
+        <f t="shared" ref="G26:G45" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
         <v>4</v>
       </c>
       <c r="H26" s="334" t="s">
@@ -5467,7 +5473,7 @@
         <v>59</v>
       </c>
       <c r="L26" s="336" t="str">
-        <f t="shared" ref="L26:L44" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="L26:L45" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
@@ -5858,7 +5864,7 @@
       </c>
       <c r="L36" s="42" t="str">
         <f t="shared" ref="L36:L38" ca="1" si="12">IF(C36 = "TBD", "TBD", IF(B36 = "", "IDK!!", IF(TODAY() &gt; B36, "Passed", IF(TODAY() = B36, "Today!!", "Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15.75" thickBot="1">
@@ -5897,7 +5903,7 @@
       </c>
       <c r="L37" s="67" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
       <c r="N37" s="342" t="s">
         <v>74</v>
@@ -5909,43 +5915,43 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B38" s="316">
+    <row r="38" spans="2:16">
+      <c r="B38" s="107">
         <v>46275</v>
       </c>
-      <c r="C38" s="317" t="str">
+      <c r="C38" s="172" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D38" s="318">
+      <c r="D38" s="162">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E38" s="318">
+      <c r="E38" s="162">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="367">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="G38" s="317">
+      <c r="G38" s="172">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="H38" s="320" t="s">
+      <c r="H38" s="187" t="s">
         <v>10</v>
       </c>
-      <c r="I38" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="321" t="s">
+      <c r="I38" s="202" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="202" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="212" t="s">
         <v>72</v>
       </c>
-      <c r="L38" s="60" t="str">
+      <c r="L38" s="251" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Upcoming</v>
+        <v>Passed</v>
       </c>
       <c r="N38" s="348" t="s">
         <v>76</v>
@@ -5958,160 +5964,153 @@
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B39" s="124">
+      <c r="B39" s="316">
+        <v>46275</v>
+      </c>
+      <c r="C39" s="317" t="str">
+        <f t="shared" ref="C39" si="13">IF(ISNUMBER(FIND("?", B39, 1)), "TBD", TEXT(B39, "ddd"))</f>
+        <v>Thu</v>
+      </c>
+      <c r="D39" s="318">
+        <v>0.5</v>
+      </c>
+      <c r="E39" s="318">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F39" s="319">
+        <f t="shared" ref="F39" si="14">((E39 - D39) * 24)</f>
+        <v>3.9999999999999991</v>
+      </c>
+      <c r="G39" s="317">
+        <f t="shared" ref="G39" si="15">IF(F39 &gt; 4, (F39 - 1), F39)</f>
+        <v>3.9999999999999991</v>
+      </c>
+      <c r="H39" s="320" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="321" t="s">
+        <v>93</v>
+      </c>
+      <c r="L39" s="60" t="str">
+        <f t="shared" ref="L39" ca="1" si="16">IF(C39 = "TBD", "TBD", IF(B39 = "", "IDK!!", IF(TODAY() &gt; B39, "Passed", IF(TODAY() = B39, "Today!!", "Upcoming"))))</f>
+        <v>Passed</v>
+      </c>
+      <c r="N39" s="351"/>
+      <c r="O39" s="352"/>
+      <c r="P39" s="353"/>
+    </row>
+    <row r="40" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B40" s="124">
         <v>46353</v>
       </c>
-      <c r="C39" s="173" t="str">
+      <c r="C40" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D39" s="155">
+      <c r="D40" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E39" s="155">
+      <c r="E40" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F39" s="226">
+      <c r="F40" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G39" s="173">
+      <c r="G40" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H39" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I39" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="269" t="s">
+      <c r="H40" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="L39" s="192" t="str">
+      <c r="L40" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N39" s="351" t="s">
+      <c r="N40" s="351" t="s">
         <v>77</v>
       </c>
-      <c r="O39" s="352">
+      <c r="O40" s="352">
         <f>O38+1</f>
         <v>2025</v>
       </c>
-      <c r="P39" s="353">
+      <c r="P40" s="353">
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="2:16">
-      <c r="B40" s="112">
+    <row r="41" spans="2:16">
+      <c r="B41" s="112">
         <v>46380</v>
       </c>
-      <c r="C40" s="264" t="str">
+      <c r="C41" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D40" s="262">
+      <c r="D41" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E40" s="262">
+      <c r="E41" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F40" s="263">
+      <c r="F41" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G40" s="264">
+      <c r="G41" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H40" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="266" t="s">
+      <c r="H41" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="L40" s="42" t="str">
+      <c r="L41" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N40" s="343" t="s">
+      <c r="N41" s="343" t="s">
         <v>78</v>
       </c>
-      <c r="O40" s="70">
-        <f>O39+1</f>
+      <c r="O41" s="70">
+        <f>O40+1</f>
         <v>2026</v>
       </c>
-      <c r="P40" s="344">
+      <c r="P41" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="2:16">
-      <c r="B41" s="120">
+    <row r="42" spans="2:16">
+      <c r="B42" s="120">
         <v>46384</v>
       </c>
-      <c r="C41" s="274" t="str">
+      <c r="C42" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D41" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E41" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F41" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G41" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H41" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="L41" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="N41" s="343" t="s">
-        <v>79</v>
-      </c>
-      <c r="O41" s="70">
-        <f t="shared" ref="O41:O47" si="13">O40+1</f>
-        <v>2027</v>
-      </c>
-      <c r="P41" s="344">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16">
-      <c r="B42" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C42" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
       <c r="D42" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -6119,47 +6118,47 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F42" s="276">
-        <f t="shared" ref="F42:F44" si="14">((E42 - D42) * 24)</f>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G42" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H42" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="273" t="s">
+      <c r="H42" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="L42" s="193" t="str">
+      <c r="L42" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
       <c r="N42" s="343" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O42" s="70">
-        <f t="shared" si="13"/>
-        <v>2028</v>
+        <f t="shared" ref="O42:O48" si="17">O41+1</f>
+        <v>2027</v>
       </c>
       <c r="P42" s="344">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="2:16">
       <c r="B43" s="270">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C43" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D43" s="275">
         <v>0.29166666666666669</v>
@@ -6168,7 +6167,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F43" s="276">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="F43:F45" si="18">((E43 - D43) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G43" s="274">
@@ -6192,23 +6191,23 @@
         <v>Upcoming</v>
       </c>
       <c r="N43" s="343" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O43" s="70">
-        <f t="shared" si="13"/>
-        <v>2029</v>
+        <f t="shared" si="17"/>
+        <v>2028</v>
       </c>
       <c r="P43" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B44" s="113">
-        <v>46387</v>
+    <row r="44" spans="2:16">
+      <c r="B44" s="270">
+        <v>46386</v>
       </c>
       <c r="C44" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D44" s="275">
         <v>0.29166666666666669</v>
@@ -6217,23 +6216,23 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F44" s="276">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G44" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H44" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="268" t="s">
+      <c r="H44" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="273" t="s">
         <v>60</v>
       </c>
       <c r="L44" s="193" t="str">
@@ -6241,135 +6240,184 @@
         <v>Upcoming</v>
       </c>
       <c r="N44" s="343" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O44" s="70">
-        <f t="shared" si="13"/>
-        <v>2030</v>
+        <f t="shared" si="17"/>
+        <v>2029</v>
       </c>
       <c r="P44" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="45" spans="2:16">
-      <c r="B45" s="102"/>
-      <c r="C45" s="165" t="str">
-        <f t="shared" ref="C45:C46" si="15">IF(ISNUMBER(FIND("?", B45, 1)), "TBD", TEXT(B45, "ddd"))</f>
-        <v>Sat</v>
-      </c>
-      <c r="D45" s="157"/>
-      <c r="E45" s="157"/>
-      <c r="F45" s="220">
-        <f t="shared" ref="F45:F46" si="16">((E45 - D45) * 24)</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="217">
-        <f t="shared" ref="G45:G46" si="17">IF(F45 &gt; 4, (F45 - 1), F45)</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="180"/>
-      <c r="I45" s="197" t="s">
-        <v>66</v>
-      </c>
-      <c r="J45" s="197" t="s">
-        <v>66</v>
-      </c>
-      <c r="K45" s="205"/>
-      <c r="L45" s="252" t="str">
-        <f t="shared" ref="L45:L46" ca="1" si="18">IF(C45 = "TBD", "TBD", IF(B45 = "", "IDK!!", IF(TODAY() &gt; B45, "Passed", IF(TODAY() = B45, "Today!!", "Upcoming"))))</f>
-        <v>IDK!!</v>
+    <row r="45" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B45" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C45" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D45" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E45" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F45" s="276">
+        <f t="shared" si="18"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G45" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H45" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="L45" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
       </c>
       <c r="N45" s="343" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O45" s="70">
-        <f t="shared" si="13"/>
-        <v>2031</v>
+        <f t="shared" si="17"/>
+        <v>2030</v>
       </c>
       <c r="P45" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B46" s="259"/>
-      <c r="C46" s="253" t="str">
-        <f t="shared" si="15"/>
+    <row r="46" spans="2:16">
+      <c r="B46" s="102"/>
+      <c r="C46" s="165" t="str">
+        <f t="shared" ref="C46:C47" si="19">IF(ISNUMBER(FIND("?", B46, 1)), "TBD", TEXT(B46, "ddd"))</f>
         <v>Sat</v>
       </c>
-      <c r="D46" s="260"/>
-      <c r="E46" s="260"/>
-      <c r="F46" s="261">
-        <f t="shared" si="16"/>
+      <c r="D46" s="157"/>
+      <c r="E46" s="157"/>
+      <c r="F46" s="220">
+        <f t="shared" ref="F46:F47" si="20">((E46 - D46) * 24)</f>
         <v>0</v>
       </c>
-      <c r="G46" s="253">
+      <c r="G46" s="217">
+        <f t="shared" ref="G46:G47" si="21">IF(F46 &gt; 4, (F46 - 1), F46)</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="180"/>
+      <c r="I46" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="J46" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="K46" s="205"/>
+      <c r="L46" s="252" t="str">
+        <f t="shared" ref="L46:L47" ca="1" si="22">IF(C46 = "TBD", "TBD", IF(B46 = "", "IDK!!", IF(TODAY() &gt; B46, "Passed", IF(TODAY() = B46, "Today!!", "Upcoming"))))</f>
+        <v>IDK!!</v>
+      </c>
+      <c r="N46" s="343" t="s">
+        <v>83</v>
+      </c>
+      <c r="O46" s="70">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="254"/>
-      <c r="I46" s="202" t="s">
-        <v>66</v>
-      </c>
-      <c r="J46" s="202" t="s">
-        <v>66</v>
-      </c>
-      <c r="K46" s="255"/>
-      <c r="L46" s="251" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v>IDK!!</v>
-      </c>
-      <c r="N46" s="343" t="s">
-        <v>84</v>
-      </c>
-      <c r="O46" s="70">
-        <f t="shared" si="13"/>
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="P46" s="344">
         <v>176</v>
       </c>
     </row>
     <row r="47" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B47" s="86" t="s">
+      <c r="B47" s="259"/>
+      <c r="C47" s="253" t="str">
+        <f t="shared" si="19"/>
+        <v>Sat</v>
+      </c>
+      <c r="D47" s="260"/>
+      <c r="E47" s="260"/>
+      <c r="F47" s="261">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="253">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="254"/>
+      <c r="I47" s="202" t="s">
+        <v>66</v>
+      </c>
+      <c r="J47" s="202" t="s">
+        <v>66</v>
+      </c>
+      <c r="K47" s="255"/>
+      <c r="L47" s="251" t="str">
+        <f t="shared" ca="1" si="22"/>
+        <v>IDK!!</v>
+      </c>
+      <c r="N47" s="343" t="s">
+        <v>84</v>
+      </c>
+      <c r="O47" s="70">
+        <f t="shared" si="17"/>
+        <v>2032</v>
+      </c>
+      <c r="P47" s="344">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B48" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="303"/>
-      <c r="D47" s="304"/>
-      <c r="E47" s="305"/>
-      <c r="F47" s="228">
-        <f>SUM(F14:F46)</f>
-        <v>175.5</v>
-      </c>
-      <c r="G47" s="256">
-        <f>SUM(G14:G46)</f>
-        <v>152.5</v>
-      </c>
-      <c r="H47" s="301"/>
-      <c r="I47" s="302"/>
-      <c r="J47" s="302"/>
-      <c r="K47" s="302"/>
-      <c r="L47" s="302"/>
-      <c r="N47" s="345" t="s">
+      <c r="C48" s="303"/>
+      <c r="D48" s="304"/>
+      <c r="E48" s="305"/>
+      <c r="F48" s="228">
+        <f>SUM(F14:F47)</f>
+        <v>179.5</v>
+      </c>
+      <c r="G48" s="256">
+        <f>SUM(G14:G47)</f>
+        <v>156.5</v>
+      </c>
+      <c r="H48" s="301"/>
+      <c r="I48" s="302"/>
+      <c r="J48" s="302"/>
+      <c r="K48" s="302"/>
+      <c r="L48" s="302"/>
+      <c r="N48" s="345" t="s">
         <v>85</v>
       </c>
-      <c r="O47" s="346">
-        <f t="shared" si="13"/>
+      <c r="O48" s="346">
+        <f t="shared" si="17"/>
         <v>2033</v>
       </c>
-      <c r="P47" s="347">
+      <c r="P48" s="347">
         <f>192 + 10</f>
         <v>202</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B13:K47" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <autoFilter ref="B13:K48" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B14:L46">
+  <conditionalFormatting sqref="B14:L47">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F46 L14:L46">
+  <conditionalFormatting sqref="C14:F47 L14:L47">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -6384,7 +6432,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J46">
+  <conditionalFormatting sqref="I14:J47">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
